--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD4E200-275A-43C2-B321-B9CF901C8A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6676DE-052C-4BF0-98D8-190CF8C7583E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="274">
   <si>
     <t>HITO</t>
   </si>
@@ -701,9 +701,6 @@
     <t>Condicionado. 1 ejem para todos los tipos</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1 HOME </t>
-  </si>
-  <si>
     <t>validación contenidos</t>
   </si>
   <si>
@@ -782,12 +779,6 @@
     <t>En curso. No final. Fase 2</t>
   </si>
   <si>
-    <t>Suma y links (15/10/2026)</t>
-  </si>
-  <si>
-    <t>Suma y links</t>
-  </si>
-  <si>
     <t>85% Finalizado.  Ajustes css</t>
   </si>
   <si>
@@ -846,6 +837,30 @@
   </si>
   <si>
     <t>80% Finalizado. 1ra prueba hecha.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+I de información es un tooltip https://getbootstrap.com/docs/5.0/components/tooltips/ cualquier cosa nos comentáis pues tenemos el código en local
+La i he visto que tenía una BKTT-Icon dentro de otro BKTT-Icon. El padre debería ser BKTT-Button btn btn-link. I si el icono de dentro es &lt;i class="fa-regular fa-info"&gt;&lt;/i&gt; en vez del cicle fenomenal
+Las a's que entiendo que son los botones de CTA, deberían de tener la siguiente class BKTT-Button btn btn-primary. Sobre todo BKTT-Button</t>
+  </si>
+  <si>
+    <t>Muy dificil rojoy media amarillo</t>
+  </si>
+  <si>
+    <t>3.1 HOME http://turi.santurtzi.com/es-es/Paginas/Default2.aspx</t>
+  </si>
+  <si>
+    <t>SUMMARYLINKSLIDER2026</t>
+  </si>
+  <si>
+    <t>SUMMARYLINK2026</t>
+  </si>
+  <si>
+    <t>SUMMARYLINKSLIDER2026 (15/10/2026)</t>
+  </si>
+  <si>
+    <t>SUMMARYLINK2026 (15/10/2026)</t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1031,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1149,6 +1164,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1164,7 +1185,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1330,6 +1351,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1641,7 +1665,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AI125"/>
+  <dimension ref="A1:AL126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="49" customWidth="1"/>
@@ -1667,10 +1691,11 @@
     <col min="31" max="31" width="17.5546875" style="19" customWidth="1"/>
     <col min="32" max="32" width="12.88671875" style="19" customWidth="1"/>
     <col min="33" max="33" width="18.44140625" customWidth="1"/>
+    <col min="36" max="36" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="22.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:35" ht="216" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" ht="22.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="1:38" ht="216" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1757,7 +1782,7 @@
         <v>179</v>
       </c>
       <c r="AD2" s="35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE2" s="35" t="s">
         <v>180</v>
@@ -1766,7 +1791,7 @@
         <v>179</v>
       </c>
       <c r="AG2" s="35" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AH2" s="35" t="s">
         <v>180</v>
@@ -1774,8 +1799,17 @@
       <c r="AI2" s="35" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ2" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="AK2" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="AL2" s="35" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A3" s="50">
         <v>0</v>
       </c>
@@ -1819,8 +1853,13 @@
       </c>
       <c r="AH3" s="19"/>
       <c r="AI3" s="19"/>
-    </row>
-    <row r="4" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ3" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK3" s="19"/>
+      <c r="AL3" s="19"/>
+    </row>
+    <row r="4" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D4" s="30" t="s">
         <v>13</v>
       </c>
@@ -1845,8 +1884,11 @@
       <c r="AG4" s="19"/>
       <c r="AH4" s="19"/>
       <c r="AI4" s="19"/>
-    </row>
-    <row r="5" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ4" s="19"/>
+      <c r="AK4" s="19"/>
+      <c r="AL4" s="19"/>
+    </row>
+    <row r="5" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D5" s="19" t="s">
         <v>16</v>
       </c>
@@ -1857,8 +1899,11 @@
       <c r="AG5" s="19"/>
       <c r="AH5" s="19"/>
       <c r="AI5" s="19"/>
-    </row>
-    <row r="6" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ5" s="19"/>
+      <c r="AK5" s="19"/>
+      <c r="AL5" s="19"/>
+    </row>
+    <row r="6" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D6" s="30" t="s">
         <v>17</v>
       </c>
@@ -1883,8 +1928,11 @@
       <c r="AG6" s="19"/>
       <c r="AH6" s="19"/>
       <c r="AI6" s="19"/>
-    </row>
-    <row r="7" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ6" s="19"/>
+      <c r="AK6" s="19"/>
+      <c r="AL6" s="19"/>
+    </row>
+    <row r="7" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D7" s="19" t="s">
         <v>20</v>
       </c>
@@ -1895,8 +1943,11 @@
       <c r="AG7" s="19"/>
       <c r="AH7" s="19"/>
       <c r="AI7" s="19"/>
-    </row>
-    <row r="8" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ7" s="19"/>
+      <c r="AK7" s="19"/>
+      <c r="AL7" s="19"/>
+    </row>
+    <row r="8" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D8" s="31" t="s">
         <v>21</v>
       </c>
@@ -1921,8 +1972,11 @@
       <c r="AG8" s="19"/>
       <c r="AH8" s="19"/>
       <c r="AI8" s="19"/>
-    </row>
-    <row r="9" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ8" s="19"/>
+      <c r="AK8" s="19"/>
+      <c r="AL8" s="19"/>
+    </row>
+    <row r="9" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D9" s="19" t="s">
         <v>22</v>
       </c>
@@ -1933,8 +1987,11 @@
       <c r="AG9" s="19"/>
       <c r="AH9" s="19"/>
       <c r="AI9" s="19"/>
-    </row>
-    <row r="10" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ9" s="19"/>
+      <c r="AK9" s="19"/>
+      <c r="AL9" s="19"/>
+    </row>
+    <row r="10" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A10" s="50">
         <v>1</v>
       </c>
@@ -1974,8 +2031,11 @@
       <c r="AG10" s="19"/>
       <c r="AH10" s="19"/>
       <c r="AI10" s="19"/>
-    </row>
-    <row r="11" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ10" s="19"/>
+      <c r="AK10" s="19"/>
+      <c r="AL10" s="19"/>
+    </row>
+    <row r="11" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>26</v>
       </c>
@@ -2020,8 +2080,13 @@
       </c>
       <c r="AH11" s="19"/>
       <c r="AI11" s="19"/>
-    </row>
-    <row r="12" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ11" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK11" s="19"/>
+      <c r="AL11" s="19"/>
+    </row>
+    <row r="12" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>30</v>
       </c>
@@ -2041,8 +2106,11 @@
       <c r="AG12" s="19"/>
       <c r="AH12" s="19"/>
       <c r="AI12" s="19"/>
-    </row>
-    <row r="13" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ12" s="19"/>
+      <c r="AK12" s="19"/>
+      <c r="AL12" s="19"/>
+    </row>
+    <row r="13" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>31</v>
       </c>
@@ -2062,8 +2130,11 @@
       <c r="AG13" s="19"/>
       <c r="AH13" s="19"/>
       <c r="AI13" s="19"/>
-    </row>
-    <row r="14" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ13" s="19"/>
+      <c r="AK13" s="19"/>
+      <c r="AL13" s="19"/>
+    </row>
+    <row r="14" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>32</v>
       </c>
@@ -2083,8 +2154,11 @@
       <c r="AG14" s="19"/>
       <c r="AH14" s="19"/>
       <c r="AI14" s="19"/>
-    </row>
-    <row r="15" spans="1:35" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ14" s="19"/>
+      <c r="AK14" s="19"/>
+      <c r="AL14" s="19"/>
+    </row>
+    <row r="15" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>33</v>
       </c>
@@ -2111,17 +2185,22 @@
         <v>214</v>
       </c>
       <c r="AD15" s="56" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AE15" s="33"/>
       <c r="AF15" s="33"/>
       <c r="AG15" s="43" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AH15" s="19"/>
       <c r="AI15" s="19"/>
-    </row>
-    <row r="16" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ15" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="AK15" s="19"/>
+      <c r="AL15" s="19"/>
+    </row>
+    <row r="16" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>34</v>
       </c>
@@ -2141,8 +2220,11 @@
       <c r="AG16" s="19"/>
       <c r="AH16" s="19"/>
       <c r="AI16" s="19"/>
-    </row>
-    <row r="17" spans="1:35" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ16" s="19"/>
+      <c r="AK16" s="19"/>
+      <c r="AL16" s="19"/>
+    </row>
+    <row r="17" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>35</v>
       </c>
@@ -2183,10 +2265,17 @@
       </c>
       <c r="AH17" s="19"/>
       <c r="AI17" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="18" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ17" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>36</v>
       </c>
@@ -2206,8 +2295,11 @@
       <c r="AG18" s="19"/>
       <c r="AH18" s="19"/>
       <c r="AI18" s="19"/>
-    </row>
-    <row r="19" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ18" s="19"/>
+      <c r="AK18" s="19"/>
+      <c r="AL18" s="19"/>
+    </row>
+    <row r="19" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>37</v>
       </c>
@@ -2227,8 +2319,11 @@
       <c r="AG19" s="19"/>
       <c r="AH19" s="19"/>
       <c r="AI19" s="19"/>
-    </row>
-    <row r="20" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ19" s="19"/>
+      <c r="AK19" s="19"/>
+      <c r="AL19" s="19"/>
+    </row>
+    <row r="20" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>38</v>
       </c>
@@ -2254,8 +2349,11 @@
       <c r="AG20" s="19"/>
       <c r="AH20" s="19"/>
       <c r="AI20" s="19"/>
-    </row>
-    <row r="21" spans="1:35" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ20" s="19"/>
+      <c r="AK20" s="19"/>
+      <c r="AL20" s="19"/>
+    </row>
+    <row r="21" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
         <v>39</v>
       </c>
@@ -2306,10 +2404,19 @@
         <v>206</v>
       </c>
       <c r="AI21" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="22" spans="1:35" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ21" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK21" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL21" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>40</v>
       </c>
@@ -2329,8 +2436,11 @@
       <c r="AG22" s="19"/>
       <c r="AH22" s="19"/>
       <c r="AI22" s="19"/>
-    </row>
-    <row r="23" spans="1:35" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ22" s="19"/>
+      <c r="AK22" s="19"/>
+      <c r="AL22" s="19"/>
+    </row>
+    <row r="23" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A23" s="30" t="s">
         <v>41</v>
       </c>
@@ -2370,11 +2480,18 @@
         <v>166</v>
       </c>
       <c r="AH23" s="19" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AI23" s="19"/>
-    </row>
-    <row r="24" spans="1:35" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AJ23" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK23" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="AL23" s="19"/>
+    </row>
+    <row r="24" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>42</v>
       </c>
@@ -2394,8 +2511,11 @@
       <c r="AG24" s="19"/>
       <c r="AH24" s="19"/>
       <c r="AI24" s="19"/>
-    </row>
-    <row r="25" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ24" s="19"/>
+      <c r="AK24" s="19"/>
+      <c r="AL24" s="19"/>
+    </row>
+    <row r="25" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2568,11 @@
       <c r="AG25" s="19"/>
       <c r="AH25" s="19"/>
       <c r="AI25" s="19"/>
-    </row>
-    <row r="26" spans="1:35" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AJ25" s="19"/>
+      <c r="AK25" s="19"/>
+      <c r="AL25" s="19"/>
+    </row>
+    <row r="26" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>175</v>
       </c>
@@ -2477,10 +2600,17 @@
       </c>
       <c r="AH26" s="19"/>
       <c r="AI26" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="27" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ26" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK26" s="19"/>
+      <c r="AL26" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="30" t="s">
         <v>45</v>
       </c>
@@ -2516,8 +2646,11 @@
       <c r="AG27" s="19"/>
       <c r="AH27" s="19"/>
       <c r="AI27" s="19"/>
-    </row>
-    <row r="28" spans="1:35" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AJ27" s="19"/>
+      <c r="AK27" s="19"/>
+      <c r="AL27" s="19"/>
+    </row>
+    <row r="28" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>173</v>
       </c>
@@ -2545,10 +2678,17 @@
       </c>
       <c r="AH28" s="19"/>
       <c r="AI28" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="29" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ28" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK28" s="19"/>
+      <c r="AL28" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
         <v>46</v>
       </c>
@@ -2584,10 +2724,17 @@
       </c>
       <c r="AH29" s="19"/>
       <c r="AI29" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="30" spans="1:35" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ29" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK29" s="19"/>
+      <c r="AL29" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
         <v>47</v>
       </c>
@@ -2629,7 +2776,7 @@
         <v>207</v>
       </c>
       <c r="AD30" s="58" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AE30" s="33"/>
       <c r="AF30" s="33"/>
@@ -2638,10 +2785,17 @@
       </c>
       <c r="AH30" s="19"/>
       <c r="AI30" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="31" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ30" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK30" s="19"/>
+      <c r="AL30" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>48</v>
       </c>
@@ -2669,10 +2823,17 @@
       </c>
       <c r="AH31" s="19"/>
       <c r="AI31" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="32" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ31" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK31" s="19"/>
+      <c r="AL31" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>49</v>
       </c>
@@ -2689,8 +2850,11 @@
       <c r="AG32" s="19"/>
       <c r="AH32" s="19"/>
       <c r="AI32" s="19"/>
-    </row>
-    <row r="33" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ32" s="19"/>
+      <c r="AK32" s="19"/>
+      <c r="AL32" s="19"/>
+    </row>
+    <row r="33" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A33" s="50">
         <v>2</v>
       </c>
@@ -2709,8 +2873,11 @@
       <c r="AG33" s="19"/>
       <c r="AH33" s="19"/>
       <c r="AI33" s="19"/>
-    </row>
-    <row r="34" spans="1:35" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ33" s="19"/>
+      <c r="AK33" s="19"/>
+      <c r="AL33" s="19"/>
+    </row>
+    <row r="34" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A34" s="30" t="s">
         <v>52</v>
       </c>
@@ -2735,8 +2902,11 @@
       <c r="AG34" s="19"/>
       <c r="AH34" s="19"/>
       <c r="AI34" s="19"/>
-    </row>
-    <row r="35" spans="1:35" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ34" s="19"/>
+      <c r="AK34" s="19"/>
+      <c r="AL34" s="19"/>
+    </row>
+    <row r="35" spans="1:38" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>177</v>
       </c>
@@ -2781,26 +2951,35 @@
         <v>185</v>
       </c>
       <c r="AC35" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AD35" s="60" t="s">
         <v>208</v>
       </c>
       <c r="AE35" s="33" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF35" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG35" s="45" t="s">
         <v>167</v>
       </c>
       <c r="AH35" s="19"/>
       <c r="AI35" s="19" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="36" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+      <c r="AJ35" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK35" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="AL35" s="19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>54</v>
       </c>
@@ -2841,8 +3020,11 @@
       <c r="AG36" s="19"/>
       <c r="AH36" s="19"/>
       <c r="AI36" s="19"/>
-    </row>
-    <row r="37" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ36" s="19"/>
+      <c r="AK36" s="19"/>
+      <c r="AL36" s="19"/>
+    </row>
+    <row r="37" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>55</v>
       </c>
@@ -2871,8 +3053,11 @@
       <c r="AG37" s="19"/>
       <c r="AH37" s="19"/>
       <c r="AI37" s="19"/>
-    </row>
-    <row r="38" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ37" s="19"/>
+      <c r="AK37" s="19"/>
+      <c r="AL37" s="19"/>
+    </row>
+    <row r="38" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>56</v>
       </c>
@@ -2895,8 +3080,11 @@
       <c r="AG38" s="19"/>
       <c r="AH38" s="19"/>
       <c r="AI38" s="19"/>
-    </row>
-    <row r="39" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ38" s="19"/>
+      <c r="AK38" s="19"/>
+      <c r="AL38" s="19"/>
+    </row>
+    <row r="39" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>57</v>
       </c>
@@ -2925,8 +3113,11 @@
       <c r="AG39" s="19"/>
       <c r="AH39" s="19"/>
       <c r="AI39" s="19"/>
-    </row>
-    <row r="40" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ39" s="19"/>
+      <c r="AK39" s="19"/>
+      <c r="AL39" s="19"/>
+    </row>
+    <row r="40" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>58</v>
       </c>
@@ -2955,8 +3146,11 @@
       <c r="AG40" s="19"/>
       <c r="AH40" s="19"/>
       <c r="AI40" s="19"/>
-    </row>
-    <row r="41" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ40" s="19"/>
+      <c r="AK40" s="19"/>
+      <c r="AL40" s="19"/>
+    </row>
+    <row r="41" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>59</v>
       </c>
@@ -2985,8 +3179,11 @@
       <c r="AG41" s="19"/>
       <c r="AH41" s="19"/>
       <c r="AI41" s="19"/>
-    </row>
-    <row r="42" spans="1:35" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AJ41" s="19"/>
+      <c r="AK41" s="19"/>
+      <c r="AL41" s="19"/>
+    </row>
+    <row r="42" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>60</v>
       </c>
@@ -3015,8 +3212,11 @@
       <c r="AG42" s="19"/>
       <c r="AH42" s="19"/>
       <c r="AI42" s="19"/>
-    </row>
-    <row r="43" spans="1:35" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ42" s="19"/>
+      <c r="AK42" s="19"/>
+      <c r="AL42" s="19"/>
+    </row>
+    <row r="43" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>62</v>
       </c>
@@ -3053,25 +3253,30 @@
         <v>220</v>
       </c>
       <c r="AB43" s="54" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AC43" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AD43" s="58" t="s">
         <v>220</v>
       </c>
       <c r="AE43" s="33"/>
       <c r="AF43" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG43" s="47"/>
       <c r="AH43" s="19"/>
       <c r="AI43" s="19" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="44" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+      <c r="AJ43" s="47"/>
+      <c r="AK43" s="19"/>
+      <c r="AL43" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="44" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C44" s="25" t="s">
         <v>63</v>
       </c>
@@ -3103,10 +3308,13 @@
       <c r="AG44" s="47"/>
       <c r="AH44" s="19"/>
       <c r="AI44" s="19"/>
-    </row>
-    <row r="45" spans="1:35" ht="72" x14ac:dyDescent="0.3">
+      <c r="AJ44" s="47"/>
+      <c r="AK44" s="19"/>
+      <c r="AL44" s="19"/>
+    </row>
+    <row r="45" spans="1:38" ht="72" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
-        <v>221</v>
+        <v>269</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>64</v>
@@ -3136,7 +3344,7 @@
         <v>219</v>
       </c>
       <c r="AC45" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AD45" s="58" t="s">
         <v>209</v>
@@ -3145,19 +3353,28 @@
         <v>219</v>
       </c>
       <c r="AF45" s="33" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AG45" s="44" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AH45" s="19" t="s">
         <v>219</v>
       </c>
       <c r="AI45" s="19" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="46" spans="1:35" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+      <c r="AJ45" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="AK45" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="AL45" s="19" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="46" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>66</v>
       </c>
@@ -3210,8 +3427,15 @@
         <v>210</v>
       </c>
       <c r="AI46" s="19"/>
-    </row>
-    <row r="47" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ46" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK46" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AL46" s="19"/>
+    </row>
+    <row r="47" spans="1:38" ht="43.2" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
         <v>67</v>
       </c>
@@ -3264,8 +3488,15 @@
         <v>210</v>
       </c>
       <c r="AI47" s="19"/>
-    </row>
-    <row r="48" spans="1:35" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ47" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK47" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="AL47" s="19"/>
+    </row>
+    <row r="48" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
         <v>68</v>
       </c>
@@ -3321,10 +3552,17 @@
         <v>186</v>
       </c>
       <c r="AI48" s="19"/>
-    </row>
-    <row r="49" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ48" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK48" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="AL48" s="19"/>
+    </row>
+    <row r="49" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A49" s="32" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D49" s="33"/>
       <c r="E49" s="6"/>
@@ -3339,10 +3577,15 @@
       </c>
       <c r="AH49" s="19"/>
       <c r="AI49" s="19"/>
-    </row>
-    <row r="50" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ49" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK49" s="19"/>
+      <c r="AL49" s="19"/>
+    </row>
+    <row r="50" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="6"/>
@@ -3360,10 +3603,15 @@
       </c>
       <c r="AH50" s="19"/>
       <c r="AI50" s="19"/>
-    </row>
-    <row r="51" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ50" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK50" s="19"/>
+      <c r="AL50" s="19"/>
+    </row>
+    <row r="51" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D51" s="33"/>
       <c r="E51" s="6"/>
@@ -3381,10 +3629,15 @@
       </c>
       <c r="AH51" s="19"/>
       <c r="AI51" s="19"/>
-    </row>
-    <row r="52" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ51" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK51" s="19"/>
+      <c r="AL51" s="19"/>
+    </row>
+    <row r="52" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D52" s="33"/>
       <c r="E52" s="6"/>
@@ -3402,10 +3655,15 @@
       </c>
       <c r="AH52" s="19"/>
       <c r="AI52" s="19"/>
-    </row>
-    <row r="53" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ52" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK52" s="19"/>
+      <c r="AL52" s="19"/>
+    </row>
+    <row r="53" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D53" s="33"/>
       <c r="E53" s="6"/>
@@ -3423,10 +3681,15 @@
       </c>
       <c r="AH53" s="19"/>
       <c r="AI53" s="19"/>
-    </row>
-    <row r="54" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ53" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK53" s="19"/>
+      <c r="AL53" s="19"/>
+    </row>
+    <row r="54" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A54" s="32" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D54" s="33"/>
       <c r="E54" s="6"/>
@@ -3444,10 +3707,15 @@
       </c>
       <c r="AH54" s="19"/>
       <c r="AI54" s="19"/>
-    </row>
-    <row r="55" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ54" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK54" s="19"/>
+      <c r="AL54" s="19"/>
+    </row>
+    <row r="55" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D55" s="33"/>
       <c r="E55" s="6"/>
@@ -3465,10 +3733,15 @@
       </c>
       <c r="AH55" s="19"/>
       <c r="AI55" s="19"/>
-    </row>
-    <row r="56" spans="1:35" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ55" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK55" s="19"/>
+      <c r="AL55" s="19"/>
+    </row>
+    <row r="56" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D56" s="33"/>
       <c r="E56" s="6"/>
@@ -3486,8 +3759,13 @@
       </c>
       <c r="AH56" s="19"/>
       <c r="AI56" s="19"/>
-    </row>
-    <row r="57" spans="1:35" ht="72" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AJ56" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK56" s="19"/>
+      <c r="AL56" s="19"/>
+    </row>
+    <row r="57" spans="1:38" ht="72" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A57" s="33" t="s">
         <v>171</v>
       </c>
@@ -3530,20 +3808,27 @@
         <v>167</v>
       </c>
       <c r="AE57" s="62" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AF57" s="33"/>
       <c r="AG57" s="45" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AH57" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AI57" s="19"/>
-    </row>
-    <row r="58" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ57" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="AK57" s="55" t="s">
+        <v>241</v>
+      </c>
+      <c r="AL57" s="19"/>
+    </row>
+    <row r="58" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A58" s="50" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B58" s="16" t="s">
         <v>69</v>
@@ -3576,13 +3861,16 @@
       <c r="AG58" s="19"/>
       <c r="AH58" s="19"/>
       <c r="AI58" s="19"/>
-    </row>
-    <row r="59" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ58" s="19"/>
+      <c r="AK58" s="19"/>
+      <c r="AL58" s="19"/>
+    </row>
+    <row r="59" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
@@ -3601,13 +3889,18 @@
       </c>
       <c r="AH59" s="19"/>
       <c r="AI59" s="19"/>
-    </row>
-    <row r="60" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ59" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK59" s="19"/>
+      <c r="AL59" s="19"/>
+    </row>
+    <row r="60" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -3625,13 +3918,18 @@
       </c>
       <c r="AH60" s="19"/>
       <c r="AI60" s="19"/>
-    </row>
-    <row r="61" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ60" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK60" s="19"/>
+      <c r="AL60" s="19"/>
+    </row>
+    <row r="61" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -3649,13 +3947,18 @@
       </c>
       <c r="AH61" s="19"/>
       <c r="AI61" s="19"/>
-    </row>
-    <row r="62" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ61" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK61" s="19"/>
+      <c r="AL61" s="19"/>
+    </row>
+    <row r="62" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -3671,13 +3974,16 @@
       <c r="AG62" s="19"/>
       <c r="AH62" s="19"/>
       <c r="AI62" s="19"/>
-    </row>
-    <row r="63" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ62" s="19"/>
+      <c r="AK62" s="19"/>
+      <c r="AL62" s="19"/>
+    </row>
+    <row r="63" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A63" s="32" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -3695,13 +4001,18 @@
       </c>
       <c r="AH63" s="19"/>
       <c r="AI63" s="19"/>
-    </row>
-    <row r="64" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ63" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK63" s="19"/>
+      <c r="AL63" s="19"/>
+    </row>
+    <row r="64" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A64" s="32" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -3719,13 +4030,18 @@
       </c>
       <c r="AH64" s="19"/>
       <c r="AI64" s="19"/>
-    </row>
-    <row r="65" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ64" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK64" s="19"/>
+      <c r="AL64" s="19"/>
+    </row>
+    <row r="65" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -3743,13 +4059,18 @@
       </c>
       <c r="AH65" s="19"/>
       <c r="AI65" s="19"/>
-    </row>
-    <row r="66" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ65" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK65" s="19"/>
+      <c r="AL65" s="19"/>
+    </row>
+    <row r="66" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A66" s="32" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="6"/>
@@ -3765,8 +4086,11 @@
       <c r="AG66" s="19"/>
       <c r="AH66" s="19"/>
       <c r="AI66" s="19"/>
-    </row>
-    <row r="67" spans="1:35" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ66" s="19"/>
+      <c r="AK66" s="19"/>
+      <c r="AL66" s="19"/>
+    </row>
+    <row r="67" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A67" s="30" t="s">
         <v>71</v>
       </c>
@@ -3806,14 +4130,21 @@
       </c>
       <c r="AF67" s="33"/>
       <c r="AG67" s="46" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AH67" s="19" t="s">
         <v>187</v>
       </c>
       <c r="AI67" s="19"/>
-    </row>
-    <row r="68" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ67" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="AK67" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AL67" s="19"/>
+    </row>
+    <row r="68" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D68" s="13" t="s">
         <v>72</v>
       </c>
@@ -3821,8 +4152,11 @@
       <c r="AG68" s="19"/>
       <c r="AH68" s="19"/>
       <c r="AI68" s="19"/>
-    </row>
-    <row r="69" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ68" s="19"/>
+      <c r="AK68" s="19"/>
+      <c r="AL68" s="19"/>
+    </row>
+    <row r="69" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D69" s="13" t="s">
         <v>73</v>
       </c>
@@ -3830,8 +4164,11 @@
       <c r="AG69" s="19"/>
       <c r="AH69" s="19"/>
       <c r="AI69" s="19"/>
-    </row>
-    <row r="70" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ69" s="19"/>
+      <c r="AK69" s="19"/>
+      <c r="AL69" s="19"/>
+    </row>
+    <row r="70" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D70" s="13" t="s">
         <v>74</v>
       </c>
@@ -3839,8 +4176,11 @@
       <c r="AG70" s="19"/>
       <c r="AH70" s="19"/>
       <c r="AI70" s="19"/>
-    </row>
-    <row r="71" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ70" s="19"/>
+      <c r="AK70" s="19"/>
+      <c r="AL70" s="19"/>
+    </row>
+    <row r="71" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D71" s="13" t="s">
         <v>75</v>
       </c>
@@ -3848,8 +4188,11 @@
       <c r="AG71" s="19"/>
       <c r="AH71" s="19"/>
       <c r="AI71" s="19"/>
-    </row>
-    <row r="72" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ71" s="19"/>
+      <c r="AK71" s="19"/>
+      <c r="AL71" s="19"/>
+    </row>
+    <row r="72" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D72" s="13" t="s">
         <v>76</v>
       </c>
@@ -3857,8 +4200,11 @@
       <c r="AG72" s="19"/>
       <c r="AH72" s="19"/>
       <c r="AI72" s="19"/>
-    </row>
-    <row r="73" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ72" s="19"/>
+      <c r="AK72" s="19"/>
+      <c r="AL72" s="19"/>
+    </row>
+    <row r="73" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D73" s="13" t="s">
         <v>77</v>
       </c>
@@ -3866,8 +4212,11 @@
       <c r="AG73" s="19"/>
       <c r="AH73" s="19"/>
       <c r="AI73" s="19"/>
-    </row>
-    <row r="74" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ73" s="19"/>
+      <c r="AK73" s="19"/>
+      <c r="AL73" s="19"/>
+    </row>
+    <row r="74" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D74" s="13" t="s">
         <v>78</v>
       </c>
@@ -3887,8 +4236,11 @@
       <c r="AG74" s="19"/>
       <c r="AH74" s="19"/>
       <c r="AI74" s="19"/>
-    </row>
-    <row r="75" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ74" s="19"/>
+      <c r="AK74" s="19"/>
+      <c r="AL74" s="19"/>
+    </row>
+    <row r="75" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D75" s="13" t="s">
         <v>79</v>
       </c>
@@ -3908,8 +4260,11 @@
       <c r="AG75" s="19"/>
       <c r="AH75" s="19"/>
       <c r="AI75" s="19"/>
-    </row>
-    <row r="76" spans="1:35" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AJ75" s="19"/>
+      <c r="AK75" s="19"/>
+      <c r="AL75" s="19"/>
+    </row>
+    <row r="76" spans="1:38" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A76" s="23" t="s">
         <v>80</v>
       </c>
@@ -3960,13 +4315,22 @@
         <v>165</v>
       </c>
       <c r="AH76" s="55" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AI76" s="19" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="77" spans="1:35" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ76" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK76" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="AL76" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="77" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>82</v>
       </c>
@@ -3998,17 +4362,24 @@
         <v>165</v>
       </c>
       <c r="AB77" s="55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG77" s="43" t="s">
         <v>165</v>
       </c>
       <c r="AH77" s="55" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AI77" s="19"/>
-    </row>
-    <row r="78" spans="1:35" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ77" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK77" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="AL77" s="19"/>
+    </row>
+    <row r="78" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
         <v>191</v>
       </c>
@@ -4055,16 +4426,25 @@
         <v>188</v>
       </c>
       <c r="AG78" s="43" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AH78" s="55" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AI78" s="19" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="79" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ78" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="AK78" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="AL78" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="79" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>83</v>
       </c>
@@ -4103,8 +4483,13 @@
       </c>
       <c r="AH79" s="19"/>
       <c r="AI79" s="19"/>
-    </row>
-    <row r="80" spans="1:35" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ79" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK79" s="19"/>
+      <c r="AL79" s="19"/>
+    </row>
+    <row r="80" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
         <v>84</v>
       </c>
@@ -4139,20 +4524,27 @@
         <v>192</v>
       </c>
       <c r="AA80" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AB80" s="19" t="s">
         <v>213</v>
       </c>
       <c r="AG80" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AH80" s="19" t="s">
         <v>213</v>
       </c>
       <c r="AI80" s="19"/>
-    </row>
-    <row r="81" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ80" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="AK80" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL80" s="19"/>
+    </row>
+    <row r="81" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>85</v>
       </c>
@@ -4177,8 +4569,11 @@
       <c r="AG81" s="19"/>
       <c r="AH81" s="19"/>
       <c r="AI81" s="19"/>
-    </row>
-    <row r="82" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ81" s="19"/>
+      <c r="AK81" s="19"/>
+      <c r="AL81" s="19"/>
+    </row>
+    <row r="82" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
         <v>79</v>
       </c>
@@ -4207,8 +4602,11 @@
       <c r="AG82" s="19"/>
       <c r="AH82" s="19"/>
       <c r="AI82" s="19"/>
-    </row>
-    <row r="83" spans="1:35" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ82" s="19"/>
+      <c r="AK82" s="19"/>
+      <c r="AL82" s="19"/>
+    </row>
+    <row r="83" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>86</v>
       </c>
@@ -4249,8 +4647,17 @@
       <c r="AI83" s="19" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="84" spans="1:35" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ83" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK83" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL83" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="84" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
         <v>87</v>
       </c>
@@ -4294,8 +4701,17 @@
       <c r="AI84" s="19" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="85" spans="1:35" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ84" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="AK84" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL84" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="85" spans="1:38" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>88</v>
       </c>
@@ -4331,7 +4747,7 @@
         <v>201</v>
       </c>
       <c r="AG85" s="46" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AH85" s="19" t="s">
         <v>193</v>
@@ -4339,8 +4755,17 @@
       <c r="AI85" s="19" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="86" spans="1:35" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AJ85" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="AK85" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL85" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A86" s="50">
         <v>4</v>
       </c>
@@ -4356,8 +4781,11 @@
       <c r="AG86" s="19"/>
       <c r="AH86" s="19"/>
       <c r="AI86" s="19"/>
-    </row>
-    <row r="87" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ86" s="19"/>
+      <c r="AK86" s="19"/>
+      <c r="AL86" s="19"/>
+    </row>
+    <row r="87" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A87" s="49" t="s">
         <v>216</v>
       </c>
@@ -4400,8 +4828,13 @@
       </c>
       <c r="AH87" s="19"/>
       <c r="AI87" s="19"/>
-    </row>
-    <row r="88" spans="1:35" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ87" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK87" s="19"/>
+      <c r="AL87" s="19"/>
+    </row>
+    <row r="88" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A88" s="49" t="s">
         <v>217</v>
       </c>
@@ -4446,22 +4879,31 @@
         <v>168</v>
       </c>
       <c r="AB88" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AC88" s="19" t="s">
         <v>196</v>
       </c>
       <c r="AG88" s="43" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AH88" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AI88" s="19" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="89" spans="1:35" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+      <c r="AJ88" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK88" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL88" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="89" spans="1:38" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A89" s="30" t="s">
         <v>95</v>
       </c>
@@ -4505,17 +4947,24 @@
         <v>168</v>
       </c>
       <c r="AB89" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG89" s="45" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AH89" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AI89" s="19"/>
-    </row>
-    <row r="90" spans="1:35" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ89" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="AK89" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL89" s="19"/>
+    </row>
+    <row r="90" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A90" s="30" t="s">
         <v>97</v>
       </c>
@@ -4547,17 +4996,22 @@
         <v>168</v>
       </c>
       <c r="AB90" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG90" s="19"/>
       <c r="AH90" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AI90" s="19"/>
-    </row>
-    <row r="91" spans="1:35" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ90" s="19"/>
+      <c r="AK90" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AL90" s="19"/>
+    </row>
+    <row r="91" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A91" s="30" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="23" t="s">
@@ -4586,19 +5040,26 @@
         <v>166</v>
       </c>
       <c r="AC91" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG91" s="44" t="s">
         <v>166</v>
       </c>
       <c r="AH91" s="19"/>
       <c r="AI91" s="19" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="92" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+      <c r="AJ91" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK91" s="19"/>
+      <c r="AL91" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="92" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A92" s="30" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="23"/>
@@ -4623,8 +5084,13 @@
       </c>
       <c r="AH92" s="19"/>
       <c r="AI92" s="19"/>
-    </row>
-    <row r="93" spans="1:35" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ92" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK92" s="19"/>
+      <c r="AL92" s="19"/>
+    </row>
+    <row r="93" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A93" s="30" t="s">
         <v>100</v>
       </c>
@@ -4658,17 +5124,24 @@
         <v>168</v>
       </c>
       <c r="AB93" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AG93" s="45" t="s">
         <v>167</v>
       </c>
       <c r="AH93" s="19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AI93" s="19"/>
-    </row>
-    <row r="94" spans="1:35" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ93" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK93" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AL93" s="19"/>
+    </row>
+    <row r="94" spans="1:38" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A94" s="30" t="s">
         <v>102</v>
       </c>
@@ -4717,8 +5190,15 @@
       <c r="AI94" s="19" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="95" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ94" s="19"/>
+      <c r="AK94" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AL94" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="95" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>104</v>
       </c>
@@ -4746,8 +5226,13 @@
       </c>
       <c r="AH95" s="19"/>
       <c r="AI95" s="19"/>
-    </row>
-    <row r="96" spans="1:35" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ95" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK95" s="19"/>
+      <c r="AL95" s="19"/>
+    </row>
+    <row r="96" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A96" s="30" t="s">
         <v>105</v>
       </c>
@@ -4797,8 +5282,17 @@
       <c r="AI96" s="19" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="97" spans="1:35" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ96" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK96" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AL96" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A97" s="30" t="s">
         <v>107</v>
       </c>
@@ -4847,8 +5341,17 @@
       <c r="AI97" s="19" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="98" spans="1:35" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ97" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK97" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL97" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="98" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>109</v>
       </c>
@@ -4884,25 +5387,32 @@
         <v>168</v>
       </c>
       <c r="AB98" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC98" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="AC98" s="19" t="s">
-        <v>227</v>
-      </c>
       <c r="AG98" s="43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AH98" s="19"/>
       <c r="AI98" s="19" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="99" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AJ98" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="AK98" s="19"/>
+      <c r="AL98" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="99" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="6"/>
@@ -4919,75 +5429,76 @@
       <c r="AG99" s="43"/>
       <c r="AH99" s="19"/>
       <c r="AI99" s="19"/>
-    </row>
-    <row r="100" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A100" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C100" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="M100" s="28">
-        <v>156</v>
-      </c>
-      <c r="X100" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA100" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG100" s="46" t="s">
-        <v>203</v>
-      </c>
+      <c r="AJ99" s="43"/>
+      <c r="AK99" s="19"/>
+      <c r="AL99" s="19"/>
+    </row>
+    <row r="100" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" s="13"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="11"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="26"/>
+      <c r="X100" s="37"/>
+      <c r="AA100" s="46"/>
+      <c r="AG100" s="43"/>
       <c r="AH100" s="19"/>
       <c r="AI100" s="19"/>
-    </row>
-    <row r="101" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B101" s="18"/>
-      <c r="C101" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E101" s="6"/>
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
-      <c r="M101" s="26"/>
+      <c r="AJ100" s="43"/>
+      <c r="AK100" s="19"/>
+      <c r="AL100" s="19"/>
+    </row>
+    <row r="101" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A101" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C101" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="M101" s="28">
+        <v>156</v>
+      </c>
       <c r="X101" s="37" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="AA101" s="46" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="AG101" s="46" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="AH101" s="19"/>
       <c r="AI101" s="19"/>
-    </row>
-    <row r="102" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ101" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK101" s="19"/>
+      <c r="AL101" s="19"/>
+    </row>
+    <row r="102" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B102" s="18"/>
       <c r="C102" s="16" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -5010,32 +5521,56 @@
       </c>
       <c r="AH102" s="19"/>
       <c r="AI102" s="19"/>
-    </row>
-    <row r="103" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A103"/>
+      <c r="AJ102" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK102" s="19"/>
+      <c r="AL102" s="19"/>
+    </row>
+    <row r="103" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="B103" s="18"/>
-      <c r="C103"/>
+      <c r="C103" s="16" t="s">
+        <v>116</v>
+      </c>
       <c r="D103" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
-      <c r="H103" s="21"/>
+      <c r="H103" s="21" t="s">
+        <v>115</v>
+      </c>
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
       <c r="M103" s="26"/>
-      <c r="AG103" s="19"/>
+      <c r="X103" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA103" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG103" s="46" t="s">
+        <v>168</v>
+      </c>
       <c r="AH103" s="19"/>
       <c r="AI103" s="19"/>
-    </row>
-    <row r="104" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ103" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK103" s="19"/>
+      <c r="AL103" s="19"/>
+    </row>
+    <row r="104" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A104"/>
       <c r="B104" s="18"/>
       <c r="C104"/>
       <c r="D104" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -5048,13 +5583,16 @@
       <c r="AG104" s="19"/>
       <c r="AH104" s="19"/>
       <c r="AI104" s="19"/>
-    </row>
-    <row r="105" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ104" s="19"/>
+      <c r="AK104" s="19"/>
+      <c r="AL104" s="19"/>
+    </row>
+    <row r="105" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A105"/>
       <c r="B105" s="18"/>
       <c r="C105"/>
       <c r="D105" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -5067,13 +5605,16 @@
       <c r="AG105" s="19"/>
       <c r="AH105" s="19"/>
       <c r="AI105" s="19"/>
-    </row>
-    <row r="106" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ105" s="19"/>
+      <c r="AK105" s="19"/>
+      <c r="AL105" s="19"/>
+    </row>
+    <row r="106" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A106"/>
       <c r="B106" s="18"/>
       <c r="C106"/>
       <c r="D106" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -5086,13 +5627,16 @@
       <c r="AG106" s="19"/>
       <c r="AH106" s="19"/>
       <c r="AI106" s="19"/>
-    </row>
-    <row r="107" spans="1:35" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="AJ106" s="19"/>
+      <c r="AK106" s="19"/>
+      <c r="AL106" s="19"/>
+    </row>
+    <row r="107" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A107"/>
       <c r="B107" s="18"/>
       <c r="C107"/>
       <c r="D107" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -5105,85 +5649,104 @@
       <c r="AG107" s="19"/>
       <c r="AH107" s="19"/>
       <c r="AI107" s="19"/>
-    </row>
-    <row r="108" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="AJ107" s="19"/>
+      <c r="AK107" s="19"/>
+      <c r="AL107" s="19"/>
+    </row>
+    <row r="108" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A108"/>
       <c r="B108" s="18"/>
-      <c r="C108" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D108" s="13"/>
+      <c r="C108"/>
+      <c r="D108" s="13" t="s">
+        <v>122</v>
+      </c>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
-      <c r="H108" s="21" t="s">
-        <v>115</v>
-      </c>
+      <c r="H108" s="21"/>
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
       <c r="M108" s="26"/>
-      <c r="X108" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA108" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG108" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AG108" s="19"/>
       <c r="AH108" s="19"/>
       <c r="AI108" s="19"/>
-    </row>
-    <row r="109" spans="1:35" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A109" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C109" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="M109" s="28">
-        <v>89</v>
-      </c>
-      <c r="X109" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA109" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG109" s="46" t="s">
-        <v>203</v>
+      <c r="AJ108" s="19"/>
+      <c r="AK108" s="19"/>
+      <c r="AL108" s="19"/>
+    </row>
+    <row r="109" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" s="18"/>
+      <c r="C109" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D109" s="13"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="26"/>
+      <c r="X109" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA109" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG109" s="45" t="s">
+        <v>167</v>
       </c>
       <c r="AH109" s="19"/>
       <c r="AI109" s="19"/>
-    </row>
-    <row r="110" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="48"/>
-      <c r="B110" s="18"/>
-      <c r="C110" s="16"/>
-      <c r="D110" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="E110" s="6"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="21"/>
-      <c r="J110" s="6"/>
-      <c r="K110" s="6"/>
-      <c r="L110" s="6"/>
-      <c r="M110" s="26"/>
-    </row>
-    <row r="111" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ109" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK109" s="19"/>
+      <c r="AL109" s="19"/>
+    </row>
+    <row r="110" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A110" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="M110" s="28">
+        <v>89</v>
+      </c>
+      <c r="X110" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA110" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG110" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AH110" s="19"/>
+      <c r="AI110" s="19"/>
+      <c r="AJ110" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK110" s="19"/>
+      <c r="AL110" s="19"/>
+    </row>
+    <row r="111" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A111" s="48"/>
       <c r="B111" s="18"/>
       <c r="C111" s="16"/>
       <c r="D111" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -5194,12 +5757,12 @@
       <c r="L111" s="6"/>
       <c r="M111" s="26"/>
     </row>
-    <row r="112" spans="1:35" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A112" s="48"/>
       <c r="B112" s="18"/>
       <c r="C112" s="16"/>
       <c r="D112" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -5215,7 +5778,7 @@
       <c r="B113" s="18"/>
       <c r="C113" s="16"/>
       <c r="D113" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -5226,36 +5789,38 @@
       <c r="L113" s="6"/>
       <c r="M113" s="26"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A114" s="48"/>
       <c r="B114" s="18"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="19"/>
-      <c r="J114" s="12"/>
-      <c r="K114" s="17"/>
-      <c r="L114" s="17"/>
-      <c r="M114" s="17"/>
+      <c r="C114" s="16"/>
+      <c r="D114" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="21"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="26"/>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D115" s="12"/>
-      <c r="E115" s="6"/>
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="6"/>
+      <c r="A115" s="48"/>
+      <c r="B115" s="18"/>
+      <c r="C115" s="18"/>
+      <c r="D115" s="18"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="18"/>
+      <c r="G115" s="18"/>
+      <c r="H115" s="18"/>
+      <c r="I115" s="19"/>
+      <c r="J115" s="12"/>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
     </row>
-    <row r="116" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A116" s="51"/>
-      <c r="B116" s="8"/>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D116" s="12"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -5265,38 +5830,52 @@
       <c r="J116" s="6"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
-      <c r="M116" s="29">
-        <f>M3+M10+M33+M45+M58+M86+M100+M109</f>
+      <c r="M116" s="17"/>
+    </row>
+    <row r="117" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A117" s="51"/>
+      <c r="B117" s="8"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="6"/>
+      <c r="F117" s="6"/>
+      <c r="G117" s="6"/>
+      <c r="H117" s="6"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6"/>
+      <c r="K117" s="17"/>
+      <c r="L117" s="17"/>
+      <c r="M117" s="29">
+        <f>M3+M10+M33+M45+M58+M86+M101+M110</f>
         <v>825</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A121" s="52" t="s">
+    <row r="122" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A122" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="B121" s="1"/>
-    </row>
-    <row r="122" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A122" s="52" t="s">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="123" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A123" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="B122" s="1"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="B124" s="8"/>
-      <c r="C124" s="15" t="s">
-        <v>133</v>
-      </c>
+      <c r="B123" s="1"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A125" s="51" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B125" s="8"/>
       <c r="C125" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="8"/>
+      <c r="C126" s="15" t="s">
         <v>135</v>
       </c>
     </row>
@@ -5346,6 +5925,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010021AB849DB9524648A8F6CDAE5A42EE85" ma:contentTypeVersion="54" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf342e325584cfc73779b32cd8516cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xmlns:ns3="06fec347-a373-485e-bb4f-f611040a1dd3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97bec9e280156beb57af844d85b9963b" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -5745,15 +6333,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
   <ds:schemaRefs>
@@ -5773,6 +6352,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B271E1E9-4B5A-43C8-93E9-EF9A1A456C27}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5790,12 +6377,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6676DE-052C-4BF0-98D8-190CF8C7583E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D819444C-89CB-4A16-988E-E7D216D3E791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="284">
   <si>
     <t>HITO</t>
   </si>
@@ -839,28 +839,55 @@
     <t>80% Finalizado. 1ra prueba hecha.</t>
   </si>
   <si>
-    <t xml:space="preserve">
-I de información es un tooltip https://getbootstrap.com/docs/5.0/components/tooltips/ cualquier cosa nos comentáis pues tenemos el código en local
-La i he visto que tenía una BKTT-Icon dentro de otro BKTT-Icon. El padre debería ser BKTT-Button btn btn-link. I si el icono de dentro es &lt;i class="fa-regular fa-info"&gt;&lt;/i&gt; en vez del cicle fenomenal
-Las a's que entiendo que son los botones de CTA, deberían de tener la siguiente class BKTT-Button btn btn-primary. Sobre todo BKTT-Button</t>
-  </si>
-  <si>
-    <t>Muy dificil rojoy media amarillo</t>
-  </si>
-  <si>
     <t>3.1 HOME http://turi.santurtzi.com/es-es/Paginas/Default2.aspx</t>
   </si>
   <si>
-    <t>SUMMARYLINKSLIDER2026</t>
-  </si>
-  <si>
-    <t>SUMMARYLINK2026</t>
-  </si>
-  <si>
     <t>SUMMARYLINKSLIDER2026 (15/10/2026)</t>
   </si>
   <si>
     <t>SUMMARYLINK2026 (15/10/2026)</t>
+  </si>
+  <si>
+    <t>Sin comenzar (no prioritario)</t>
+  </si>
+  <si>
+    <t>A la espera modificaciones y definición con DESA. Opción bg transparente?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condicionado a que todos los compoenntes estén "finalizados" sin test wpz. </t>
+  </si>
+  <si>
+    <t>Confirmar que se muestra 3 en vez de 4 por falta de contenido</t>
+  </si>
+  <si>
+    <t>necesaria opción columna o row</t>
+  </si>
+  <si>
+    <t>dropdown submenú https://getbootstrap.com/docs/4.0/components/dropdowns/</t>
+  </si>
+  <si>
+    <t>incluir Servicios?</t>
+  </si>
+  <si>
+    <t>Incluir algún dato más?</t>
+  </si>
+  <si>
+    <t>SUMMARYLINK2026 (destacados)</t>
+  </si>
+  <si>
+    <t>SUMMARYLINKSLIDER2026 (cards slider)</t>
+  </si>
+  <si>
+    <t>Propuesta de nav en email</t>
+  </si>
+  <si>
+    <t>bis anterior</t>
+  </si>
+  <si>
+    <t>no prioritario</t>
+  </si>
+  <si>
+    <t>Pendiente edición padre</t>
   </si>
 </sst>
 </file>
@@ -871,7 +898,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1026,6 +1053,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1185,7 +1220,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1354,6 +1389,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2158,7 +2196,7 @@
       <c r="AK14" s="19"/>
       <c r="AL14" s="19"/>
     </row>
-    <row r="15" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="115.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>33</v>
       </c>
@@ -2194,11 +2232,15 @@
       </c>
       <c r="AH15" s="19"/>
       <c r="AI15" s="19"/>
-      <c r="AJ15" s="43" t="s">
-        <v>247</v>
-      </c>
-      <c r="AK15" s="19"/>
-      <c r="AL15" s="19"/>
+      <c r="AJ15" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK15" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="AL15" s="63" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="16" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
@@ -2906,7 +2948,7 @@
       <c r="AK34" s="19"/>
       <c r="AL34" s="19"/>
     </row>
-    <row r="35" spans="1:38" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>177</v>
       </c>
@@ -2969,15 +3011,11 @@
       <c r="AI35" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="AJ35" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK35" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="AL35" s="19" t="s">
-        <v>232</v>
-      </c>
+      <c r="AJ35" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK35" s="19"/>
+      <c r="AL35" s="19"/>
     </row>
     <row r="36" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
@@ -3057,7 +3095,7 @@
       <c r="AK37" s="19"/>
       <c r="AL37" s="19"/>
     </row>
-    <row r="38" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>56</v>
       </c>
@@ -3080,7 +3118,9 @@
       <c r="AG38" s="19"/>
       <c r="AH38" s="19"/>
       <c r="AI38" s="19"/>
-      <c r="AJ38" s="19"/>
+      <c r="AJ38" s="47" t="s">
+        <v>270</v>
+      </c>
       <c r="AK38" s="19"/>
       <c r="AL38" s="19"/>
     </row>
@@ -3314,7 +3354,7 @@
     </row>
     <row r="45" spans="1:38" ht="72" x14ac:dyDescent="0.3">
       <c r="A45" s="50" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B45" s="16" t="s">
         <v>64</v>
@@ -3365,14 +3405,10 @@
         <v>263</v>
       </c>
       <c r="AJ45" s="44" t="s">
-        <v>262</v>
-      </c>
-      <c r="AK45" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="AL45" s="19" t="s">
-        <v>263</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="AK45" s="19"/>
+      <c r="AL45" s="64"/>
     </row>
     <row r="46" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
@@ -3430,12 +3466,10 @@
       <c r="AJ46" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="AK46" s="19" t="s">
-        <v>210</v>
-      </c>
+      <c r="AK46" s="19"/>
       <c r="AL46" s="19"/>
     </row>
-    <row r="47" spans="1:38" ht="43.2" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="19" t="s">
         <v>67</v>
       </c>
@@ -3491,9 +3525,7 @@
       <c r="AJ47" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="AK47" s="63" t="s">
-        <v>268</v>
-      </c>
+      <c r="AK47" s="19"/>
       <c r="AL47" s="19"/>
     </row>
     <row r="48" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3552,15 +3584,13 @@
         <v>186</v>
       </c>
       <c r="AI48" s="19"/>
-      <c r="AJ48" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK48" s="19" t="s">
+      <c r="AJ48" s="47" t="s">
         <v>186</v>
       </c>
+      <c r="AK48" s="19"/>
       <c r="AL48" s="19"/>
     </row>
-    <row r="49" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A49" s="32" t="s">
         <v>254</v>
       </c>
@@ -3577,10 +3607,12 @@
       </c>
       <c r="AH49" s="19"/>
       <c r="AI49" s="19"/>
-      <c r="AJ49" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK49" s="19"/>
+      <c r="AJ49" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK49" s="63" t="s">
+        <v>273</v>
+      </c>
       <c r="AL49" s="19"/>
     </row>
     <row r="50" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3603,10 +3635,12 @@
       </c>
       <c r="AH50" s="19"/>
       <c r="AI50" s="19"/>
-      <c r="AJ50" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK50" s="19"/>
+      <c r="AJ50" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK50" s="63" t="s">
+        <v>281</v>
+      </c>
       <c r="AL50" s="19"/>
     </row>
     <row r="51" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3629,13 +3663,13 @@
       </c>
       <c r="AH51" s="19"/>
       <c r="AI51" s="19"/>
-      <c r="AJ51" s="45" t="s">
-        <v>167</v>
+      <c r="AJ51" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AK51" s="19"/>
       <c r="AL51" s="19"/>
     </row>
-    <row r="52" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" ht="57.6" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
         <v>259</v>
       </c>
@@ -3655,13 +3689,15 @@
       </c>
       <c r="AH52" s="19"/>
       <c r="AI52" s="19"/>
-      <c r="AJ52" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK52" s="19"/>
+      <c r="AJ52" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK52" s="63" t="s">
+        <v>274</v>
+      </c>
       <c r="AL52" s="19"/>
     </row>
-    <row r="53" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
         <v>257</v>
       </c>
@@ -3681,11 +3717,13 @@
       </c>
       <c r="AH53" s="19"/>
       <c r="AI53" s="19"/>
-      <c r="AJ53" s="45" t="s">
-        <v>167</v>
+      <c r="AJ53" s="44" t="s">
+        <v>166</v>
       </c>
       <c r="AK53" s="19"/>
-      <c r="AL53" s="19"/>
+      <c r="AL53" s="63" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="54" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A54" s="32" t="s">
@@ -3707,13 +3745,13 @@
       </c>
       <c r="AH54" s="19"/>
       <c r="AI54" s="19"/>
-      <c r="AJ54" s="45" t="s">
-        <v>167</v>
+      <c r="AJ54" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AK54" s="19"/>
       <c r="AL54" s="19"/>
     </row>
-    <row r="55" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
         <v>258</v>
       </c>
@@ -3733,11 +3771,13 @@
       </c>
       <c r="AH55" s="19"/>
       <c r="AI55" s="19"/>
-      <c r="AJ55" s="45" t="s">
-        <v>167</v>
+      <c r="AJ55" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AK55" s="19"/>
-      <c r="AL55" s="19"/>
+      <c r="AL55" s="63" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="56" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A56" s="32" t="s">
@@ -3759,13 +3799,13 @@
       </c>
       <c r="AH56" s="19"/>
       <c r="AI56" s="19"/>
-      <c r="AJ56" s="46" t="s">
-        <v>168</v>
+      <c r="AJ56" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AK56" s="19"/>
       <c r="AL56" s="19"/>
     </row>
-    <row r="57" spans="1:38" ht="72" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:38" ht="115.2" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A57" s="33" t="s">
         <v>171</v>
       </c>
@@ -3822,7 +3862,7 @@
         <v>246</v>
       </c>
       <c r="AK57" s="55" t="s">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="AL57" s="19"/>
     </row>
@@ -4711,7 +4751,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="85" spans="1:38" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>88</v>
       </c>
@@ -4903,7 +4943,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="89" spans="1:38" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A89" s="30" t="s">
         <v>95</v>
       </c>
@@ -5351,7 +5391,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="98" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
         <v>109</v>
       </c>
@@ -5400,7 +5440,7 @@
         <v>249</v>
       </c>
       <c r="AJ98" s="43" t="s">
-        <v>245</v>
+        <v>165</v>
       </c>
       <c r="AK98" s="19"/>
       <c r="AL98" s="19" t="s">
@@ -5409,10 +5449,10 @@
     </row>
     <row r="99" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="6"/>
@@ -5429,16 +5469,18 @@
       <c r="AG99" s="43"/>
       <c r="AH99" s="19"/>
       <c r="AI99" s="19"/>
-      <c r="AJ99" s="43"/>
+      <c r="AJ99" s="47" t="s">
+        <v>282</v>
+      </c>
       <c r="AK99" s="19"/>
       <c r="AL99" s="19"/>
     </row>
-    <row r="100" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D100" s="13"/>
       <c r="E100" s="6"/>
@@ -5455,11 +5497,15 @@
       <c r="AG100" s="43"/>
       <c r="AH100" s="19"/>
       <c r="AI100" s="19"/>
-      <c r="AJ100" s="43"/>
-      <c r="AK100" s="19"/>
+      <c r="AJ100" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK100" s="63" t="s">
+        <v>283</v>
+      </c>
       <c r="AL100" s="19"/>
     </row>
-    <row r="101" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A101" s="50" t="s">
         <v>223</v>
       </c>
@@ -5711,7 +5757,7 @@
       <c r="AK109" s="19"/>
       <c r="AL109" s="19"/>
     </row>
-    <row r="110" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A110" s="50" t="s">
         <v>224</v>
       </c>

--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D819444C-89CB-4A16-988E-E7D216D3E791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6F4C3D-4935-4155-8F5F-E87AF0AF06E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="290">
   <si>
     <t>HITO</t>
   </si>
@@ -860,9 +860,6 @@
     <t>Confirmar que se muestra 3 en vez de 4 por falta de contenido</t>
   </si>
   <si>
-    <t>necesaria opción columna o row</t>
-  </si>
-  <si>
     <t>dropdown submenú https://getbootstrap.com/docs/4.0/components/dropdowns/</t>
   </si>
   <si>
@@ -888,6 +885,27 @@
   </si>
   <si>
     <t>Pendiente edición padre</t>
+  </si>
+  <si>
+    <t>Servicios</t>
+  </si>
+  <si>
+    <t>90% Condicionado</t>
+  </si>
+  <si>
+    <t>80% Finalizado</t>
+  </si>
+  <si>
+    <t>Fata filtros calendaio 2da fse</t>
+  </si>
+  <si>
+    <t>80% Finalizado (Pte. WPZ)</t>
+  </si>
+  <si>
+    <t>80% Finalizado (Pte.WPZ)</t>
+  </si>
+  <si>
+    <t>BKTT-Card (Consulta contenido extendidas)</t>
   </si>
 </sst>
 </file>
@@ -2236,10 +2254,10 @@
         <v>166</v>
       </c>
       <c r="AK15" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AL15" s="63" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3530,7 +3548,7 @@
     </row>
     <row r="48" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A48" s="33" t="s">
-        <v>68</v>
+        <v>289</v>
       </c>
       <c r="D48" s="33" t="s">
         <v>68</v>
@@ -3608,7 +3626,7 @@
       <c r="AH49" s="19"/>
       <c r="AI49" s="19"/>
       <c r="AJ49" s="43" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AK49" s="63" t="s">
         <v>273</v>
@@ -3636,10 +3654,10 @@
       <c r="AH50" s="19"/>
       <c r="AI50" s="19"/>
       <c r="AJ50" s="43" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AK50" s="63" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AL50" s="19"/>
     </row>
@@ -3664,12 +3682,12 @@
       <c r="AH51" s="19"/>
       <c r="AI51" s="19"/>
       <c r="AJ51" s="43" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AK51" s="19"/>
       <c r="AL51" s="19"/>
     </row>
-    <row r="52" spans="1:38" ht="57.6" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
         <v>259</v>
       </c>
@@ -3689,12 +3707,10 @@
       </c>
       <c r="AH52" s="19"/>
       <c r="AI52" s="19"/>
-      <c r="AJ52" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK52" s="63" t="s">
-        <v>274</v>
-      </c>
+      <c r="AJ52" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AK52" s="19"/>
       <c r="AL52" s="19"/>
     </row>
     <row r="53" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3722,7 +3738,7 @@
       </c>
       <c r="AK53" s="19"/>
       <c r="AL53" s="63" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3746,7 +3762,7 @@
       <c r="AH54" s="19"/>
       <c r="AI54" s="19"/>
       <c r="AJ54" s="43" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AK54" s="19"/>
       <c r="AL54" s="19"/>
@@ -3772,11 +3788,11 @@
       <c r="AH55" s="19"/>
       <c r="AI55" s="19"/>
       <c r="AJ55" s="43" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AK55" s="19"/>
       <c r="AL55" s="63" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="56" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
@@ -3800,7 +3816,7 @@
       <c r="AH56" s="19"/>
       <c r="AI56" s="19"/>
       <c r="AJ56" s="43" t="s">
-        <v>165</v>
+        <v>285</v>
       </c>
       <c r="AK56" s="19"/>
       <c r="AL56" s="19"/>
@@ -3858,8 +3874,8 @@
         <v>241</v>
       </c>
       <c r="AI57" s="19"/>
-      <c r="AJ57" s="45" t="s">
-        <v>246</v>
+      <c r="AJ57" s="43" t="s">
+        <v>285</v>
       </c>
       <c r="AK57" s="55" t="s">
         <v>271</v>
@@ -3905,7 +3921,7 @@
       <c r="AK58" s="19"/>
       <c r="AL58" s="19"/>
     </row>
-    <row r="59" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
         <v>254</v>
       </c>
@@ -3929,13 +3945,15 @@
       </c>
       <c r="AH59" s="19"/>
       <c r="AI59" s="19"/>
-      <c r="AJ59" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK59" s="19"/>
+      <c r="AJ59" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="AK59" s="63" t="s">
+        <v>286</v>
+      </c>
       <c r="AL59" s="19"/>
     </row>
-    <row r="60" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
         <v>255</v>
       </c>
@@ -3958,13 +3976,13 @@
       </c>
       <c r="AH60" s="19"/>
       <c r="AI60" s="19"/>
-      <c r="AJ60" s="45" t="s">
-        <v>167</v>
+      <c r="AJ60" s="43" t="s">
+        <v>287</v>
       </c>
       <c r="AK60" s="19"/>
       <c r="AL60" s="19"/>
     </row>
-    <row r="61" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
         <v>256</v>
       </c>
@@ -3987,8 +4005,8 @@
       </c>
       <c r="AH61" s="19"/>
       <c r="AI61" s="19"/>
-      <c r="AJ61" s="45" t="s">
-        <v>167</v>
+      <c r="AJ61" s="43" t="s">
+        <v>288</v>
       </c>
       <c r="AK61" s="19"/>
       <c r="AL61" s="19"/>
@@ -4014,7 +4032,9 @@
       <c r="AG62" s="19"/>
       <c r="AH62" s="19"/>
       <c r="AI62" s="19"/>
-      <c r="AJ62" s="19"/>
+      <c r="AJ62" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AK62" s="19"/>
       <c r="AL62" s="19"/>
     </row>
@@ -5090,14 +5110,16 @@
         <v>227</v>
       </c>
       <c r="AJ91" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK91" s="19"/>
+        <v>284</v>
+      </c>
+      <c r="AK91" s="63" t="s">
+        <v>283</v>
+      </c>
       <c r="AL91" s="19" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="92" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A92" s="30" t="s">
         <v>244</v>
       </c>
@@ -5449,7 +5471,7 @@
     </row>
     <row r="99" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C99" s="16" t="s">
         <v>268</v>
@@ -5470,14 +5492,14 @@
       <c r="AH99" s="19"/>
       <c r="AI99" s="19"/>
       <c r="AJ99" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AK99" s="19"/>
       <c r="AL99" s="19"/>
     </row>
     <row r="100" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A100" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C100" s="16" t="s">
         <v>269</v>
@@ -5501,7 +5523,7 @@
         <v>166</v>
       </c>
       <c r="AK100" s="63" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AL100" s="19"/>
     </row>
@@ -5936,50 +5958,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
-    <Area xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">7</Area>
-    <Acciones xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <sys xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <Sociedad xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <fechadeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">2022-07-13T22:00:00+00:00</fechadeproyecto>
-    <OfertaAnterior xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Oferta xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <Value>5919</Value>
-    </Oferta>
-    <responsableproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <UserInfo>
-        <DisplayName>Aitor Roncero Val</DisplayName>
-        <AccountId>927</AccountId>
-        <AccountType/>
-      </UserInfo>
-    </responsableproyecto>
-    <Oficina xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">1</Oficina>
-    <codigodeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">Maquetación de páginas web dentro del proyecto Biscaytik</codigodeproyecto>
-    <fechafinestimado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <TaxCatchAll xmlns="06fec347-a373-485e-bb4f-f611040a1dd3" xsi:nil="true"/>
-    <Cliente xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">209</Cliente>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <fechafinreal xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-    <Oferta_x0020_Antigua xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010021AB849DB9524648A8F6CDAE5A42EE85" ma:contentTypeVersion="54" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf342e325584cfc73779b32cd8516cb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xmlns:ns3="06fec347-a373-485e-bb4f-f611040a1dd3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="97bec9e280156beb57af844d85b9963b" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6379,7 +6357,71 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
+    <Area xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">7</Area>
+    <Acciones xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <sys xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <Sociedad xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <fechadeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">2022-07-13T22:00:00+00:00</fechadeproyecto>
+    <OfertaAnterior xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <DocumentSetDescription xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Oferta xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <Value>5919</Value>
+    </Oferta>
+    <responsableproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <UserInfo>
+        <DisplayName>Aitor Roncero Val</DisplayName>
+        <AccountId>927</AccountId>
+        <AccountType/>
+      </UserInfo>
+    </responsableproyecto>
+    <Oficina xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">1</Oficina>
+    <codigodeproyecto xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">Maquetación de páginas web dentro del proyecto Biscaytik</codigodeproyecto>
+    <fechafinestimado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <TaxCatchAll xmlns="06fec347-a373-485e-bb4f-f611040a1dd3" xsi:nil="true"/>
+    <Cliente xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">209</Cliente>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <fechafinreal xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+    <Oferta_x0020_Antigua xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B271E1E9-4B5A-43C8-93E9-EF9A1A456C27}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb"/>
+    <ds:schemaRef ds:uri="06fec347-a373-485e-bb4f-f611040a1dd3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -6397,30 +6439,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B271E1E9-4B5A-43C8-93E9-EF9A1A456C27}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb"/>
-    <ds:schemaRef ds:uri="06fec347-a373-485e-bb4f-f611040a1dd3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6F4C3D-4935-4155-8F5F-E87AF0AF06E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A843D364-F585-4F12-893A-83B4F61437D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="306">
   <si>
     <t>HITO</t>
   </si>
@@ -906,6 +906,54 @@
   </si>
   <si>
     <t>BKTT-Card (Consulta contenido extendidas)</t>
+  </si>
+  <si>
+    <t>Imágenes servicios (restaurante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO  (22-09 parta teknei) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO  (29-09 parta teknei) </t>
+  </si>
+  <si>
+    <t>bares</t>
+  </si>
+  <si>
+    <t>alojamientos</t>
+  </si>
+  <si>
+    <t>eventos</t>
+  </si>
+  <si>
+    <t>noticias</t>
+  </si>
+  <si>
+    <t>playa</t>
+  </si>
+  <si>
+    <t>ruta</t>
+  </si>
+  <si>
+    <t>Imágenes tipo alojamiento</t>
+  </si>
+  <si>
+    <t>decontenido</t>
+  </si>
+  <si>
+    <t>patrimonio</t>
+  </si>
+  <si>
+    <t>rutas</t>
+  </si>
+  <si>
+    <t>eroror trasladado teams</t>
+  </si>
+  <si>
+    <t>Subida, parece que no coje última versión, desde que cambió nombres?</t>
+  </si>
+  <si>
+    <t>Propuesta* DETALLE EVENTO (Base) layout</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1769,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AL126"/>
+  <dimension ref="A1:AO143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="49" customWidth="1"/>
@@ -1748,191 +1796,223 @@
     <col min="32" max="32" width="12.88671875" style="19" customWidth="1"/>
     <col min="33" max="33" width="18.44140625" customWidth="1"/>
     <col min="36" max="36" width="18.109375" customWidth="1"/>
+    <col min="39" max="39" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="22.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:38" ht="216" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="1" spans="1:41" ht="216" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3" t="s">
+      <c r="K1" s="3"/>
+      <c r="L1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="35" t="s">
+      <c r="N1" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="O2" s="35" t="s">
+      <c r="O1" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="P2" s="35" t="s">
+      <c r="P1" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="Q2" s="35" t="s">
+      <c r="Q1" s="35" t="s">
         <v>140</v>
       </c>
-      <c r="R2" s="35" t="s">
+      <c r="R1" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="S2" s="35" t="s">
+      <c r="S1" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="T2" s="35" t="s">
+      <c r="T1" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="U2" s="35" t="s">
+      <c r="U1" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="V2" s="35" t="s">
+      <c r="V1" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="W2" s="35" t="s">
+      <c r="W1" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="X1" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="Y2" s="35" t="s">
+      <c r="Y1" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="Z2" s="35" t="s">
+      <c r="Z1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AA2" s="35" t="s">
+      <c r="AA1" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="AB2" s="35" t="s">
+      <c r="AB1" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="AC2" s="35" t="s">
+      <c r="AC1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AD2" s="35" t="s">
+      <c r="AD1" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="AE2" s="35" t="s">
+      <c r="AE1" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="AF2" s="35" t="s">
+      <c r="AF1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AG2" s="35" t="s">
+      <c r="AG1" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="AH2" s="35" t="s">
+      <c r="AH1" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="AI2" s="35" t="s">
+      <c r="AI1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AJ2" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="AK2" s="35" t="s">
+      <c r="AJ1" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="AK1" s="35" t="s">
         <v>180</v>
       </c>
-      <c r="AL2" s="35" t="s">
+      <c r="AL1" s="35" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="3" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="50">
+      <c r="AM1" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="AN1" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="AO1" s="35" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="50">
         <v>0</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B2" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="L3">
+      <c r="L2">
         <v>40</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M2" s="28">
         <v>69</v>
       </c>
-      <c r="N3">
+      <c r="N2">
         <v>60</v>
       </c>
-      <c r="O3">
+      <c r="O2">
         <v>70</v>
       </c>
-      <c r="V3">
+      <c r="V2">
         <v>90</v>
       </c>
-      <c r="W3">
+      <c r="W2">
         <v>80</v>
       </c>
-      <c r="X3" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA3" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD3" s="56" t="s">
-        <v>165</v>
-      </c>
+      <c r="X2" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA2" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD2" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE2" s="33"/>
+      <c r="AF2" s="33"/>
+      <c r="AG2" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH2" s="19"/>
+      <c r="AI2" s="19"/>
+      <c r="AJ2" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK2" s="19"/>
+      <c r="AL2" s="19"/>
+      <c r="AM2" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+    </row>
+    <row r="3" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D3" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="M3" s="26"/>
+      <c r="AD3" s="33"/>
       <c r="AE3" s="33"/>
       <c r="AF3" s="33"/>
-      <c r="AG3" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AG3" s="19"/>
       <c r="AH3" s="19"/>
       <c r="AI3" s="19"/>
-      <c r="AJ3" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AJ3" s="19"/>
       <c r="AK3" s="19"/>
       <c r="AL3" s="19"/>
-    </row>
-    <row r="4" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="5"/>
+      <c r="AM3" s="19"/>
+      <c r="AN3" s="19"/>
+      <c r="AO3" s="19"/>
+    </row>
+    <row r="4" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D4" s="19" t="s">
+        <v>16</v>
+      </c>
       <c r="M4" s="26"/>
       <c r="AD4" s="33"/>
       <c r="AE4" s="33"/>
@@ -1943,11 +2023,28 @@
       <c r="AJ4" s="19"/>
       <c r="AK4" s="19"/>
       <c r="AL4" s="19"/>
-    </row>
-    <row r="5" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="19" t="s">
-        <v>16</v>
-      </c>
+      <c r="AM4" s="19"/>
+      <c r="AN4" s="19"/>
+      <c r="AO4" s="19"/>
+    </row>
+    <row r="5" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D5" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="5"/>
       <c r="M5" s="26"/>
       <c r="AD5" s="33"/>
       <c r="AE5" s="33"/>
@@ -1958,25 +2055,14 @@
       <c r="AJ5" s="19"/>
       <c r="AK5" s="19"/>
       <c r="AL5" s="19"/>
-    </row>
-    <row r="6" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D6" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="5"/>
+      <c r="AM5" s="19"/>
+      <c r="AN5" s="19"/>
+      <c r="AO5" s="19"/>
+    </row>
+    <row r="6" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="19" t="s">
+        <v>20</v>
+      </c>
       <c r="M6" s="26"/>
       <c r="AD6" s="33"/>
       <c r="AE6" s="33"/>
@@ -1987,11 +2073,28 @@
       <c r="AJ6" s="19"/>
       <c r="AK6" s="19"/>
       <c r="AL6" s="19"/>
-    </row>
-    <row r="7" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D7" s="19" t="s">
-        <v>20</v>
-      </c>
+      <c r="AM6" s="19"/>
+      <c r="AN6" s="19"/>
+      <c r="AO6" s="19"/>
+    </row>
+    <row r="7" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D7" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="5"/>
+      <c r="H7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" s="5"/>
       <c r="M7" s="26"/>
       <c r="AD7" s="33"/>
       <c r="AE7" s="33"/>
@@ -2002,25 +2105,14 @@
       <c r="AJ7" s="19"/>
       <c r="AK7" s="19"/>
       <c r="AL7" s="19"/>
-    </row>
-    <row r="8" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="5"/>
+      <c r="AM7" s="19"/>
+      <c r="AN7" s="19"/>
+      <c r="AO7" s="19"/>
+    </row>
+    <row r="8" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="19" t="s">
+        <v>22</v>
+      </c>
       <c r="M8" s="26"/>
       <c r="AD8" s="33"/>
       <c r="AE8" s="33"/>
@@ -2031,12 +2123,44 @@
       <c r="AJ8" s="19"/>
       <c r="AK8" s="19"/>
       <c r="AL8" s="19"/>
-    </row>
-    <row r="9" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="26"/>
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+    </row>
+    <row r="9" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="50">
+        <v>1</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>40</v>
+      </c>
+      <c r="M9" s="28">
+        <v>94</v>
+      </c>
+      <c r="N9">
+        <v>60</v>
+      </c>
+      <c r="O9">
+        <v>70</v>
+      </c>
+      <c r="Q9" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="U9">
+        <v>80</v>
+      </c>
+      <c r="V9">
+        <v>95</v>
+      </c>
+      <c r="W9">
+        <v>95</v>
+      </c>
       <c r="AD9" s="33"/>
       <c r="AE9" s="33"/>
       <c r="AF9" s="33"/>
@@ -2046,108 +2170,99 @@
       <c r="AJ9" s="19"/>
       <c r="AK9" s="19"/>
       <c r="AL9" s="19"/>
-    </row>
-    <row r="10" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="50">
-        <v>1</v>
-      </c>
-      <c r="B10" s="16" t="s">
-        <v>23</v>
+      <c r="AM9" s="19"/>
+      <c r="AN9" s="19"/>
+      <c r="AO9" s="19"/>
+    </row>
+    <row r="10" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10">
-        <v>40</v>
-      </c>
-      <c r="M10" s="28">
-        <v>94</v>
-      </c>
-      <c r="N10">
-        <v>60</v>
-      </c>
-      <c r="O10">
-        <v>70</v>
-      </c>
-      <c r="Q10" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="U10">
-        <v>80</v>
-      </c>
-      <c r="V10">
-        <v>95</v>
-      </c>
-      <c r="W10">
-        <v>95</v>
-      </c>
-      <c r="AD10" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M10" s="26"/>
+      <c r="X10" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA10" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD10" s="56" t="s">
+        <v>165</v>
+      </c>
       <c r="AE10" s="33"/>
       <c r="AF10" s="33"/>
-      <c r="AG10" s="19"/>
+      <c r="AG10" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AH10" s="19"/>
       <c r="AI10" s="19"/>
-      <c r="AJ10" s="19"/>
+      <c r="AJ10" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AK10" s="19"/>
       <c r="AL10" s="19"/>
-    </row>
-    <row r="11" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="AM10" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN10" s="19"/>
+      <c r="AO10" s="19"/>
+    </row>
+    <row r="11" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
       <c r="M11" s="26"/>
-      <c r="X11" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA11" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD11" s="56" t="s">
-        <v>165</v>
-      </c>
+      <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AF11" s="33"/>
-      <c r="AG11" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AG11" s="19"/>
       <c r="AH11" s="19"/>
       <c r="AI11" s="19"/>
-      <c r="AJ11" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AJ11" s="19"/>
       <c r="AK11" s="19"/>
       <c r="AL11" s="19"/>
-    </row>
-    <row r="12" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM11" s="19"/>
+      <c r="AN11" s="19"/>
+      <c r="AO11" s="19"/>
+    </row>
+    <row r="12" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -2165,13 +2280,16 @@
       <c r="AJ12" s="19"/>
       <c r="AK12" s="19"/>
       <c r="AL12" s="19"/>
-    </row>
-    <row r="13" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM12" s="19"/>
+      <c r="AN12" s="19"/>
+      <c r="AO12" s="19"/>
+    </row>
+    <row r="13" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -2189,13 +2307,16 @@
       <c r="AJ13" s="19"/>
       <c r="AK13" s="19"/>
       <c r="AL13" s="19"/>
-    </row>
-    <row r="14" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM13" s="19"/>
+      <c r="AN13" s="19"/>
+      <c r="AO13" s="19"/>
+    </row>
+    <row r="14" spans="1:41" ht="115.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -2204,22 +2325,53 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="M14" s="26"/>
-      <c r="AD14" s="33"/>
+      <c r="X14" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y14" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA14" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB14" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="AD14" s="56" t="s">
+        <v>251</v>
+      </c>
       <c r="AE14" s="33"/>
       <c r="AF14" s="33"/>
-      <c r="AG14" s="19"/>
+      <c r="AG14" s="43" t="s">
+        <v>247</v>
+      </c>
       <c r="AH14" s="19"/>
       <c r="AI14" s="19"/>
-      <c r="AJ14" s="19"/>
-      <c r="AK14" s="19"/>
-      <c r="AL14" s="19"/>
-    </row>
-    <row r="15" spans="1:38" ht="115.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AJ14" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK14" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="AL14" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="AM14" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN14" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="AO14" s="63" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="15" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -2228,119 +2380,110 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="M15" s="26"/>
-      <c r="X15" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y15" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA15" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB15" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="AD15" s="56" t="s">
-        <v>251</v>
-      </c>
+      <c r="AD15" s="33"/>
       <c r="AE15" s="33"/>
       <c r="AF15" s="33"/>
-      <c r="AG15" s="43" t="s">
-        <v>247</v>
-      </c>
+      <c r="AG15" s="19"/>
       <c r="AH15" s="19"/>
       <c r="AI15" s="19"/>
-      <c r="AJ15" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK15" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="AL15" s="63" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
+      <c r="AJ15" s="19"/>
+      <c r="AK15" s="19"/>
+      <c r="AL15" s="19"/>
+      <c r="AM15" s="19"/>
+      <c r="AN15" s="19"/>
+      <c r="AO15" s="19"/>
+    </row>
+    <row r="16" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="H16" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J16" s="6"/>
       <c r="M16" s="26"/>
-      <c r="AD16" s="33"/>
+      <c r="X16" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y16" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA16" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD16" s="56" t="s">
+        <v>165</v>
+      </c>
       <c r="AE16" s="33"/>
       <c r="AF16" s="33"/>
-      <c r="AG16" s="19"/>
+      <c r="AG16" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AH16" s="19"/>
-      <c r="AI16" s="19"/>
-      <c r="AJ16" s="19"/>
+      <c r="AI16" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ16" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AK16" s="19"/>
-      <c r="AL16" s="19"/>
-    </row>
-    <row r="17" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL16" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM16" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN16" s="19"/>
+      <c r="AO16" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
       <c r="J17" s="6"/>
       <c r="M17" s="26"/>
-      <c r="X17" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y17" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA17" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="AD17" s="56" t="s">
-        <v>165</v>
-      </c>
+      <c r="AD17" s="33"/>
       <c r="AE17" s="33"/>
       <c r="AF17" s="33"/>
-      <c r="AG17" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AG17" s="19"/>
       <c r="AH17" s="19"/>
-      <c r="AI17" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ17" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AI17" s="19"/>
+      <c r="AJ17" s="19"/>
       <c r="AK17" s="19"/>
-      <c r="AL17" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AL17" s="19"/>
+      <c r="AM17" s="19"/>
+      <c r="AN17" s="19"/>
+      <c r="AO17" s="19"/>
+    </row>
+    <row r="18" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
@@ -2358,13 +2501,16 @@
       <c r="AJ18" s="19"/>
       <c r="AK18" s="19"/>
       <c r="AL18" s="19"/>
-    </row>
-    <row r="19" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM18" s="19"/>
+      <c r="AN18" s="19"/>
+      <c r="AO18" s="19"/>
+    </row>
+    <row r="19" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -2373,6 +2519,12 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="M19" s="26"/>
+      <c r="S19" t="s">
+        <v>149</v>
+      </c>
+      <c r="U19" s="36" t="s">
+        <v>159</v>
+      </c>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
       <c r="AF19" s="33"/>
@@ -2382,188 +2534,240 @@
       <c r="AJ19" s="19"/>
       <c r="AK19" s="19"/>
       <c r="AL19" s="19"/>
-    </row>
-    <row r="20" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
+      <c r="AM19" s="19"/>
+      <c r="AN19" s="19"/>
+      <c r="AO19" s="19"/>
+    </row>
+    <row r="20" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
+      <c r="H20" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J20" s="6"/>
       <c r="M20" s="26"/>
-      <c r="S20" t="s">
-        <v>149</v>
-      </c>
-      <c r="U20" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="AD20" s="33"/>
-      <c r="AE20" s="33"/>
+      <c r="V20">
+        <v>95</v>
+      </c>
+      <c r="W20">
+        <v>95</v>
+      </c>
+      <c r="X20" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA20" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB20" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AD20" s="56" t="s">
+        <v>165</v>
+      </c>
+      <c r="AE20" s="33" t="s">
+        <v>206</v>
+      </c>
       <c r="AF20" s="33"/>
-      <c r="AG20" s="19"/>
-      <c r="AH20" s="19"/>
-      <c r="AI20" s="19"/>
-      <c r="AJ20" s="19"/>
-      <c r="AK20" s="19"/>
-      <c r="AL20" s="19"/>
-    </row>
-    <row r="21" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="AG20" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH20" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AI20" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ20" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK20" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AL20" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM20" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN20" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="AO20" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="M21" s="26"/>
-      <c r="V21">
-        <v>95</v>
-      </c>
-      <c r="W21">
-        <v>95</v>
-      </c>
-      <c r="X21" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA21" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB21" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="AD21" s="56" t="s">
-        <v>165</v>
-      </c>
-      <c r="AE21" s="33" t="s">
-        <v>206</v>
-      </c>
+      <c r="AD21" s="33"/>
+      <c r="AE21" s="33"/>
       <c r="AF21" s="33"/>
-      <c r="AG21" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AH21" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="AI21" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ21" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK21" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL21" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="22" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="AG21" s="19"/>
+      <c r="AH21" s="19"/>
+      <c r="AI21" s="19"/>
+      <c r="AJ21" s="19"/>
+      <c r="AK21" s="19"/>
+      <c r="AL21" s="19"/>
+      <c r="AM21" s="19"/>
+      <c r="AN21" s="19"/>
+      <c r="AO21" s="19"/>
+    </row>
+    <row r="22" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="H22" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J22" s="6"/>
       <c r="M22" s="26"/>
-      <c r="AD22" s="33"/>
+      <c r="W22">
+        <v>60</v>
+      </c>
+      <c r="X22" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA22" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="AD22" s="57" t="s">
+        <v>205</v>
+      </c>
       <c r="AE22" s="33"/>
       <c r="AF22" s="33"/>
-      <c r="AG22" s="19"/>
-      <c r="AH22" s="19"/>
+      <c r="AG22" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH22" s="19" t="s">
+        <v>248</v>
+      </c>
       <c r="AI22" s="19"/>
-      <c r="AJ22" s="19"/>
-      <c r="AK22" s="19"/>
+      <c r="AJ22" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK22" s="19" t="s">
+        <v>248</v>
+      </c>
       <c r="AL22" s="19"/>
-    </row>
-    <row r="23" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="6"/>
+      <c r="AM22" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN22" s="19" t="s">
+        <v>248</v>
+      </c>
+      <c r="AO22" s="19"/>
+    </row>
+    <row r="23" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>42</v>
+      </c>
       <c r="M23" s="26"/>
-      <c r="W23">
-        <v>60</v>
-      </c>
-      <c r="X23" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA23" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="AD23" s="57" t="s">
-        <v>205</v>
-      </c>
+      <c r="S23" t="s">
+        <v>155</v>
+      </c>
+      <c r="U23" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="AD23" s="33"/>
       <c r="AE23" s="33"/>
       <c r="AF23" s="33"/>
-      <c r="AG23" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AH23" s="19" t="s">
-        <v>248</v>
-      </c>
+      <c r="AG23" s="19"/>
+      <c r="AH23" s="19"/>
       <c r="AI23" s="19"/>
-      <c r="AJ23" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK23" s="19" t="s">
-        <v>248</v>
-      </c>
+      <c r="AJ23" s="19"/>
+      <c r="AK23" s="19"/>
       <c r="AL23" s="19"/>
-    </row>
-    <row r="24" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>42</v>
+      <c r="AM23" s="19"/>
+      <c r="AN23" s="19"/>
+      <c r="AO23" s="19"/>
+    </row>
+    <row r="24" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24">
+        <v>40</v>
       </c>
       <c r="M24" s="26"/>
-      <c r="S24" t="s">
-        <v>155</v>
-      </c>
-      <c r="U24" s="36" t="s">
-        <v>156</v>
+      <c r="N24">
+        <v>60</v>
+      </c>
+      <c r="O24">
+        <v>70</v>
+      </c>
+      <c r="Q24" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="S24">
+        <v>80</v>
+      </c>
+      <c r="U24">
+        <v>70</v>
+      </c>
+      <c r="V24" s="36" t="s">
+        <v>162</v>
+      </c>
+      <c r="W24">
+        <v>75</v>
       </c>
       <c r="AD24" s="33"/>
       <c r="AE24" s="33"/>
@@ -2574,156 +2778,165 @@
       <c r="AJ24" s="19"/>
       <c r="AK24" s="19"/>
       <c r="AL24" s="19"/>
-    </row>
-    <row r="25" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I25" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25">
-        <v>40</v>
-      </c>
+      <c r="AM24" s="19"/>
+      <c r="AN24" s="19"/>
+      <c r="AO24" s="19"/>
+    </row>
+    <row r="25" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="9"/>
       <c r="M25" s="26"/>
-      <c r="N25">
-        <v>60</v>
-      </c>
-      <c r="O25">
-        <v>70</v>
-      </c>
-      <c r="Q25" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="S25">
-        <v>80</v>
-      </c>
-      <c r="U25">
-        <v>70</v>
-      </c>
-      <c r="V25" s="36" t="s">
-        <v>162</v>
-      </c>
-      <c r="W25">
-        <v>75</v>
-      </c>
-      <c r="AD25" s="33"/>
+      <c r="X25" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA25" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD25" s="56" t="s">
+        <v>165</v>
+      </c>
       <c r="AE25" s="33"/>
       <c r="AF25" s="33"/>
-      <c r="AG25" s="19"/>
+      <c r="AG25" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AH25" s="19"/>
-      <c r="AI25" s="19"/>
-      <c r="AJ25" s="19"/>
+      <c r="AI25" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ25" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AK25" s="19"/>
-      <c r="AL25" s="19"/>
-    </row>
-    <row r="26" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="9"/>
+      <c r="AL25" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM25" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN25" s="19"/>
+      <c r="AO25" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="M26" s="26"/>
-      <c r="X26" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA26" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD26" s="56" t="s">
-        <v>165</v>
-      </c>
+      <c r="S26" t="s">
+        <v>149</v>
+      </c>
+      <c r="U26" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="W26" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="X26" s="19"/>
+      <c r="AD26" s="33"/>
       <c r="AE26" s="33"/>
       <c r="AF26" s="33"/>
-      <c r="AG26" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AG26" s="19"/>
       <c r="AH26" s="19"/>
-      <c r="AI26" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ26" s="43" t="s">
-        <v>165</v>
-      </c>
+      <c r="AI26" s="19"/>
+      <c r="AJ26" s="19"/>
       <c r="AK26" s="19"/>
-      <c r="AL26" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="27" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="AL26" s="19"/>
+      <c r="AM26" s="19"/>
+      <c r="AN26" s="19"/>
+      <c r="AO26" s="19"/>
+    </row>
+    <row r="27" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="9"/>
       <c r="M27" s="26"/>
-      <c r="S27" t="s">
-        <v>149</v>
-      </c>
-      <c r="U27" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="W27" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="X27" s="19"/>
-      <c r="AD27" s="33"/>
+      <c r="X27" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA27" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD27" s="56" t="s">
+        <v>165</v>
+      </c>
       <c r="AE27" s="33"/>
       <c r="AF27" s="33"/>
-      <c r="AG27" s="19"/>
+      <c r="AG27" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AH27" s="19"/>
-      <c r="AI27" s="19"/>
-      <c r="AJ27" s="19"/>
+      <c r="AI27" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AJ27" s="43" t="s">
+        <v>165</v>
+      </c>
       <c r="AK27" s="19"/>
-      <c r="AL27" s="19"/>
-    </row>
-    <row r="28" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="9"/>
+      <c r="AL27" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="AM27" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN27" s="19"/>
+      <c r="AO27" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I28" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="M28" s="26"/>
-      <c r="X28" s="42" t="s">
-        <v>174</v>
+      <c r="X28" s="39" t="s">
+        <v>165</v>
       </c>
       <c r="AA28" s="43" t="s">
         <v>165</v>
@@ -2747,13 +2960,20 @@
       <c r="AL28" s="19" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="29" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM28" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN28" s="19"/>
+      <c r="AO28" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D29" s="30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>18</v>
@@ -2768,14 +2988,29 @@
         <v>15</v>
       </c>
       <c r="M29" s="26"/>
-      <c r="X29" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA29" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD29" s="56" t="s">
-        <v>165</v>
+      <c r="S29" t="s">
+        <v>149</v>
+      </c>
+      <c r="U29" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="W29" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="X29" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y29" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA29" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AB29" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="AD29" s="58" t="s">
+        <v>252</v>
       </c>
       <c r="AE29" s="33"/>
       <c r="AF29" s="33"/>
@@ -2793,116 +3028,95 @@
       <c r="AL29" s="19" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="30" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="AM29" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN29" s="19"/>
+      <c r="AO29" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="30" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="9"/>
       <c r="M30" s="26"/>
-      <c r="S30" t="s">
-        <v>149</v>
-      </c>
-      <c r="U30" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="W30" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="X30" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y30" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA30" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AB30" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD30" s="58" t="s">
-        <v>252</v>
+      <c r="X30" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA30" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AD30" s="59" t="s">
+        <v>165</v>
       </c>
       <c r="AE30" s="33"/>
       <c r="AF30" s="33"/>
-      <c r="AG30" s="43" t="s">
+      <c r="AG30" s="39" t="s">
         <v>165</v>
       </c>
       <c r="AH30" s="19"/>
       <c r="AI30" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="AJ30" s="43" t="s">
+      <c r="AJ30" s="39" t="s">
         <v>165</v>
       </c>
       <c r="AK30" s="19"/>
       <c r="AL30" s="19" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="31" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="9"/>
+      <c r="AM30" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN30" s="19"/>
+      <c r="AO30" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>49</v>
+      </c>
       <c r="M31" s="26"/>
-      <c r="X31" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA31" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AD31" s="59" t="s">
-        <v>165</v>
-      </c>
+      <c r="W31">
+        <v>70</v>
+      </c>
+      <c r="AD31" s="33"/>
       <c r="AE31" s="33"/>
       <c r="AF31" s="33"/>
-      <c r="AG31" s="39" t="s">
-        <v>165</v>
-      </c>
+      <c r="AG31" s="19"/>
       <c r="AH31" s="19"/>
-      <c r="AI31" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ31" s="39" t="s">
-        <v>165</v>
-      </c>
+      <c r="AI31" s="19"/>
+      <c r="AJ31" s="19"/>
       <c r="AK31" s="19"/>
-      <c r="AL31" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="32" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="M32" s="26"/>
-      <c r="W32">
-        <v>70</v>
+      <c r="AL31" s="19"/>
+      <c r="AM31" s="19"/>
+      <c r="AN31" s="19"/>
+      <c r="AO31" s="19"/>
+    </row>
+    <row r="32" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="50">
+        <v>2</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="M32" s="28">
+        <v>94</v>
       </c>
       <c r="AD32" s="33"/>
       <c r="AE32" s="33"/>
@@ -2913,19 +3127,28 @@
       <c r="AJ32" s="19"/>
       <c r="AK32" s="19"/>
       <c r="AL32" s="19"/>
-    </row>
-    <row r="33" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="50">
-        <v>2</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="M33" s="28">
-        <v>94</v>
+      <c r="AM32" s="19"/>
+      <c r="AN32" s="19"/>
+      <c r="AO32" s="19"/>
+    </row>
+    <row r="33" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="6"/>
+      <c r="M33" s="26"/>
+      <c r="Q33" s="36" t="s">
+        <v>144</v>
       </c>
       <c r="AD33" s="33"/>
       <c r="AE33" s="33"/>
@@ -2936,111 +3159,138 @@
       <c r="AJ33" s="19"/>
       <c r="AK33" s="19"/>
       <c r="AL33" s="19"/>
-    </row>
-    <row r="34" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D34" s="30" t="s">
-        <v>52</v>
+      <c r="AM33" s="19"/>
+      <c r="AN33" s="19"/>
+      <c r="AO33" s="19"/>
+    </row>
+    <row r="34" spans="1:41" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>177</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="9"/>
+      <c r="H34" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J34" s="6"/>
       <c r="M34" s="26"/>
       <c r="Q34" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="AD34" s="33"/>
-      <c r="AE34" s="33"/>
-      <c r="AF34" s="33"/>
-      <c r="AG34" s="19"/>
+      <c r="S34" t="s">
+        <v>149</v>
+      </c>
+      <c r="U34" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="X34" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y34" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z34" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA34" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AD34" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE34" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF34" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="AG34" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AH34" s="19"/>
-      <c r="AI34" s="19"/>
-      <c r="AJ34" s="19"/>
+      <c r="AI34" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AJ34" s="39" t="s">
+        <v>165</v>
+      </c>
       <c r="AK34" s="19"/>
       <c r="AL34" s="19"/>
-    </row>
-    <row r="35" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM34" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN34" s="19"/>
+      <c r="AO34" s="19"/>
+    </row>
+    <row r="35" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
-        <v>177</v>
+        <v>54</v>
       </c>
       <c r="D35" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E35" s="6"/>
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H35" s="11"/>
+      <c r="I35" s="9"/>
       <c r="J35" s="6"/>
       <c r="M35" s="26"/>
-      <c r="Q35" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="S35" t="s">
-        <v>149</v>
-      </c>
-      <c r="U35" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="X35" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y35" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z35" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA35" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB35" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="AC35" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="AD35" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE35" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="AF35" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="AG35" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="N35">
+        <v>5</v>
+      </c>
+      <c r="O35">
+        <v>10</v>
+      </c>
+      <c r="P35">
+        <v>50</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>146</v>
+      </c>
+      <c r="T35">
+        <v>80</v>
+      </c>
+      <c r="U35">
+        <v>70</v>
+      </c>
+      <c r="W35">
+        <v>80</v>
+      </c>
+      <c r="AD35" s="33"/>
+      <c r="AE35" s="33"/>
+      <c r="AF35" s="33"/>
+      <c r="AG35" s="19"/>
       <c r="AH35" s="19"/>
-      <c r="AI35" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ35" s="39" t="s">
-        <v>165</v>
-      </c>
+      <c r="AI35" s="19"/>
+      <c r="AJ35" s="19"/>
       <c r="AK35" s="19"/>
       <c r="AL35" s="19"/>
-    </row>
-    <row r="36" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM35" s="19"/>
+      <c r="AN35" s="19"/>
+      <c r="AO35" s="19"/>
+    </row>
+    <row r="36" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
@@ -3049,26 +3299,14 @@
       <c r="I36" s="9"/>
       <c r="J36" s="6"/>
       <c r="M36" s="26"/>
-      <c r="N36">
-        <v>5</v>
-      </c>
       <c r="O36">
         <v>10</v>
       </c>
       <c r="P36">
         <v>50</v>
       </c>
-      <c r="Q36" t="s">
-        <v>146</v>
-      </c>
-      <c r="T36">
-        <v>80</v>
-      </c>
-      <c r="U36">
-        <v>70</v>
-      </c>
-      <c r="W36">
-        <v>80</v>
+      <c r="Q36">
+        <v>5</v>
       </c>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -3079,13 +3317,16 @@
       <c r="AJ36" s="19"/>
       <c r="AK36" s="19"/>
       <c r="AL36" s="19"/>
-    </row>
-    <row r="37" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM36" s="19"/>
+      <c r="AN36" s="19"/>
+      <c r="AO36" s="19"/>
+    </row>
+    <row r="37" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -3094,14 +3335,8 @@
       <c r="I37" s="9"/>
       <c r="J37" s="6"/>
       <c r="M37" s="26"/>
-      <c r="O37">
-        <v>10</v>
-      </c>
-      <c r="P37">
-        <v>50</v>
-      </c>
-      <c r="Q37">
-        <v>5</v>
+      <c r="Q37" t="s">
+        <v>143</v>
       </c>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -3109,16 +3344,23 @@
       <c r="AG37" s="19"/>
       <c r="AH37" s="19"/>
       <c r="AI37" s="19"/>
-      <c r="AJ37" s="19"/>
+      <c r="AJ37" s="47" t="s">
+        <v>270</v>
+      </c>
       <c r="AK37" s="19"/>
       <c r="AL37" s="19"/>
-    </row>
-    <row r="38" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM37" s="47" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN37" s="19"/>
+      <c r="AO37" s="19"/>
+    </row>
+    <row r="38" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -3127,8 +3369,14 @@
       <c r="I38" s="9"/>
       <c r="J38" s="6"/>
       <c r="M38" s="26"/>
-      <c r="Q38" t="s">
-        <v>143</v>
+      <c r="O38">
+        <v>20</v>
+      </c>
+      <c r="P38">
+        <v>50</v>
+      </c>
+      <c r="Q38">
+        <v>5</v>
       </c>
       <c r="AD38" s="33"/>
       <c r="AE38" s="33"/>
@@ -3136,18 +3384,19 @@
       <c r="AG38" s="19"/>
       <c r="AH38" s="19"/>
       <c r="AI38" s="19"/>
-      <c r="AJ38" s="47" t="s">
-        <v>270</v>
-      </c>
+      <c r="AJ38" s="19"/>
       <c r="AK38" s="19"/>
       <c r="AL38" s="19"/>
-    </row>
-    <row r="39" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM38" s="19"/>
+      <c r="AN38" s="19"/>
+      <c r="AO38" s="19"/>
+    </row>
+    <row r="39" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -3157,13 +3406,13 @@
       <c r="J39" s="6"/>
       <c r="M39" s="26"/>
       <c r="O39">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P39">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q39">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD39" s="33"/>
       <c r="AE39" s="33"/>
@@ -3174,13 +3423,16 @@
       <c r="AJ39" s="19"/>
       <c r="AK39" s="19"/>
       <c r="AL39" s="19"/>
-    </row>
-    <row r="40" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM39" s="19"/>
+      <c r="AN39" s="19"/>
+      <c r="AO39" s="19"/>
+    </row>
+    <row r="40" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
@@ -3190,10 +3442,10 @@
       <c r="J40" s="6"/>
       <c r="M40" s="26"/>
       <c r="O40">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="P40">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -3207,13 +3459,16 @@
       <c r="AJ40" s="19"/>
       <c r="AK40" s="19"/>
       <c r="AL40" s="19"/>
-    </row>
-    <row r="41" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM40" s="19"/>
+      <c r="AN40" s="19"/>
+      <c r="AO40" s="19"/>
+    </row>
+    <row r="41" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D41" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -3223,10 +3478,10 @@
       <c r="J41" s="6"/>
       <c r="M41" s="26"/>
       <c r="O41">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="P41">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -3240,200 +3495,247 @@
       <c r="AJ41" s="19"/>
       <c r="AK41" s="19"/>
       <c r="AL41" s="19"/>
-    </row>
-    <row r="42" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="6"/>
+      <c r="AM41" s="19"/>
+      <c r="AN41" s="19"/>
+      <c r="AO41" s="19"/>
+    </row>
+    <row r="42" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="9"/>
+      <c r="H42" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J42" s="6"/>
       <c r="M42" s="26"/>
-      <c r="O42">
-        <v>40</v>
-      </c>
-      <c r="P42">
+      <c r="Q42" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="T42">
         <v>50</v>
       </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="33"/>
+      <c r="U42">
+        <v>10</v>
+      </c>
+      <c r="X42" s="41"/>
+      <c r="AA42" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="AB42" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC42" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD42" s="58" t="s">
+        <v>220</v>
+      </c>
       <c r="AE42" s="33"/>
-      <c r="AF42" s="33"/>
-      <c r="AG42" s="19"/>
+      <c r="AF42" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="AG42" s="47"/>
       <c r="AH42" s="19"/>
-      <c r="AI42" s="19"/>
-      <c r="AJ42" s="19"/>
+      <c r="AI42" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="AJ42" s="47"/>
       <c r="AK42" s="19"/>
-      <c r="AL42" s="19"/>
-    </row>
-    <row r="43" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="32" t="s">
-        <v>62</v>
-      </c>
+      <c r="AL42" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="AM42" s="47"/>
+      <c r="AN42" s="19"/>
+      <c r="AO42" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="43" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="C43" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D43" s="32" t="s">
-        <v>62</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="D43" s="30"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="11" t="s">
-        <v>53</v>
+      <c r="F43" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I43" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J43" s="6"/>
       <c r="M43" s="26"/>
       <c r="Q43" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="T43">
-        <v>50</v>
-      </c>
-      <c r="U43">
-        <v>10</v>
+      <c r="U43" s="36" t="s">
+        <v>158</v>
       </c>
       <c r="X43" s="41"/>
-      <c r="AA43" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB43" s="54" t="s">
-        <v>222</v>
-      </c>
-      <c r="AC43" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="AD43" s="58" t="s">
-        <v>220</v>
-      </c>
+      <c r="AA43" s="47"/>
+      <c r="AD43" s="61"/>
       <c r="AE43" s="33"/>
-      <c r="AF43" s="33" t="s">
-        <v>221</v>
-      </c>
+      <c r="AF43" s="33"/>
       <c r="AG43" s="47"/>
       <c r="AH43" s="19"/>
-      <c r="AI43" s="19" t="s">
-        <v>221</v>
-      </c>
+      <c r="AI43" s="19"/>
       <c r="AJ43" s="47"/>
       <c r="AK43" s="19"/>
-      <c r="AL43" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="44" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="D44" s="30"/>
+      <c r="AL43" s="19"/>
+      <c r="AM43" s="47"/>
+      <c r="AN43" s="19"/>
+      <c r="AO43" s="19"/>
+    </row>
+    <row r="44" spans="1:41" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="50" t="s">
+        <v>267</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F44" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M44" s="26"/>
-      <c r="Q44" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="U44" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="X44" s="41"/>
-      <c r="AA44" s="47"/>
-      <c r="AD44" s="61"/>
-      <c r="AE44" s="33"/>
-      <c r="AF44" s="33"/>
-      <c r="AG44" s="47"/>
-      <c r="AH44" s="19"/>
-      <c r="AI44" s="19"/>
-      <c r="AJ44" s="47"/>
+      <c r="M44" s="28">
+        <v>130</v>
+      </c>
+      <c r="U44">
+        <v>30</v>
+      </c>
+      <c r="W44">
+        <v>60</v>
+      </c>
+      <c r="X44" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA44" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="AB44" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="AC44" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="AD44" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="AE44" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="AF44" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="AG44" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="AH44" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="AI44" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="AJ44" s="44" t="s">
+        <v>272</v>
+      </c>
       <c r="AK44" s="19"/>
-      <c r="AL44" s="19"/>
-    </row>
-    <row r="45" spans="1:38" ht="72" x14ac:dyDescent="0.3">
-      <c r="A45" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M45" s="28">
-        <v>130</v>
-      </c>
-      <c r="U45">
-        <v>30</v>
-      </c>
-      <c r="W45">
-        <v>60</v>
-      </c>
-      <c r="X45" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA45" s="44" t="s">
-        <v>209</v>
+      <c r="AL44" s="64"/>
+      <c r="AM44" s="44" t="s">
+        <v>272</v>
+      </c>
+      <c r="AN44" s="19"/>
+      <c r="AO44" s="64"/>
+    </row>
+    <row r="45" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A45" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E45" s="6"/>
+      <c r="M45" s="26"/>
+      <c r="O45">
+        <v>40</v>
+      </c>
+      <c r="P45">
+        <v>70</v>
+      </c>
+      <c r="Q45">
+        <v>0</v>
+      </c>
+      <c r="R45">
+        <v>50</v>
+      </c>
+      <c r="S45" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="T45">
+        <v>50</v>
+      </c>
+      <c r="U45" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="X45" s="39" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA45" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AB45" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC45" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="AD45" s="58" t="s">
-        <v>209</v>
+        <v>210</v>
+      </c>
+      <c r="AD45" s="56" t="s">
+        <v>165</v>
       </c>
       <c r="AE45" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="AF45" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="AG45" s="44" t="s">
-        <v>262</v>
+        <v>210</v>
+      </c>
+      <c r="AF45" s="33"/>
+      <c r="AG45" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AH45" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI45" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="AJ45" s="44" t="s">
-        <v>272</v>
+        <v>210</v>
+      </c>
+      <c r="AI45" s="19"/>
+      <c r="AJ45" s="43" t="s">
+        <v>165</v>
       </c>
       <c r="AK45" s="19"/>
-      <c r="AL45" s="64"/>
-    </row>
-    <row r="46" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AL45" s="19"/>
+      <c r="AM45" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN45" s="19"/>
+      <c r="AO45" s="19"/>
+    </row>
+    <row r="46" spans="1:41" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E46" s="6"/>
       <c r="M46" s="26"/>
@@ -3441,19 +3743,19 @@
         <v>40</v>
       </c>
       <c r="P46">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q46">
         <v>0</v>
       </c>
       <c r="R46">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S46" s="36" t="s">
         <v>144</v>
       </c>
       <c r="T46">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U46" s="36" t="s">
         <v>144</v>
@@ -3486,18 +3788,23 @@
       </c>
       <c r="AK46" s="19"/>
       <c r="AL46" s="19"/>
-    </row>
-    <row r="47" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A47" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>67</v>
+      <c r="AM46" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN46" s="19"/>
+      <c r="AO46" s="19"/>
+    </row>
+    <row r="47" spans="1:41" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A47" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>68</v>
       </c>
       <c r="E47" s="6"/>
       <c r="M47" s="26"/>
       <c r="O47">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="P47">
         <v>90</v>
@@ -3506,120 +3813,101 @@
         <v>0</v>
       </c>
       <c r="R47">
-        <v>100</v>
-      </c>
-      <c r="S47" s="36" t="s">
-        <v>144</v>
+        <v>70</v>
+      </c>
+      <c r="S47">
+        <v>5</v>
       </c>
       <c r="T47">
-        <v>100</v>
-      </c>
-      <c r="U47" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="X47" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA47" s="43" t="s">
-        <v>165</v>
+        <v>70</v>
+      </c>
+      <c r="U47">
+        <v>10</v>
+      </c>
+      <c r="X47" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y47" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA47" s="46" t="s">
+        <v>168</v>
       </c>
       <c r="AB47" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD47" s="56" t="s">
-        <v>165</v>
+        <v>186</v>
+      </c>
+      <c r="AD47" s="57" t="s">
+        <v>167</v>
       </c>
       <c r="AE47" s="33" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="AF47" s="33"/>
-      <c r="AG47" s="43" t="s">
-        <v>165</v>
+      <c r="AG47" s="45" t="s">
+        <v>167</v>
       </c>
       <c r="AH47" s="19" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="AI47" s="19"/>
-      <c r="AJ47" s="43" t="s">
-        <v>165</v>
+      <c r="AJ47" s="47" t="s">
+        <v>186</v>
       </c>
       <c r="AK47" s="19"/>
       <c r="AL47" s="19"/>
-    </row>
-    <row r="48" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A48" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="D48" s="33" t="s">
-        <v>68</v>
-      </c>
+      <c r="AM47" s="47" t="s">
+        <v>186</v>
+      </c>
+      <c r="AN47" s="19"/>
+      <c r="AO47" s="19"/>
+    </row>
+    <row r="48" spans="1:41" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A48" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="D48" s="33"/>
       <c r="E48" s="6"/>
       <c r="M48" s="26"/>
-      <c r="O48">
-        <v>10</v>
-      </c>
-      <c r="P48">
-        <v>90</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>70</v>
-      </c>
-      <c r="S48">
-        <v>5</v>
-      </c>
-      <c r="T48">
-        <v>70</v>
-      </c>
-      <c r="U48">
-        <v>10</v>
-      </c>
-      <c r="X48" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y48" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA48" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB48" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="AD48" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE48" s="33" t="s">
-        <v>186</v>
-      </c>
+      <c r="X48" s="37"/>
+      <c r="AA48" s="46"/>
+      <c r="AD48" s="57"/>
+      <c r="AE48" s="33"/>
       <c r="AF48" s="33"/>
       <c r="AG48" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="AH48" s="19" t="s">
-        <v>186</v>
-      </c>
+      <c r="AH48" s="19"/>
       <c r="AI48" s="19"/>
-      <c r="AJ48" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="AK48" s="19"/>
+      <c r="AJ48" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AK48" s="63" t="s">
+        <v>273</v>
+      </c>
       <c r="AL48" s="19"/>
-    </row>
-    <row r="49" spans="1:38" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AM48" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN48" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="AO48" s="19"/>
+    </row>
+    <row r="49" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A49" s="32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D49" s="33"/>
       <c r="E49" s="6"/>
       <c r="M49" s="26"/>
-      <c r="X49" s="37"/>
-      <c r="AA49" s="46"/>
-      <c r="AD49" s="57"/>
-      <c r="AE49" s="33"/>
-      <c r="AF49" s="33"/>
+      <c r="Y49"/>
+      <c r="Z49"/>
+      <c r="AA49"/>
+      <c r="AB49"/>
+      <c r="AC49"/>
+      <c r="AD49"/>
+      <c r="AE49"/>
+      <c r="AF49"/>
       <c r="AG49" s="45" t="s">
         <v>167</v>
       </c>
@@ -3629,13 +3917,20 @@
         <v>285</v>
       </c>
       <c r="AK49" s="63" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="AL49" s="19"/>
-    </row>
-    <row r="50" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AM49" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN49" s="63" t="s">
+        <v>280</v>
+      </c>
+      <c r="AO49" s="19"/>
+    </row>
+    <row r="50" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="6"/>
@@ -3656,14 +3951,17 @@
       <c r="AJ50" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="AK50" s="63" t="s">
-        <v>280</v>
-      </c>
+      <c r="AK50" s="19"/>
       <c r="AL50" s="19"/>
-    </row>
-    <row r="51" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AM50" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN50" s="19"/>
+      <c r="AO50" s="19"/>
+    </row>
+    <row r="51" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D51" s="33"/>
       <c r="E51" s="6"/>
@@ -3686,10 +3984,15 @@
       </c>
       <c r="AK51" s="19"/>
       <c r="AL51" s="19"/>
-    </row>
-    <row r="52" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AM51" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN51" s="19"/>
+      <c r="AO51" s="19"/>
+    </row>
+    <row r="52" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D52" s="33"/>
       <c r="E52" s="6"/>
@@ -3707,15 +4010,24 @@
       </c>
       <c r="AH52" s="19"/>
       <c r="AI52" s="19"/>
-      <c r="AJ52" s="43" t="s">
-        <v>285</v>
+      <c r="AJ52" s="44" t="s">
+        <v>166</v>
       </c>
       <c r="AK52" s="19"/>
-      <c r="AL52" s="19"/>
-    </row>
-    <row r="53" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AL52" s="63" t="s">
+        <v>275</v>
+      </c>
+      <c r="AM52" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN52" s="19"/>
+      <c r="AO52" s="63" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="53" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D53" s="33"/>
       <c r="E53" s="6"/>
@@ -3733,17 +4045,20 @@
       </c>
       <c r="AH53" s="19"/>
       <c r="AI53" s="19"/>
-      <c r="AJ53" s="44" t="s">
-        <v>166</v>
+      <c r="AJ53" s="43" t="s">
+        <v>285</v>
       </c>
       <c r="AK53" s="19"/>
-      <c r="AL53" s="63" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="54" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AL53" s="19"/>
+      <c r="AM53" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN53" s="19"/>
+      <c r="AO53" s="19"/>
+    </row>
+    <row r="54" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A54" s="32" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D54" s="33"/>
       <c r="E54" s="6"/>
@@ -3765,11 +4080,20 @@
         <v>285</v>
       </c>
       <c r="AK54" s="19"/>
-      <c r="AL54" s="19"/>
-    </row>
-    <row r="55" spans="1:38" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AL54" s="63" t="s">
+        <v>276</v>
+      </c>
+      <c r="AM54" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN54" s="19"/>
+      <c r="AO54" s="63" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="55" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A55" s="32" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D55" s="33"/>
       <c r="E55" s="6"/>
@@ -3782,8 +4106,8 @@
       <c r="AD55"/>
       <c r="AE55"/>
       <c r="AF55"/>
-      <c r="AG55" s="45" t="s">
-        <v>167</v>
+      <c r="AG55" s="46" t="s">
+        <v>168</v>
       </c>
       <c r="AH55" s="19"/>
       <c r="AI55" s="19"/>
@@ -3791,142 +4115,168 @@
         <v>285</v>
       </c>
       <c r="AK55" s="19"/>
-      <c r="AL55" s="63" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="56" spans="1:38" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A56" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D56" s="33"/>
+      <c r="AL55" s="19"/>
+      <c r="AM55" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN55" s="19"/>
+      <c r="AO55" s="19"/>
+    </row>
+    <row r="56" spans="1:41" ht="115.2" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A56" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="D56" s="33" t="s">
+        <v>171</v>
+      </c>
       <c r="E56" s="6"/>
       <c r="M56" s="26"/>
-      <c r="Y56"/>
-      <c r="Z56"/>
-      <c r="AA56"/>
-      <c r="AB56"/>
-      <c r="AC56"/>
-      <c r="AD56"/>
-      <c r="AE56"/>
-      <c r="AF56"/>
-      <c r="AG56" s="46" t="s">
+      <c r="P56">
+        <v>70</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>50</v>
+      </c>
+      <c r="S56">
+        <v>5</v>
+      </c>
+      <c r="T56">
+        <v>50</v>
+      </c>
+      <c r="U56">
+        <v>5</v>
+      </c>
+      <c r="X56" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="AH56" s="19"/>
+      <c r="Y56" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA56" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB56" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AD56" s="57" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE56" s="62" t="s">
+        <v>241</v>
+      </c>
+      <c r="AF56" s="33"/>
+      <c r="AG56" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="AH56" s="55" t="s">
+        <v>241</v>
+      </c>
       <c r="AI56" s="19"/>
       <c r="AJ56" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="AK56" s="19"/>
+      <c r="AK56" s="55" t="s">
+        <v>271</v>
+      </c>
       <c r="AL56" s="19"/>
-    </row>
-    <row r="57" spans="1:38" ht="115.2" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A57" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="D57" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E57" s="6"/>
-      <c r="M57" s="26"/>
-      <c r="P57">
+      <c r="AM56" s="43" t="s">
+        <v>285</v>
+      </c>
+      <c r="AN56" s="55" t="s">
+        <v>271</v>
+      </c>
+      <c r="AO56" s="19"/>
+    </row>
+    <row r="57" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="Q57">
-        <v>0</v>
-      </c>
-      <c r="R57">
-        <v>50</v>
-      </c>
-      <c r="S57">
-        <v>5</v>
-      </c>
-      <c r="T57">
-        <v>50</v>
-      </c>
-      <c r="U57">
-        <v>5</v>
-      </c>
-      <c r="X57" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y57" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA57" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB57" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="AD57" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE57" s="62" t="s">
-        <v>241</v>
-      </c>
+      <c r="E57" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="28">
+        <v>87</v>
+      </c>
+      <c r="W57" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD57" s="33"/>
+      <c r="AE57" s="33"/>
       <c r="AF57" s="33"/>
-      <c r="AG57" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="AH57" s="55" t="s">
-        <v>241</v>
-      </c>
+      <c r="AG57" s="19"/>
+      <c r="AH57" s="19"/>
       <c r="AI57" s="19"/>
-      <c r="AJ57" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AK57" s="55" t="s">
-        <v>271</v>
-      </c>
+      <c r="AJ57" s="19"/>
+      <c r="AK57" s="19"/>
       <c r="AL57" s="19"/>
-    </row>
-    <row r="58" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C58" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="AM57" s="19"/>
+      <c r="AN57" s="19"/>
+      <c r="AO57" s="19"/>
+    </row>
+    <row r="58" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="E58" s="6"/>
       <c r="F58" s="6"/>
       <c r="G58" s="6"/>
-      <c r="H58" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H58" s="11"/>
+      <c r="I58" s="9"/>
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
-      <c r="M58" s="28">
-        <v>87</v>
-      </c>
-      <c r="W58" t="s">
-        <v>163</v>
-      </c>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
       <c r="AD58" s="33"/>
       <c r="AE58" s="33"/>
       <c r="AF58" s="33"/>
-      <c r="AG58" s="19"/>
+      <c r="AG58" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AH58" s="19"/>
       <c r="AI58" s="19"/>
-      <c r="AJ58" s="19"/>
-      <c r="AK58" s="19"/>
+      <c r="AJ58" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="AK58" s="63" t="s">
+        <v>286</v>
+      </c>
       <c r="AL58" s="19"/>
-    </row>
-    <row r="59" spans="1:38" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="AM58" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="AN58" s="63" t="s">
+        <v>286</v>
+      </c>
+      <c r="AO58" s="19"/>
+    </row>
+    <row r="59" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A59" s="32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D59" s="32" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="6"/>
@@ -3936,7 +4286,6 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
       <c r="M59" s="28"/>
-      <c r="N59" s="28"/>
       <c r="AD59" s="33"/>
       <c r="AE59" s="33"/>
       <c r="AF59" s="33"/>
@@ -3948,17 +4297,20 @@
       <c r="AJ59" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="AK59" s="63" t="s">
-        <v>286</v>
-      </c>
+      <c r="AK59" s="19"/>
       <c r="AL59" s="19"/>
-    </row>
-    <row r="60" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="AM59" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="AN59" s="19"/>
+      <c r="AO59" s="19"/>
+    </row>
+    <row r="60" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -3977,17 +4329,22 @@
       <c r="AH60" s="19"/>
       <c r="AI60" s="19"/>
       <c r="AJ60" s="43" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AK60" s="19"/>
       <c r="AL60" s="19"/>
-    </row>
-    <row r="61" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="AM60" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="AN60" s="19"/>
+      <c r="AO60" s="19"/>
+    </row>
+    <row r="61" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -4000,23 +4357,26 @@
       <c r="AD61" s="33"/>
       <c r="AE61" s="33"/>
       <c r="AF61" s="33"/>
-      <c r="AG61" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AG61" s="19"/>
       <c r="AH61" s="19"/>
       <c r="AI61" s="19"/>
-      <c r="AJ61" s="43" t="s">
-        <v>288</v>
+      <c r="AJ61" s="45" t="s">
+        <v>167</v>
       </c>
       <c r="AK61" s="19"/>
       <c r="AL61" s="19"/>
-    </row>
-    <row r="62" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AM61" s="43" t="s">
+        <v>288</v>
+      </c>
+      <c r="AN61" s="19"/>
+      <c r="AO61" s="19"/>
+    </row>
+    <row r="62" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -4029,7 +4389,9 @@
       <c r="AD62" s="33"/>
       <c r="AE62" s="33"/>
       <c r="AF62" s="33"/>
-      <c r="AG62" s="19"/>
+      <c r="AG62" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AH62" s="19"/>
       <c r="AI62" s="19"/>
       <c r="AJ62" s="45" t="s">
@@ -4037,13 +4399,20 @@
       </c>
       <c r="AK62" s="19"/>
       <c r="AL62" s="19"/>
-    </row>
-    <row r="63" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AM62" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN62" s="63" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO62" s="19"/>
+    </row>
+    <row r="63" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="32" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -4061,18 +4430,23 @@
       </c>
       <c r="AH63" s="19"/>
       <c r="AI63" s="19"/>
-      <c r="AJ63" s="45" t="s">
-        <v>167</v>
+      <c r="AJ63" s="43" t="s">
+        <v>287</v>
       </c>
       <c r="AK63" s="19"/>
       <c r="AL63" s="19"/>
-    </row>
-    <row r="64" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AM63" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="AN63" s="19"/>
+      <c r="AO63" s="19"/>
+    </row>
+    <row r="64" spans="1:41" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A64" s="32" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -4095,13 +4469,20 @@
       </c>
       <c r="AK64" s="19"/>
       <c r="AL64" s="19"/>
-    </row>
-    <row r="65" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="AM64" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN64" s="63" t="s">
+        <v>304</v>
+      </c>
+      <c r="AO64" s="19"/>
+    </row>
+    <row r="65" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="6"/>
@@ -4114,99 +4495,95 @@
       <c r="AD65" s="33"/>
       <c r="AE65" s="33"/>
       <c r="AF65" s="33"/>
-      <c r="AG65" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AG65" s="19"/>
       <c r="AH65" s="19"/>
       <c r="AI65" s="19"/>
-      <c r="AJ65" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AJ65" s="19"/>
       <c r="AK65" s="19"/>
       <c r="AL65" s="19"/>
-    </row>
-    <row r="66" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D66" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="11"/>
-      <c r="I66" s="9"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="28"/>
-      <c r="AD66" s="33"/>
-      <c r="AE66" s="33"/>
+      <c r="AM65" s="19"/>
+      <c r="AN65" s="19"/>
+      <c r="AO65" s="19"/>
+    </row>
+    <row r="66" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="M66" s="26"/>
+      <c r="R66">
+        <v>10</v>
+      </c>
+      <c r="S66" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="V66">
+        <v>60</v>
+      </c>
+      <c r="W66" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="X66" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y66" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AA66" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB66" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD66" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="AE66" s="33" t="s">
+        <v>187</v>
+      </c>
       <c r="AF66" s="33"/>
-      <c r="AG66" s="19"/>
-      <c r="AH66" s="19"/>
+      <c r="AG66" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="AH66" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="AI66" s="19"/>
-      <c r="AJ66" s="19"/>
-      <c r="AK66" s="19"/>
+      <c r="AJ66" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="AK66" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="AL66" s="19"/>
-    </row>
-    <row r="67" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D67" s="30" t="s">
-        <v>71</v>
+      <c r="AM66" s="46" t="s">
+        <v>264</v>
+      </c>
+      <c r="AN66" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="AO66" s="19"/>
+    </row>
+    <row r="67" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="M67" s="26"/>
-      <c r="R67">
-        <v>10</v>
-      </c>
-      <c r="S67" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="V67">
-        <v>60</v>
-      </c>
-      <c r="W67" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="X67" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y67" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA67" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB67" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD67" s="60" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE67" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="AF67" s="33"/>
-      <c r="AG67" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="AH67" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="AG67" s="19"/>
+      <c r="AH67" s="19"/>
       <c r="AI67" s="19"/>
-      <c r="AJ67" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="AK67" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="AJ67" s="19"/>
+      <c r="AK67" s="19"/>
       <c r="AL67" s="19"/>
-    </row>
-    <row r="68" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM67" s="19"/>
+      <c r="AN67" s="19"/>
+      <c r="AO67" s="19"/>
+    </row>
+    <row r="68" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D68" s="13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M68" s="26"/>
       <c r="AG68" s="19"/>
@@ -4215,10 +4592,13 @@
       <c r="AJ68" s="19"/>
       <c r="AK68" s="19"/>
       <c r="AL68" s="19"/>
-    </row>
-    <row r="69" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM68" s="19"/>
+      <c r="AN68" s="19"/>
+      <c r="AO68" s="19"/>
+    </row>
+    <row r="69" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D69" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M69" s="26"/>
       <c r="AG69" s="19"/>
@@ -4227,10 +4607,13 @@
       <c r="AJ69" s="19"/>
       <c r="AK69" s="19"/>
       <c r="AL69" s="19"/>
-    </row>
-    <row r="70" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM69" s="19"/>
+      <c r="AN69" s="19"/>
+      <c r="AO69" s="19"/>
+    </row>
+    <row r="70" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D70" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M70" s="26"/>
       <c r="AG70" s="19"/>
@@ -4239,10 +4622,13 @@
       <c r="AJ70" s="19"/>
       <c r="AK70" s="19"/>
       <c r="AL70" s="19"/>
-    </row>
-    <row r="71" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM70" s="19"/>
+      <c r="AN70" s="19"/>
+      <c r="AO70" s="19"/>
+    </row>
+    <row r="71" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D71" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M71" s="26"/>
       <c r="AG71" s="19"/>
@@ -4251,10 +4637,13 @@
       <c r="AJ71" s="19"/>
       <c r="AK71" s="19"/>
       <c r="AL71" s="19"/>
-    </row>
-    <row r="72" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM71" s="19"/>
+      <c r="AN71" s="19"/>
+      <c r="AO71" s="19"/>
+    </row>
+    <row r="72" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D72" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M72" s="26"/>
       <c r="AG72" s="19"/>
@@ -4263,22 +4652,40 @@
       <c r="AJ72" s="19"/>
       <c r="AK72" s="19"/>
       <c r="AL72" s="19"/>
-    </row>
-    <row r="73" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM72" s="19"/>
+      <c r="AN72" s="19"/>
+      <c r="AO72" s="19"/>
+    </row>
+    <row r="73" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D73" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M73" s="26"/>
+      <c r="P73">
+        <v>5</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>5</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
       <c r="AG73" s="19"/>
       <c r="AH73" s="19"/>
       <c r="AI73" s="19"/>
       <c r="AJ73" s="19"/>
       <c r="AK73" s="19"/>
       <c r="AL73" s="19"/>
-    </row>
-    <row r="74" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM73" s="19"/>
+      <c r="AN73" s="19"/>
+      <c r="AO73" s="19"/>
+    </row>
+    <row r="74" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="D74" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M74" s="26"/>
       <c r="P74">
@@ -4299,104 +4706,148 @@
       <c r="AJ74" s="19"/>
       <c r="AK74" s="19"/>
       <c r="AL74" s="19"/>
-    </row>
-    <row r="75" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM74" s="19"/>
+      <c r="AN74" s="19"/>
+      <c r="AO74" s="19"/>
+    </row>
+    <row r="75" spans="1:41" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>80</v>
+      </c>
       <c r="D75" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="M75" s="26"/>
+        <v>81</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
       <c r="P75">
         <v>5</v>
       </c>
       <c r="Q75">
         <v>0</v>
       </c>
-      <c r="R75">
-        <v>5</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="AG75" s="19"/>
-      <c r="AH75" s="19"/>
-      <c r="AI75" s="19"/>
-      <c r="AJ75" s="19"/>
-      <c r="AK75" s="19"/>
-      <c r="AL75" s="19"/>
-    </row>
-    <row r="76" spans="1:38" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>80</v>
-      </c>
+      <c r="S75" t="s">
+        <v>151</v>
+      </c>
+      <c r="W75" t="s">
+        <v>164</v>
+      </c>
+      <c r="X75" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA75" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AB75" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC75" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG75" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH75" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="AI75" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="AJ75" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK75" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="AL75" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="AM75" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN75" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="AO75" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C76" s="13"/>
       <c r="D76" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="E76" s="6"/>
       <c r="F76" s="6"/>
       <c r="G76" s="6"/>
-      <c r="H76" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I76" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="9"/>
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
-      <c r="P76">
-        <v>5</v>
-      </c>
-      <c r="Q76">
-        <v>0</v>
-      </c>
-      <c r="S76" t="s">
-        <v>151</v>
-      </c>
-      <c r="W76" t="s">
-        <v>164</v>
+      <c r="M76" s="26"/>
+      <c r="R76">
+        <v>90</v>
+      </c>
+      <c r="S76" s="36" t="s">
+        <v>152</v>
       </c>
       <c r="X76" s="38" t="s">
         <v>166</v>
       </c>
+      <c r="Y76" s="19" t="s">
+        <v>183</v>
+      </c>
       <c r="AA76" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="AB76" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC76" s="19" t="s">
-        <v>212</v>
+      <c r="AB76" s="55" t="s">
+        <v>235</v>
       </c>
       <c r="AG76" s="43" t="s">
         <v>165</v>
       </c>
       <c r="AH76" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="AI76" s="19" t="s">
-        <v>212</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AI76" s="19"/>
       <c r="AJ76" s="43" t="s">
         <v>165</v>
       </c>
       <c r="AK76" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="AL76" s="19" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="77" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+      <c r="AL76" s="19"/>
+      <c r="AM76" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN76" s="55" t="s">
+        <v>235</v>
+      </c>
+      <c r="AO76" s="19"/>
+    </row>
+    <row r="77" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13" t="s">
-        <v>82</v>
+        <v>191</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -4406,46 +4857,71 @@
       <c r="K77" s="12"/>
       <c r="L77" s="12"/>
       <c r="M77" s="26"/>
+      <c r="P77">
+        <v>10</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
       <c r="R77">
-        <v>90</v>
-      </c>
-      <c r="S77" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="X77" s="38" t="s">
-        <v>166</v>
+        <v>30</v>
+      </c>
+      <c r="S77">
+        <v>5</v>
+      </c>
+      <c r="X77" s="42" t="s">
+        <v>190</v>
       </c>
       <c r="Y77" s="19" t="s">
-        <v>183</v>
+        <v>189</v>
+      </c>
+      <c r="Z77" s="19" t="s">
+        <v>188</v>
       </c>
       <c r="AA77" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="AB77" s="55" t="s">
-        <v>235</v>
+      <c r="AB77" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="AC77" s="19" t="s">
+        <v>188</v>
       </c>
       <c r="AG77" s="43" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="AH77" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="AI77" s="19"/>
+        <v>239</v>
+      </c>
+      <c r="AI77" s="19" t="s">
+        <v>188</v>
+      </c>
       <c r="AJ77" s="43" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="AK77" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="AL77" s="19"/>
-    </row>
-    <row r="78" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+      <c r="AL77" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AM77" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="AN77" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="AO77" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="78" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="C78" s="13"/>
       <c r="D78" s="13" t="s">
-        <v>191</v>
+        <v>83</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -4456,61 +4932,46 @@
       <c r="L78" s="12"/>
       <c r="M78" s="26"/>
       <c r="P78">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q78">
         <v>0</v>
       </c>
       <c r="R78">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S78">
         <v>5</v>
       </c>
-      <c r="X78" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y78" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z78" s="19" t="s">
-        <v>188</v>
+      <c r="X78" s="39" t="s">
+        <v>165</v>
       </c>
       <c r="AA78" s="43" t="s">
         <v>165</v>
       </c>
-      <c r="AB78" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="AC78" s="19" t="s">
-        <v>188</v>
-      </c>
       <c r="AG78" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="AH78" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="AI78" s="19" t="s">
-        <v>188</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="AH78" s="19"/>
+      <c r="AI78" s="19"/>
       <c r="AJ78" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="AK78" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="AL78" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="79" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="AK78" s="19"/>
+      <c r="AL78" s="19"/>
+      <c r="AM78" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN78" s="19"/>
+      <c r="AO78" s="19"/>
+    </row>
+    <row r="79" spans="1:41" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C79" s="13"/>
       <c r="D79" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -4521,41 +4982,58 @@
       <c r="L79" s="12"/>
       <c r="M79" s="26"/>
       <c r="P79">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="Q79">
         <v>0</v>
       </c>
       <c r="R79">
-        <v>40</v>
-      </c>
-      <c r="S79">
-        <v>5</v>
-      </c>
-      <c r="X79" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA79" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AG79" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AH79" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="S79" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="X79" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y79" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA79" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="AB79" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AG79" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="AH79" s="19" t="s">
+        <v>213</v>
+      </c>
       <c r="AI79" s="19"/>
-      <c r="AJ79" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK79" s="19"/>
+      <c r="AJ79" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="AK79" s="19" t="s">
+        <v>213</v>
+      </c>
       <c r="AL79" s="19"/>
-    </row>
-    <row r="80" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM79" s="44" t="s">
+        <v>236</v>
+      </c>
+      <c r="AN79" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO79" s="19"/>
+    </row>
+    <row r="80" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -4565,66 +5043,47 @@
       <c r="K80" s="12"/>
       <c r="L80" s="12"/>
       <c r="M80" s="26"/>
-      <c r="P80">
-        <v>5</v>
-      </c>
-      <c r="Q80">
-        <v>0</v>
-      </c>
       <c r="R80">
-        <v>30</v>
-      </c>
-      <c r="S80" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="X80" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y80" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA80" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB80" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG80" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AH80" s="19" t="s">
-        <v>213</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="S80">
+        <v>10</v>
+      </c>
+      <c r="AG80" s="19"/>
+      <c r="AH80" s="19"/>
       <c r="AI80" s="19"/>
-      <c r="AJ80" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AK80" s="19" t="s">
-        <v>213</v>
-      </c>
+      <c r="AJ80" s="19"/>
+      <c r="AK80" s="19"/>
       <c r="AL80" s="19"/>
-    </row>
-    <row r="81" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM80" s="19"/>
+      <c r="AN80" s="19"/>
+      <c r="AO80" s="19"/>
+    </row>
+    <row r="81" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="13" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
       <c r="G81" s="6"/>
       <c r="H81" s="6"/>
-      <c r="I81" s="9"/>
-      <c r="K81" s="12"/>
-      <c r="L81" s="12"/>
+      <c r="J81" s="9"/>
       <c r="M81" s="26"/>
+      <c r="P81">
+        <v>5</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
       <c r="R81">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="S81">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG81" s="19"/>
       <c r="AH81" s="19"/>
@@ -4632,14 +5091,17 @@
       <c r="AJ81" s="19"/>
       <c r="AK81" s="19"/>
       <c r="AL81" s="19"/>
-    </row>
-    <row r="82" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM81" s="19"/>
+      <c r="AN81" s="19"/>
+      <c r="AO81" s="19"/>
+    </row>
+    <row r="82" spans="1:41" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C82" s="13"/>
       <c r="D82" s="13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -4647,32 +5109,59 @@
       <c r="H82" s="6"/>
       <c r="J82" s="9"/>
       <c r="M82" s="26"/>
-      <c r="P82">
-        <v>5</v>
-      </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>10</v>
-      </c>
-      <c r="S82">
-        <v>5</v>
-      </c>
-      <c r="AG82" s="19"/>
-      <c r="AH82" s="19"/>
-      <c r="AI82" s="19"/>
-      <c r="AJ82" s="19"/>
-      <c r="AK82" s="19"/>
-      <c r="AL82" s="19"/>
-    </row>
-    <row r="83" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="X82" s="37" t="s">
+        <v>170</v>
+      </c>
+      <c r="Y82" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z82" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA82" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB82" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AC82" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AG82" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AH82" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI82" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AJ82" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AK82" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AL82" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="AM82" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="AN82" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO82" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="83" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C83" s="13"/>
       <c r="D83" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -4680,50 +5169,62 @@
       <c r="H83" s="6"/>
       <c r="J83" s="9"/>
       <c r="M83" s="26"/>
+      <c r="S83" s="36" t="s">
+        <v>144</v>
+      </c>
       <c r="X83" s="37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Y83" s="19" t="s">
         <v>193</v>
       </c>
       <c r="Z83" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AA83" s="46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AB83" s="19" t="s">
         <v>193</v>
       </c>
       <c r="AC83" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG83" s="46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AH83" s="19" t="s">
         <v>193</v>
       </c>
       <c r="AI83" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AJ83" s="46" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AK83" s="19" t="s">
         <v>193</v>
       </c>
       <c r="AL83" s="19" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="84" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+      <c r="AM83" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="AN83" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AO83" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="84" spans="1:41" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C84" s="13"/>
       <c r="D84" s="13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -4735,125 +5236,137 @@
         <v>144</v>
       </c>
       <c r="X84" s="37" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="Y84" s="19" t="s">
         <v>193</v>
       </c>
       <c r="Z84" s="19" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AA84" s="46" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="AB84" s="19" t="s">
         <v>193</v>
       </c>
       <c r="AC84" s="19" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AG84" s="46" t="s">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="AH84" s="19" t="s">
         <v>193</v>
       </c>
       <c r="AI84" s="19" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="AJ84" s="46" t="s">
-        <v>172</v>
+        <v>242</v>
       </c>
       <c r="AK84" s="19" t="s">
         <v>193</v>
       </c>
       <c r="AL84" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="85" spans="1:38" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="J85" s="9"/>
-      <c r="M85" s="26"/>
-      <c r="S85" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="X85" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y85" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="AM84" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="AN84" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="Z85" s="19" t="s">
+      <c r="AO84" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="AA85" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB85" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AC85" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG85" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="AH85" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI85" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ85" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="AK85" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL85" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="86" spans="1:38" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="50">
+    </row>
+    <row r="85" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A85" s="50">
         <v>4</v>
       </c>
-      <c r="B86" s="16" t="s">
+      <c r="B85" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C86" s="24" t="s">
+      <c r="C85" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="M86" s="28">
+      <c r="M85" s="28">
         <v>106</v>
       </c>
-      <c r="AG86" s="19"/>
+      <c r="AG85" s="19"/>
+      <c r="AH85" s="19"/>
+      <c r="AI85" s="19"/>
+      <c r="AJ85" s="19"/>
+      <c r="AK85" s="19"/>
+      <c r="AL85" s="19"/>
+      <c r="AM85" s="19"/>
+      <c r="AN85" s="19"/>
+      <c r="AO85" s="19"/>
+    </row>
+    <row r="86" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C86" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="D86" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="J86" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="M86" s="26"/>
+      <c r="P86">
+        <v>20</v>
+      </c>
+      <c r="Q86">
+        <v>5</v>
+      </c>
+      <c r="R86">
+        <v>50</v>
+      </c>
+      <c r="S86">
+        <v>10</v>
+      </c>
+      <c r="X86" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA86" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG86" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AH86" s="19"/>
       <c r="AI86" s="19"/>
-      <c r="AJ86" s="19"/>
+      <c r="AJ86" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AK86" s="19"/>
       <c r="AL86" s="19"/>
-    </row>
-    <row r="87" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM86" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN86" s="19"/>
+      <c r="AO86" s="19"/>
+    </row>
+    <row r="87" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A87" s="49" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C87" s="27" t="s">
-        <v>216</v>
-      </c>
-      <c r="D87" s="34" t="s">
-        <v>91</v>
+        <v>217</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>93</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>18</v>
@@ -4862,57 +5375,88 @@
       <c r="G87" s="6"/>
       <c r="H87" s="6"/>
       <c r="J87" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M87" s="26"/>
       <c r="P87">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q87">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R87">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="S87">
-        <v>10</v>
-      </c>
-      <c r="X87" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA87" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG87" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH87" s="19"/>
-      <c r="AI87" s="19"/>
-      <c r="AJ87" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK87" s="19"/>
-      <c r="AL87" s="19"/>
-    </row>
-    <row r="88" spans="1:38" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="C88" s="27" t="s">
-        <v>217</v>
+        <v>0</v>
+      </c>
+      <c r="X87" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y87" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z87" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA87" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB87" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AC87" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AG87" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="AH87" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AI87" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="AJ87" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="AK87" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL87" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="AM87" s="43" t="s">
+        <v>266</v>
+      </c>
+      <c r="AN87" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AO87" s="19" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="88" spans="1:41" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="J88" s="14" t="s">
-        <v>94</v>
-      </c>
+      <c r="H88" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J88" s="6"/>
+      <c r="K88" s="12"/>
+      <c r="L88" s="12"/>
       <c r="M88" s="26"/>
       <c r="P88">
         <v>10</v>
@@ -4930,48 +5474,46 @@
         <v>168</v>
       </c>
       <c r="Y88" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z88" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA88" s="46" t="s">
         <v>168</v>
       </c>
       <c r="AB88" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AC88" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG88" s="43" t="s">
-        <v>266</v>
+        <v>230</v>
+      </c>
+      <c r="AG88" s="45" t="s">
+        <v>237</v>
       </c>
       <c r="AH88" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AI88" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="AJ88" s="43" t="s">
-        <v>266</v>
+        <v>230</v>
+      </c>
+      <c r="AI88" s="19"/>
+      <c r="AJ88" s="45" t="s">
+        <v>237</v>
       </c>
       <c r="AK88" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL88" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="89" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="AL88" s="19"/>
+      <c r="AM88" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="AN88" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AO88" s="19"/>
+    </row>
+    <row r="89" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A89" s="30" t="s">
-        <v>95</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B89" s="15"/>
       <c r="C89" s="23" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>18</v>
@@ -4981,22 +5523,9 @@
       <c r="H89" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J89" s="6"/>
-      <c r="K89" s="12"/>
-      <c r="L89" s="12"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="12"/>
       <c r="M89" s="26"/>
-      <c r="P89">
-        <v>10</v>
-      </c>
-      <c r="Q89">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>10</v>
-      </c>
-      <c r="S89">
-        <v>0</v>
-      </c>
       <c r="X89" s="37" t="s">
         <v>168</v>
       </c>
@@ -5007,87 +5536,94 @@
         <v>168</v>
       </c>
       <c r="AB89" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="AG89" s="45" t="s">
-        <v>237</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="AG89" s="19"/>
       <c r="AH89" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AI89" s="19"/>
-      <c r="AJ89" s="45" t="s">
-        <v>237</v>
-      </c>
+      <c r="AJ89" s="19"/>
       <c r="AK89" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AL89" s="19"/>
-    </row>
-    <row r="90" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM89" s="19"/>
+      <c r="AN89" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AO89" s="19"/>
+    </row>
+    <row r="90" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A90" s="30" t="s">
-        <v>97</v>
+        <v>243</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="23" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="10"/>
       <c r="H90" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I90" s="6"/>
-      <c r="J90" s="12"/>
+      <c r="I90" s="15"/>
+      <c r="J90" s="10"/>
+      <c r="K90" s="13"/>
+      <c r="L90" s="13"/>
       <c r="M90" s="26"/>
-      <c r="X90" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y90" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA90" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB90" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AG90" s="19"/>
-      <c r="AH90" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AI90" s="19"/>
-      <c r="AJ90" s="19"/>
-      <c r="AK90" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AL90" s="19"/>
-    </row>
-    <row r="91" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="X90" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA90" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC90" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG90" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AH90" s="19"/>
+      <c r="AI90" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AJ90" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="AK90" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="AL90" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AM90" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN90" s="63" t="s">
+        <v>283</v>
+      </c>
+      <c r="AO90" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="91" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A91" s="30" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B91" s="15"/>
-      <c r="C91" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="D91" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="C91" s="23"/>
+      <c r="D91" s="13"/>
+      <c r="E91" s="6"/>
       <c r="F91" s="10"/>
       <c r="G91" s="10"/>
-      <c r="H91" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H91" s="11"/>
       <c r="I91" s="15"/>
       <c r="J91" s="10"/>
       <c r="K91" s="13"/>
@@ -5099,69 +5635,90 @@
       <c r="AA91" s="44" t="s">
         <v>166</v>
       </c>
-      <c r="AC91" s="19" t="s">
-        <v>227</v>
-      </c>
       <c r="AG91" s="44" t="s">
         <v>166</v>
       </c>
       <c r="AH91" s="19"/>
-      <c r="AI91" s="19" t="s">
-        <v>227</v>
-      </c>
+      <c r="AI91" s="19"/>
       <c r="AJ91" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="AK91" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="AL91" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="92" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>166</v>
+      </c>
+      <c r="AK91" s="19"/>
+      <c r="AL91" s="19"/>
+      <c r="AM91" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN91" s="19"/>
+      <c r="AO91" s="19"/>
+    </row>
+    <row r="92" spans="1:41" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A92" s="30" t="s">
-        <v>244</v>
+        <v>100</v>
       </c>
       <c r="B92" s="15"/>
-      <c r="C92" s="23"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="10"/>
-      <c r="H92" s="11"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="10"/>
-      <c r="K92" s="13"/>
-      <c r="L92" s="13"/>
+      <c r="C92" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="12"/>
+      <c r="L92" s="12"/>
       <c r="M92" s="26"/>
-      <c r="X92" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA92" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AG92" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AH92" s="19"/>
+      <c r="X92" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y92" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA92" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB92" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG92" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH92" s="19" t="s">
+        <v>228</v>
+      </c>
       <c r="AI92" s="19"/>
-      <c r="AJ92" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK92" s="19"/>
+      <c r="AJ92" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK92" s="19" t="s">
+        <v>228</v>
+      </c>
       <c r="AL92" s="19"/>
-    </row>
-    <row r="93" spans="1:38" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM92" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN92" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AO92" s="19"/>
+    </row>
+    <row r="93" spans="1:41" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A93" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="23" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>18</v>
@@ -5173,55 +5730,61 @@
       </c>
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
-      <c r="K93" s="12"/>
-      <c r="L93" s="12"/>
+      <c r="K93" s="17"/>
+      <c r="L93" s="17"/>
       <c r="M93" s="26"/>
       <c r="X93" s="37" t="s">
         <v>168</v>
       </c>
       <c r="Y93" s="19" t="s">
-        <v>182</v>
+        <v>197</v>
+      </c>
+      <c r="Z93" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="AA93" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AB93" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AG93" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH93" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AI93" s="19"/>
-      <c r="AJ93" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK93" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL93" s="19"/>
-    </row>
-    <row r="94" spans="1:38" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B94" s="15"/>
-      <c r="C94" s="23" t="s">
-        <v>102</v>
-      </c>
+      <c r="AB93" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AC93" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AG93" s="19"/>
+      <c r="AH93" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AI93" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AJ93" s="19"/>
+      <c r="AK93" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AL93" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="AM93" s="19"/>
+      <c r="AN93" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AO93" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="94" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" s="18"/>
       <c r="D94" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="E94" s="6"/>
       <c r="F94" s="6"/>
       <c r="G94" s="6"/>
-      <c r="H94" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
       <c r="K94" s="17"/>
@@ -5230,90 +5793,113 @@
       <c r="X94" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="Y94" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z94" s="19" t="s">
-        <v>198</v>
-      </c>
       <c r="AA94" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AB94" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AC94" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AG94" s="19"/>
-      <c r="AH94" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AI94" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AJ94" s="19"/>
-      <c r="AK94" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AL94" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="95" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B95" s="18"/>
+      <c r="AG94" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AH94" s="19"/>
+      <c r="AI94" s="19"/>
+      <c r="AJ94" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AK94" s="19"/>
+      <c r="AL94" s="19"/>
+      <c r="AM94" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN94" s="19"/>
+      <c r="AO94" s="19"/>
+    </row>
+    <row r="95" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>105</v>
+      </c>
       <c r="D95" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="6"/>
+        <v>106</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" s="12"/>
+      <c r="G95" s="12"/>
+      <c r="H95" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="I95" s="19"/>
+      <c r="J95" s="12"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="26"/>
       <c r="X95" s="37" t="s">
         <v>168</v>
       </c>
+      <c r="Y95" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="Z95" s="19" t="s">
+        <v>200</v>
+      </c>
       <c r="AA95" s="46" t="s">
         <v>168</v>
       </c>
+      <c r="AB95" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AC95" s="19" t="s">
+        <v>200</v>
+      </c>
       <c r="AG95" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AH95" s="19"/>
-      <c r="AI95" s="19"/>
+      <c r="AH95" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AI95" s="19" t="s">
+        <v>200</v>
+      </c>
       <c r="AJ95" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AK95" s="19"/>
-      <c r="AL95" s="19"/>
-    </row>
-    <row r="96" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AK95" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AL95" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="AM95" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN95" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AO95" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="96" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A96" s="30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C96" s="23" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E96" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F96" s="12"/>
-      <c r="G96" s="12"/>
-      <c r="H96" s="20" t="s">
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I96" s="19"/>
-      <c r="J96" s="12"/>
+      <c r="J96" s="6"/>
       <c r="K96" s="17"/>
       <c r="L96" s="17"/>
       <c r="M96" s="26"/>
@@ -5329,8 +5915,8 @@
       <c r="AA96" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AB96" s="53">
-        <v>46314</v>
+      <c r="AB96" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="AC96" s="19" t="s">
         <v>200</v>
@@ -5338,8 +5924,8 @@
       <c r="AG96" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AH96" s="53">
-        <v>46314</v>
+      <c r="AH96" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="AI96" s="19" t="s">
         <v>200</v>
@@ -5347,22 +5933,31 @@
       <c r="AJ96" s="46" t="s">
         <v>168</v>
       </c>
-      <c r="AK96" s="53">
-        <v>46314</v>
+      <c r="AK96" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="AL96" s="19" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="97" spans="1:38" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C97" s="23" t="s">
-        <v>107</v>
+      <c r="AM96" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN96" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="AO96" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="97" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C97" s="16" t="s">
+        <v>109</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>18</v>
@@ -5372,109 +5967,90 @@
       <c r="H97" s="11" t="s">
         <v>53</v>
       </c>
+      <c r="I97" s="6"/>
       <c r="J97" s="6"/>
-      <c r="K97" s="17"/>
-      <c r="L97" s="17"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
       <c r="M97" s="26"/>
+      <c r="P97">
+        <v>5</v>
+      </c>
+      <c r="S97" t="s">
+        <v>150</v>
+      </c>
       <c r="X97" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="Y97" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z97" s="19" t="s">
-        <v>200</v>
-      </c>
       <c r="AA97" s="46" t="s">
         <v>168</v>
       </c>
       <c r="AB97" s="19" t="s">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="AC97" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG97" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AH97" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="AG97" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="AH97" s="19"/>
       <c r="AI97" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AJ97" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AK97" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="AJ97" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK97" s="19"/>
       <c r="AL97" s="19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="98" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>249</v>
+      </c>
+      <c r="AM97" s="43" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN97" s="19"/>
+      <c r="AO97" s="19" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="98" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>109</v>
+        <v>278</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="D98" s="13"/>
+      <c r="E98" s="6"/>
       <c r="F98" s="6"/>
       <c r="G98" s="6"/>
-      <c r="H98" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H98" s="11"/>
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
       <c r="M98" s="26"/>
-      <c r="P98">
-        <v>5</v>
-      </c>
-      <c r="S98" t="s">
-        <v>150</v>
-      </c>
-      <c r="X98" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA98" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB98" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC98" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="AG98" s="43" t="s">
-        <v>245</v>
-      </c>
+      <c r="X98" s="37"/>
+      <c r="AA98" s="46"/>
+      <c r="AG98" s="43"/>
       <c r="AH98" s="19"/>
-      <c r="AI98" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ98" s="43" t="s">
-        <v>165</v>
+      <c r="AI98" s="19"/>
+      <c r="AJ98" s="47" t="s">
+        <v>281</v>
       </c>
       <c r="AK98" s="19"/>
-      <c r="AL98" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="99" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AL98" s="19"/>
+      <c r="AM98" s="47" t="s">
+        <v>281</v>
+      </c>
+      <c r="AN98" s="19"/>
+      <c r="AO98" s="19"/>
+    </row>
+    <row r="99" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D99" s="13"/>
       <c r="E99" s="6"/>
@@ -5491,82 +6067,109 @@
       <c r="AG99" s="43"/>
       <c r="AH99" s="19"/>
       <c r="AI99" s="19"/>
-      <c r="AJ99" s="47" t="s">
-        <v>281</v>
-      </c>
-      <c r="AK99" s="19"/>
+      <c r="AJ99" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK99" s="63" t="s">
+        <v>282</v>
+      </c>
       <c r="AL99" s="19"/>
-    </row>
-    <row r="100" spans="1:38" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C100" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="D100" s="13"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="11"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="26"/>
-      <c r="X100" s="37"/>
-      <c r="AA100" s="46"/>
-      <c r="AG100" s="43"/>
+      <c r="AM99" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN99" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO99" s="19"/>
+    </row>
+    <row r="100" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A100" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="M100" s="28">
+        <v>156</v>
+      </c>
+      <c r="X100" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA100" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG100" s="46" t="s">
+        <v>203</v>
+      </c>
       <c r="AH100" s="19"/>
       <c r="AI100" s="19"/>
-      <c r="AJ100" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK100" s="63" t="s">
-        <v>282</v>
-      </c>
+      <c r="AJ100" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AK100" s="19"/>
       <c r="AL100" s="19"/>
-    </row>
-    <row r="101" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A101" s="50" t="s">
-        <v>223</v>
-      </c>
-      <c r="B101" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C101" s="24" t="s">
-        <v>112</v>
-      </c>
-      <c r="M101" s="28">
-        <v>156</v>
-      </c>
+      <c r="AM100" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AN100" s="19"/>
+      <c r="AO100" s="19"/>
+    </row>
+    <row r="101" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B101" s="18"/>
+      <c r="C101" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D101" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="26"/>
       <c r="X101" s="37" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="AA101" s="46" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="AG101" s="46" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="AH101" s="19"/>
       <c r="AI101" s="19"/>
       <c r="AJ101" s="46" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="AK101" s="19"/>
       <c r="AL101" s="19"/>
-    </row>
-    <row r="102" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM101" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN101" s="19"/>
+      <c r="AO101" s="19"/>
+    </row>
+    <row r="102" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B102" s="18"/>
       <c r="C102" s="16" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
@@ -5594,51 +6197,43 @@
       </c>
       <c r="AK102" s="19"/>
       <c r="AL102" s="19"/>
-    </row>
-    <row r="103" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>116</v>
-      </c>
+      <c r="AM102" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="AN102" s="19"/>
+      <c r="AO102" s="19"/>
+    </row>
+    <row r="103" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A103"/>
       <c r="B103" s="18"/>
-      <c r="C103" s="16" t="s">
-        <v>116</v>
-      </c>
+      <c r="C103"/>
       <c r="D103" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E103" s="6"/>
       <c r="F103" s="6"/>
       <c r="G103" s="6"/>
-      <c r="H103" s="21" t="s">
-        <v>115</v>
-      </c>
+      <c r="H103" s="21"/>
       <c r="J103" s="6"/>
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
       <c r="M103" s="26"/>
-      <c r="X103" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA103" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG103" s="46" t="s">
-        <v>168</v>
-      </c>
+      <c r="AG103" s="19"/>
       <c r="AH103" s="19"/>
       <c r="AI103" s="19"/>
-      <c r="AJ103" s="46" t="s">
-        <v>168</v>
-      </c>
+      <c r="AJ103" s="19"/>
       <c r="AK103" s="19"/>
       <c r="AL103" s="19"/>
-    </row>
-    <row r="104" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM103" s="19"/>
+      <c r="AN103" s="19"/>
+      <c r="AO103" s="19"/>
+    </row>
+    <row r="104" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A104"/>
       <c r="B104" s="18"/>
       <c r="C104"/>
       <c r="D104" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E104" s="6"/>
       <c r="F104" s="6"/>
@@ -5654,13 +6249,16 @@
       <c r="AJ104" s="19"/>
       <c r="AK104" s="19"/>
       <c r="AL104" s="19"/>
-    </row>
-    <row r="105" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM104" s="19"/>
+      <c r="AN104" s="19"/>
+      <c r="AO104" s="19"/>
+    </row>
+    <row r="105" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A105"/>
       <c r="B105" s="18"/>
       <c r="C105"/>
       <c r="D105" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E105" s="6"/>
       <c r="F105" s="6"/>
@@ -5676,13 +6274,16 @@
       <c r="AJ105" s="19"/>
       <c r="AK105" s="19"/>
       <c r="AL105" s="19"/>
-    </row>
-    <row r="106" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM105" s="19"/>
+      <c r="AN105" s="19"/>
+      <c r="AO105" s="19"/>
+    </row>
+    <row r="106" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A106"/>
       <c r="B106" s="18"/>
       <c r="C106"/>
       <c r="D106" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
@@ -5698,13 +6299,16 @@
       <c r="AJ106" s="19"/>
       <c r="AK106" s="19"/>
       <c r="AL106" s="19"/>
-    </row>
-    <row r="107" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AM106" s="19"/>
+      <c r="AN106" s="19"/>
+      <c r="AO106" s="19"/>
+    </row>
+    <row r="107" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A107"/>
       <c r="B107" s="18"/>
       <c r="C107"/>
       <c r="D107" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
@@ -5720,101 +6324,108 @@
       <c r="AJ107" s="19"/>
       <c r="AK107" s="19"/>
       <c r="AL107" s="19"/>
-    </row>
-    <row r="108" spans="1:38" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A108"/>
+      <c r="AM107" s="19"/>
+      <c r="AN107" s="19"/>
+      <c r="AO107" s="19"/>
+    </row>
+    <row r="108" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="5" t="s">
+        <v>123</v>
+      </c>
       <c r="B108" s="18"/>
-      <c r="C108"/>
-      <c r="D108" s="13" t="s">
-        <v>122</v>
-      </c>
+      <c r="C108" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D108" s="13"/>
       <c r="E108" s="6"/>
       <c r="F108" s="6"/>
       <c r="G108" s="6"/>
-      <c r="H108" s="21"/>
+      <c r="H108" s="21" t="s">
+        <v>115</v>
+      </c>
       <c r="J108" s="6"/>
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
       <c r="M108" s="26"/>
-      <c r="AG108" s="19"/>
+      <c r="X108" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA108" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG108" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AH108" s="19"/>
       <c r="AI108" s="19"/>
-      <c r="AJ108" s="19"/>
+      <c r="AJ108" s="45" t="s">
+        <v>167</v>
+      </c>
       <c r="AK108" s="19"/>
       <c r="AL108" s="19"/>
-    </row>
-    <row r="109" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B109" s="18"/>
-      <c r="C109" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D109" s="13"/>
-      <c r="E109" s="6"/>
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="M109" s="26"/>
-      <c r="X109" s="42" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA109" s="45" t="s">
+      <c r="AM108" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="AG109" s="45" t="s">
-        <v>167</v>
+      <c r="AN108" s="19"/>
+      <c r="AO108" s="19"/>
+    </row>
+    <row r="109" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A109" s="50" t="s">
+        <v>224</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="M109" s="28">
+        <v>89</v>
+      </c>
+      <c r="X109" s="37" t="s">
+        <v>203</v>
+      </c>
+      <c r="AA109" s="46" t="s">
+        <v>203</v>
+      </c>
+      <c r="AG109" s="46" t="s">
+        <v>203</v>
       </c>
       <c r="AH109" s="19"/>
       <c r="AI109" s="19"/>
-      <c r="AJ109" s="45" t="s">
-        <v>167</v>
+      <c r="AJ109" s="46" t="s">
+        <v>203</v>
       </c>
       <c r="AK109" s="19"/>
       <c r="AL109" s="19"/>
-    </row>
-    <row r="110" spans="1:38" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A110" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="M110" s="28">
-        <v>89</v>
-      </c>
-      <c r="X110" s="37" t="s">
+      <c r="AM109" s="46" t="s">
         <v>203</v>
       </c>
-      <c r="AA110" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG110" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AH110" s="19"/>
-      <c r="AI110" s="19"/>
-      <c r="AJ110" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AK110" s="19"/>
-      <c r="AL110" s="19"/>
-    </row>
-    <row r="111" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AN109" s="19"/>
+      <c r="AO109" s="19"/>
+    </row>
+    <row r="110" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="48"/>
+      <c r="B110" s="18"/>
+      <c r="C110" s="16"/>
+      <c r="D110" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E110" s="6"/>
+      <c r="F110" s="6"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="21"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="26"/>
+    </row>
+    <row r="111" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A111" s="48"/>
       <c r="B111" s="18"/>
       <c r="C111" s="16"/>
       <c r="D111" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E111" s="6"/>
       <c r="F111" s="6"/>
@@ -5825,12 +6436,12 @@
       <c r="L111" s="6"/>
       <c r="M111" s="26"/>
     </row>
-    <row r="112" spans="1:38" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A112" s="48"/>
       <c r="B112" s="18"/>
       <c r="C112" s="16"/>
       <c r="D112" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E112" s="6"/>
       <c r="F112" s="6"/>
@@ -5841,12 +6452,12 @@
       <c r="L112" s="6"/>
       <c r="M112" s="26"/>
     </row>
-    <row r="113" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:39" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A113" s="48"/>
       <c r="B113" s="18"/>
       <c r="C113" s="16"/>
       <c r="D113" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E113" s="6"/>
       <c r="F113" s="6"/>
@@ -5857,38 +6468,36 @@
       <c r="L113" s="6"/>
       <c r="M113" s="26"/>
     </row>
-    <row r="114" spans="1:13" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A114" s="48"/>
       <c r="B114" s="18"/>
-      <c r="C114" s="16"/>
-      <c r="D114" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="21"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="M114" s="26"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="48"/>
-      <c r="B115" s="18"/>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="18"/>
-      <c r="G115" s="18"/>
-      <c r="H115" s="18"/>
-      <c r="I115" s="19"/>
-      <c r="J115" s="12"/>
+      <c r="C114" s="18"/>
+      <c r="D114" s="18"/>
+      <c r="E114" s="18"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="18"/>
+      <c r="H114" s="18"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="12"/>
+      <c r="K114" s="17"/>
+      <c r="L114" s="17"/>
+      <c r="M114" s="17"/>
+    </row>
+    <row r="115" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="D115" s="12"/>
+      <c r="E115" s="6"/>
+      <c r="F115" s="6"/>
+      <c r="G115" s="6"/>
+      <c r="H115" s="6"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6"/>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
       <c r="M115" s="17"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:39" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A116" s="51"/>
+      <c r="B116" s="8"/>
       <c r="D116" s="12"/>
       <c r="E116" s="6"/>
       <c r="F116" s="6"/>
@@ -5898,59 +6507,181 @@
       <c r="J116" s="6"/>
       <c r="K116" s="17"/>
       <c r="L116" s="17"/>
-      <c r="M116" s="17"/>
-    </row>
-    <row r="117" spans="1:13" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A117" s="51"/>
-      <c r="B117" s="8"/>
-      <c r="D117" s="12"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="6"/>
-      <c r="K117" s="17"/>
-      <c r="L117" s="17"/>
-      <c r="M117" s="29">
-        <f>M3+M10+M33+M45+M58+M86+M101+M110</f>
+      <c r="M116" s="29">
+        <f>M2+M9+M32+M44+M57+M85+M100+M109</f>
         <v>825</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:39" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A121" s="52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="1"/>
+    </row>
+    <row r="122" spans="1:39" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A122" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B122" s="1"/>
     </row>
-    <row r="123" spans="1:13" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A123" s="52" t="s">
-        <v>131</v>
-      </c>
-      <c r="B123" s="1"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A124" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="8"/>
+      <c r="C124" s="15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A125" s="51" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B125" s="8"/>
       <c r="C125" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="B126" s="8"/>
-      <c r="C126" s="15" t="s">
         <v>135</v>
+      </c>
+    </row>
+    <row r="127" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A127" s="49" t="s">
+        <v>290</v>
+      </c>
+      <c r="AM127" s="39" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="128" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A128" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="AM128" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="129" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A129" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="AM129" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="130" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A130" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="AM130" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="131" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A131" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="AM131" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="132" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A132" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM132" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="133" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A133" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="AM133" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="134" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A134" s="49" t="s">
+        <v>299</v>
+      </c>
+      <c r="AM134" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="135" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A135" s="49" t="s">
+        <v>293</v>
+      </c>
+      <c r="AM135" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="136" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A136" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="AM136" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="137" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A137" s="49" t="s">
+        <v>295</v>
+      </c>
+      <c r="AM137" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="138" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A138" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="AM138" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="139" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A139" s="49" t="s">
+        <v>301</v>
+      </c>
+      <c r="AM139" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="140" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A140" s="49" t="s">
+        <v>298</v>
+      </c>
+      <c r="AM140" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="141" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A141" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="AM141" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="142" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A142" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM142" s="47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="143" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A143" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="AM143" s="47" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D87" r:id="rId1" xr:uid="{DA624192-AF92-421C-B882-954902949584}"/>
+    <hyperlink ref="D86" r:id="rId1" xr:uid="{DA624192-AF92-421C-B882-954902949584}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -6358,6 +7089,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <Estado xmlns="7b6a70c9-bad9-43e8-985b-3d2ca80c98eb">En curso</Estado>
@@ -6392,15 +7132,6 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B271E1E9-4B5A-43C8-93E9-EF9A1A456C27}">
   <ds:schemaRefs>
@@ -6422,6 +7153,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64067D8-2529-40F8-873F-7DCFF29E6C0A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -6437,12 +7176,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D2ED08-240E-422E-815D-BA2AE63D0B29}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
+++ b/src/Documentacion/BIS011APPSY-SeguimientoPlanTrabajoDesaHERRIZ-v2_15-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sgantolin\BiscaytikApp_node-modules-incluido\src\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A843D364-F585-4F12-893A-83B4F61437D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{914ED54E-7022-4F55-9E76-393458268440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detalle" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="303">
   <si>
     <t>HITO</t>
   </si>
@@ -194,9 +194,6 @@
     <t>Piloto* HOME</t>
   </si>
   <si>
-    <t>SUMARY LINKS CON  (listado banners)</t>
-  </si>
-  <si>
     <t>DESARROLLO</t>
   </si>
   <si>
@@ -911,12 +908,6 @@
     <t>Imágenes servicios (restaurante)</t>
   </si>
   <si>
-    <t xml:space="preserve">ESTADO  (22-09 parta teknei) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESTADO  (29-09 parta teknei) </t>
-  </si>
-  <si>
     <t>bares</t>
   </si>
   <si>
@@ -947,13 +938,13 @@
     <t>rutas</t>
   </si>
   <si>
-    <t>eroror trasladado teams</t>
-  </si>
-  <si>
-    <t>Subida, parece que no coje última versión, desde que cambió nombres?</t>
-  </si>
-  <si>
     <t>Propuesta* DETALLE EVENTO (Base) layout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO  (29-10 parta teknei) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTADO  (22-10 parta teknei) </t>
   </si>
 </sst>
 </file>
@@ -1769,7 +1760,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AO143"/>
+  <dimension ref="A1:AO142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="49" customWidth="1"/>
@@ -1832,94 +1823,94 @@
       </c>
       <c r="K1" s="3"/>
       <c r="L1" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="N1" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="O1" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="O1" s="35" t="s">
+      <c r="P1" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="P1" s="35" t="s">
+      <c r="Q1" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="Q1" s="35" t="s">
-        <v>140</v>
-      </c>
       <c r="R1" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="S1" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="S1" s="35" t="s">
-        <v>148</v>
-      </c>
       <c r="T1" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="U1" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="U1" s="35" t="s">
-        <v>154</v>
-      </c>
       <c r="V1" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="W1" s="35" t="s">
         <v>160</v>
       </c>
-      <c r="W1" s="35" t="s">
-        <v>161</v>
-      </c>
       <c r="X1" s="35" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Y1" s="35" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Z1" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA1" s="35" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AA1" s="35" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB1" s="35" t="s">
-        <v>180</v>
-      </c>
       <c r="AC1" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD1" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="AE1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AD1" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="AE1" s="35" t="s">
-        <v>180</v>
-      </c>
       <c r="AF1" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AG1" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="AH1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AG1" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="AH1" s="35" t="s">
-        <v>180</v>
-      </c>
       <c r="AI1" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AJ1" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="AK1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AJ1" s="35" t="s">
-        <v>291</v>
-      </c>
-      <c r="AK1" s="35" t="s">
-        <v>180</v>
-      </c>
       <c r="AL1" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="AM1" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="AN1" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="AM1" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="AN1" s="35" t="s">
-        <v>180</v>
-      </c>
       <c r="AO1" s="35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
@@ -1951,28 +1942,28 @@
         <v>80</v>
       </c>
       <c r="X2" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA2" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD2" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE2" s="33"/>
       <c r="AF2" s="33"/>
       <c r="AG2" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH2" s="19"/>
       <c r="AI2" s="19"/>
       <c r="AJ2" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK2" s="19"/>
       <c r="AL2" s="19"/>
       <c r="AM2" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN2" s="19"/>
       <c r="AO2" s="19"/>
@@ -2150,7 +2141,7 @@
         <v>70</v>
       </c>
       <c r="Q9" s="36" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U9">
         <v>80</v>
@@ -2204,28 +2195,28 @@
       </c>
       <c r="M10" s="26"/>
       <c r="X10" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA10" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD10" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE10" s="33"/>
       <c r="AF10" s="33"/>
       <c r="AG10" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH10" s="19"/>
       <c r="AI10" s="19"/>
       <c r="AJ10" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK10" s="19"/>
       <c r="AL10" s="19"/>
       <c r="AM10" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN10" s="19"/>
       <c r="AO10" s="19"/>
@@ -2326,44 +2317,44 @@
       <c r="J14" s="6"/>
       <c r="M14" s="26"/>
       <c r="X14" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y14" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AA14" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB14" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AD14" s="56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="AE14" s="33"/>
       <c r="AF14" s="33"/>
       <c r="AG14" s="43" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AH14" s="19"/>
       <c r="AI14" s="19"/>
       <c r="AJ14" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AK14" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AL14" s="63" t="s">
-        <v>279</v>
-      </c>
-      <c r="AM14" s="44" t="s">
-        <v>166</v>
+        <v>278</v>
+      </c>
+      <c r="AM14" s="60" t="s">
+        <v>167</v>
       </c>
       <c r="AN14" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AO14" s="63" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2416,39 +2407,39 @@
       <c r="J16" s="6"/>
       <c r="M16" s="26"/>
       <c r="X16" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Y16" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA16" s="45" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AD16" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE16" s="33"/>
       <c r="AF16" s="33"/>
       <c r="AG16" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH16" s="19"/>
       <c r="AI16" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ16" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK16" s="19"/>
       <c r="AL16" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM16" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN16" s="19"/>
       <c r="AO16" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2520,10 +2511,10 @@
       <c r="J19" s="6"/>
       <c r="M19" s="26"/>
       <c r="S19" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U19" s="36" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD19" s="33"/>
       <c r="AE19" s="33"/>
@@ -2567,47 +2558,47 @@
         <v>95</v>
       </c>
       <c r="X20" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA20" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AB20" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AD20" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE20" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF20" s="33"/>
       <c r="AG20" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH20" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AI20" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ20" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK20" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL20" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM20" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN20" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AO20" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
@@ -2663,35 +2654,35 @@
         <v>60</v>
       </c>
       <c r="X22" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA22" s="45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AD22" s="57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AE22" s="33"/>
       <c r="AF22" s="33"/>
       <c r="AG22" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AH22" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AI22" s="19"/>
       <c r="AJ22" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AK22" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AL22" s="19"/>
       <c r="AM22" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AN22" s="19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AO22" s="19"/>
     </row>
@@ -2704,10 +2695,10 @@
       </c>
       <c r="M23" s="26"/>
       <c r="S23" t="s">
+        <v>154</v>
+      </c>
+      <c r="U23" s="36" t="s">
         <v>155</v>
-      </c>
-      <c r="U23" s="36" t="s">
-        <v>156</v>
       </c>
       <c r="AD23" s="33"/>
       <c r="AE23" s="33"/>
@@ -2755,7 +2746,7 @@
         <v>70</v>
       </c>
       <c r="Q24" s="36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S24">
         <v>80</v>
@@ -2764,7 +2755,7 @@
         <v>70</v>
       </c>
       <c r="V24" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="W24">
         <v>75</v>
@@ -2784,10 +2775,10 @@
     </row>
     <row r="25" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -2795,36 +2786,36 @@
       <c r="I25" s="9"/>
       <c r="M25" s="26"/>
       <c r="X25" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA25" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD25" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE25" s="33"/>
       <c r="AF25" s="33"/>
       <c r="AG25" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH25" s="19"/>
       <c r="AI25" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ25" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK25" s="19"/>
       <c r="AL25" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM25" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN25" s="19"/>
       <c r="AO25" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2848,13 +2839,13 @@
       </c>
       <c r="M26" s="26"/>
       <c r="S26" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U26" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W26" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X26" s="19"/>
       <c r="AD26" s="33"/>
@@ -2872,10 +2863,10 @@
     </row>
     <row r="27" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
@@ -2883,36 +2874,36 @@
       <c r="I27" s="9"/>
       <c r="M27" s="26"/>
       <c r="X27" s="42" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AA27" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD27" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE27" s="33"/>
       <c r="AF27" s="33"/>
       <c r="AG27" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH27" s="19"/>
       <c r="AI27" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ27" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK27" s="19"/>
       <c r="AL27" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM27" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN27" s="19"/>
       <c r="AO27" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2936,36 +2927,36 @@
       </c>
       <c r="M28" s="26"/>
       <c r="X28" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA28" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD28" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE28" s="33"/>
       <c r="AF28" s="33"/>
       <c r="AG28" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH28" s="19"/>
       <c r="AI28" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ28" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK28" s="19"/>
       <c r="AL28" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM28" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN28" s="19"/>
       <c r="AO28" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -2989,51 +2980,51 @@
       </c>
       <c r="M29" s="26"/>
       <c r="S29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U29" s="36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W29" s="36" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="X29" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y29" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA29" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB29" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AD29" s="58" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AE29" s="33"/>
       <c r="AF29" s="33"/>
       <c r="AG29" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH29" s="19"/>
       <c r="AI29" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ29" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK29" s="19"/>
       <c r="AL29" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM29" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN29" s="19"/>
       <c r="AO29" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3049,36 +3040,36 @@
       <c r="I30" s="9"/>
       <c r="M30" s="26"/>
       <c r="X30" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA30" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AD30" s="59" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE30" s="33"/>
       <c r="AF30" s="33"/>
       <c r="AG30" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH30" s="19"/>
       <c r="AI30" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AJ30" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK30" s="19"/>
       <c r="AL30" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AM30" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN30" s="19"/>
       <c r="AO30" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -3131,109 +3122,125 @@
       <c r="AN32" s="19"/>
       <c r="AO32" s="19"/>
     </row>
-    <row r="33" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="30" t="s">
-        <v>52</v>
+    <row r="33" spans="1:41" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="9"/>
+      <c r="H33" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J33" s="6"/>
       <c r="M33" s="26"/>
       <c r="Q33" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="AD33" s="33"/>
-      <c r="AE33" s="33"/>
-      <c r="AF33" s="33"/>
-      <c r="AG33" s="19"/>
+        <v>143</v>
+      </c>
+      <c r="S33" t="s">
+        <v>148</v>
+      </c>
+      <c r="U33" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="X33" s="37" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y33" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z33" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA33" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB33" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC33" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD33" s="60" t="s">
+        <v>207</v>
+      </c>
+      <c r="AE33" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="AF33" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="AG33" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AH33" s="19"/>
-      <c r="AI33" s="19"/>
-      <c r="AJ33" s="19"/>
+      <c r="AI33" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="AJ33" s="39" t="s">
+        <v>164</v>
+      </c>
       <c r="AK33" s="19"/>
       <c r="AL33" s="19"/>
-      <c r="AM33" s="19"/>
+      <c r="AM33" s="39" t="s">
+        <v>164</v>
+      </c>
       <c r="AN33" s="19"/>
       <c r="AO33" s="19"/>
     </row>
-    <row r="34" spans="1:41" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
-        <v>177</v>
+        <v>53</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I34" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H34" s="11"/>
+      <c r="I34" s="9"/>
       <c r="J34" s="6"/>
       <c r="M34" s="26"/>
-      <c r="Q34" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="S34" t="s">
-        <v>149</v>
-      </c>
-      <c r="U34" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="X34" s="37" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y34" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="Z34" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="AA34" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB34" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="AC34" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="AD34" s="60" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE34" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="AF34" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="AG34" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34">
+        <v>10</v>
+      </c>
+      <c r="P34">
+        <v>50</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>145</v>
+      </c>
+      <c r="T34">
+        <v>80</v>
+      </c>
+      <c r="U34">
+        <v>70</v>
+      </c>
+      <c r="W34">
+        <v>80</v>
+      </c>
+      <c r="AD34" s="33"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="19"/>
       <c r="AH34" s="19"/>
-      <c r="AI34" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="AJ34" s="39" t="s">
-        <v>165</v>
-      </c>
+      <c r="AI34" s="19"/>
+      <c r="AJ34" s="19"/>
       <c r="AK34" s="19"/>
       <c r="AL34" s="19"/>
-      <c r="AM34" s="39" t="s">
-        <v>165</v>
-      </c>
+      <c r="AM34" s="19"/>
       <c r="AN34" s="19"/>
       <c r="AO34" s="19"/>
     </row>
@@ -3251,26 +3258,14 @@
       <c r="I35" s="9"/>
       <c r="J35" s="6"/>
       <c r="M35" s="26"/>
-      <c r="N35">
-        <v>5</v>
-      </c>
       <c r="O35">
         <v>10</v>
       </c>
       <c r="P35">
         <v>50</v>
       </c>
-      <c r="Q35" t="s">
-        <v>146</v>
-      </c>
-      <c r="T35">
-        <v>80</v>
-      </c>
-      <c r="U35">
-        <v>70</v>
-      </c>
-      <c r="W35">
-        <v>80</v>
+      <c r="Q35">
+        <v>5</v>
       </c>
       <c r="AD35" s="33"/>
       <c r="AE35" s="33"/>
@@ -3285,7 +3280,7 @@
       <c r="AN35" s="19"/>
       <c r="AO35" s="19"/>
     </row>
-    <row r="36" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>55</v>
       </c>
@@ -3299,14 +3294,8 @@
       <c r="I36" s="9"/>
       <c r="J36" s="6"/>
       <c r="M36" s="26"/>
-      <c r="O36">
-        <v>10</v>
-      </c>
-      <c r="P36">
-        <v>50</v>
-      </c>
-      <c r="Q36">
-        <v>5</v>
+      <c r="Q36" t="s">
+        <v>142</v>
       </c>
       <c r="AD36" s="33"/>
       <c r="AE36" s="33"/>
@@ -3314,14 +3303,18 @@
       <c r="AG36" s="19"/>
       <c r="AH36" s="19"/>
       <c r="AI36" s="19"/>
-      <c r="AJ36" s="19"/>
+      <c r="AJ36" s="47" t="s">
+        <v>269</v>
+      </c>
       <c r="AK36" s="19"/>
       <c r="AL36" s="19"/>
-      <c r="AM36" s="19"/>
+      <c r="AM36" s="47" t="s">
+        <v>269</v>
+      </c>
       <c r="AN36" s="19"/>
       <c r="AO36" s="19"/>
     </row>
-    <row r="37" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>56</v>
       </c>
@@ -3335,8 +3328,14 @@
       <c r="I37" s="9"/>
       <c r="J37" s="6"/>
       <c r="M37" s="26"/>
-      <c r="Q37" t="s">
-        <v>143</v>
+      <c r="O37">
+        <v>20</v>
+      </c>
+      <c r="P37">
+        <v>50</v>
+      </c>
+      <c r="Q37">
+        <v>5</v>
       </c>
       <c r="AD37" s="33"/>
       <c r="AE37" s="33"/>
@@ -3344,14 +3343,10 @@
       <c r="AG37" s="19"/>
       <c r="AH37" s="19"/>
       <c r="AI37" s="19"/>
-      <c r="AJ37" s="47" t="s">
-        <v>270</v>
-      </c>
+      <c r="AJ37" s="19"/>
       <c r="AK37" s="19"/>
       <c r="AL37" s="19"/>
-      <c r="AM37" s="47" t="s">
-        <v>270</v>
-      </c>
+      <c r="AM37" s="19"/>
       <c r="AN37" s="19"/>
       <c r="AO37" s="19"/>
     </row>
@@ -3370,13 +3365,13 @@
       <c r="J38" s="6"/>
       <c r="M38" s="26"/>
       <c r="O38">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="P38">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="Q38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD38" s="33"/>
       <c r="AE38" s="33"/>
@@ -3406,10 +3401,10 @@
       <c r="J39" s="6"/>
       <c r="M39" s="26"/>
       <c r="O39">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -3427,7 +3422,7 @@
       <c r="AN39" s="19"/>
       <c r="AO39" s="19"/>
     </row>
-    <row r="40" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>59</v>
       </c>
@@ -3442,10 +3437,10 @@
       <c r="J40" s="6"/>
       <c r="M40" s="26"/>
       <c r="O40">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="P40">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -3463,210 +3458,238 @@
       <c r="AN40" s="19"/>
       <c r="AO40" s="19"/>
     </row>
-    <row r="41" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
+    <row r="41" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E41" s="6"/>
+      <c r="D41" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="9"/>
+      <c r="H41" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="J41" s="6"/>
       <c r="M41" s="26"/>
-      <c r="O41">
-        <v>40</v>
-      </c>
-      <c r="P41">
+      <c r="Q41" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="T41">
         <v>50</v>
       </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="33"/>
+      <c r="U41">
+        <v>10</v>
+      </c>
+      <c r="X41" s="41"/>
+      <c r="AA41" s="44" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB41" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="AC41" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="AD41" s="58" t="s">
+        <v>219</v>
+      </c>
       <c r="AE41" s="33"/>
-      <c r="AF41" s="33"/>
-      <c r="AG41" s="19"/>
+      <c r="AF41" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="AG41" s="47"/>
       <c r="AH41" s="19"/>
-      <c r="AI41" s="19"/>
-      <c r="AJ41" s="19"/>
+      <c r="AI41" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="AJ41" s="47"/>
       <c r="AK41" s="19"/>
-      <c r="AL41" s="19"/>
-      <c r="AM41" s="19"/>
+      <c r="AL41" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="AM41" s="47"/>
       <c r="AN41" s="19"/>
-      <c r="AO41" s="19"/>
-    </row>
-    <row r="42" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="32" t="s">
+      <c r="AO41" s="19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>62</v>
-      </c>
+      <c r="D42" s="30"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="11" t="s">
-        <v>53</v>
+      <c r="F42" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="J42" s="6"/>
       <c r="M42" s="26"/>
       <c r="Q42" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="T42">
-        <v>50</v>
-      </c>
-      <c r="U42">
-        <v>10</v>
+        <v>144</v>
+      </c>
+      <c r="U42" s="36" t="s">
+        <v>157</v>
       </c>
       <c r="X42" s="41"/>
-      <c r="AA42" s="44" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB42" s="54" t="s">
-        <v>222</v>
-      </c>
-      <c r="AC42" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="AD42" s="58" t="s">
-        <v>220</v>
-      </c>
+      <c r="AA42" s="47"/>
+      <c r="AD42" s="61"/>
       <c r="AE42" s="33"/>
-      <c r="AF42" s="33" t="s">
-        <v>221</v>
-      </c>
+      <c r="AF42" s="33"/>
       <c r="AG42" s="47"/>
       <c r="AH42" s="19"/>
-      <c r="AI42" s="19" t="s">
-        <v>221</v>
-      </c>
+      <c r="AI42" s="19"/>
       <c r="AJ42" s="47"/>
       <c r="AK42" s="19"/>
-      <c r="AL42" s="19" t="s">
-        <v>221</v>
-      </c>
+      <c r="AL42" s="19"/>
       <c r="AM42" s="47"/>
       <c r="AN42" s="19"/>
-      <c r="AO42" s="19" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="43" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="25" t="s">
+      <c r="AO42" s="19"/>
+    </row>
+    <row r="43" spans="1:41" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="B43" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D43" s="30"/>
+      <c r="C43" s="24" t="s">
+        <v>64</v>
+      </c>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M43" s="26"/>
-      <c r="Q43" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="U43" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="X43" s="41"/>
-      <c r="AA43" s="47"/>
-      <c r="AD43" s="61"/>
-      <c r="AE43" s="33"/>
-      <c r="AF43" s="33"/>
-      <c r="AG43" s="47"/>
-      <c r="AH43" s="19"/>
-      <c r="AI43" s="19"/>
-      <c r="AJ43" s="47"/>
+      <c r="M43" s="28">
+        <v>130</v>
+      </c>
+      <c r="U43">
+        <v>30</v>
+      </c>
+      <c r="W43">
+        <v>60</v>
+      </c>
+      <c r="X43" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA43" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB43" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC43" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="AD43" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE43" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="AF43" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="AG43" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="AH43" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="AI43" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="AJ43" s="44" t="s">
+        <v>271</v>
+      </c>
       <c r="AK43" s="19"/>
-      <c r="AL43" s="19"/>
-      <c r="AM43" s="47"/>
+      <c r="AL43" s="64"/>
+      <c r="AM43" s="44" t="s">
+        <v>271</v>
+      </c>
       <c r="AN43" s="19"/>
-      <c r="AO43" s="19"/>
-    </row>
-    <row r="44" spans="1:41" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="24" t="s">
+      <c r="AO43" s="64"/>
+    </row>
+    <row r="44" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A44" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="M44" s="28">
-        <v>130</v>
-      </c>
-      <c r="U44">
-        <v>30</v>
-      </c>
-      <c r="W44">
-        <v>60</v>
-      </c>
-      <c r="X44" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA44" s="44" t="s">
+      <c r="D44" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="6"/>
+      <c r="M44" s="26"/>
+      <c r="O44">
+        <v>40</v>
+      </c>
+      <c r="P44">
+        <v>70</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
+      </c>
+      <c r="R44">
+        <v>50</v>
+      </c>
+      <c r="S44" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="T44">
+        <v>50</v>
+      </c>
+      <c r="U44" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="X44" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA44" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB44" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="AB44" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC44" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="AD44" s="58" t="s">
+      <c r="AD44" s="56" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE44" s="33" t="s">
         <v>209</v>
       </c>
-      <c r="AE44" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="AF44" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="AG44" s="44" t="s">
-        <v>262</v>
+      <c r="AF44" s="33"/>
+      <c r="AG44" s="43" t="s">
+        <v>164</v>
       </c>
       <c r="AH44" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="AI44" s="19" t="s">
-        <v>263</v>
-      </c>
-      <c r="AJ44" s="44" t="s">
-        <v>272</v>
+        <v>209</v>
+      </c>
+      <c r="AI44" s="19"/>
+      <c r="AJ44" s="43" t="s">
+        <v>164</v>
       </c>
       <c r="AK44" s="19"/>
-      <c r="AL44" s="64"/>
-      <c r="AM44" s="44" t="s">
-        <v>272</v>
+      <c r="AL44" s="19"/>
+      <c r="AM44" s="43" t="s">
+        <v>164</v>
       </c>
       <c r="AN44" s="19"/>
-      <c r="AO44" s="64"/>
-    </row>
-    <row r="45" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="AO44" s="19"/>
+    </row>
+    <row r="45" spans="1:41" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A45" s="19" t="s">
         <v>66</v>
       </c>
@@ -3679,68 +3702,68 @@
         <v>40</v>
       </c>
       <c r="P45">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="Q45">
         <v>0</v>
       </c>
       <c r="R45">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="S45" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T45">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U45" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X45" s="39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA45" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AB45" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AD45" s="56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AE45" s="33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF45" s="33"/>
       <c r="AG45" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH45" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AI45" s="19"/>
       <c r="AJ45" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK45" s="19"/>
       <c r="AL45" s="19"/>
       <c r="AM45" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AN45" s="19"/>
       <c r="AO45" s="19"/>
     </row>
-    <row r="46" spans="1:41" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A46" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D46" s="19" t="s">
+    <row r="46" spans="1:41" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A46" s="33" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="33" t="s">
         <v>67</v>
       </c>
       <c r="E46" s="6"/>
       <c r="M46" s="26"/>
       <c r="O46">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="P46">
         <v>90</v>
@@ -3749,147 +3772,118 @@
         <v>0</v>
       </c>
       <c r="R46">
-        <v>100</v>
-      </c>
-      <c r="S46" s="36" t="s">
-        <v>144</v>
+        <v>70</v>
+      </c>
+      <c r="S46">
+        <v>5</v>
       </c>
       <c r="T46">
-        <v>100</v>
-      </c>
-      <c r="U46" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="X46" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA46" s="43" t="s">
-        <v>165</v>
+        <v>70</v>
+      </c>
+      <c r="U46">
+        <v>10</v>
+      </c>
+      <c r="X46" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y46" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="AA46" s="46" t="s">
+        <v>167</v>
       </c>
       <c r="AB46" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD46" s="56" t="s">
-        <v>165</v>
+        <v>185</v>
+      </c>
+      <c r="AD46" s="57" t="s">
+        <v>166</v>
       </c>
       <c r="AE46" s="33" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="AF46" s="33"/>
-      <c r="AG46" s="43" t="s">
-        <v>165</v>
+      <c r="AG46" s="45" t="s">
+        <v>166</v>
       </c>
       <c r="AH46" s="19" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="AI46" s="19"/>
-      <c r="AJ46" s="43" t="s">
-        <v>165</v>
+      <c r="AJ46" s="47" t="s">
+        <v>185</v>
       </c>
       <c r="AK46" s="19"/>
       <c r="AL46" s="19"/>
-      <c r="AM46" s="43" t="s">
-        <v>165</v>
+      <c r="AM46" s="47" t="s">
+        <v>185</v>
       </c>
       <c r="AN46" s="19"/>
       <c r="AO46" s="19"/>
     </row>
     <row r="47" spans="1:41" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A47" s="33" t="s">
-        <v>289</v>
-      </c>
-      <c r="D47" s="33" t="s">
-        <v>68</v>
-      </c>
+      <c r="A47" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="33"/>
       <c r="E47" s="6"/>
       <c r="M47" s="26"/>
-      <c r="O47">
-        <v>10</v>
-      </c>
-      <c r="P47">
-        <v>90</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>70</v>
-      </c>
-      <c r="S47">
-        <v>5</v>
-      </c>
-      <c r="T47">
-        <v>70</v>
-      </c>
-      <c r="U47">
-        <v>10</v>
-      </c>
-      <c r="X47" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y47" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="AA47" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB47" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="AD47" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE47" s="33" t="s">
-        <v>186</v>
-      </c>
+      <c r="X47" s="37"/>
+      <c r="AA47" s="46"/>
+      <c r="AD47" s="57"/>
+      <c r="AE47" s="33"/>
       <c r="AF47" s="33"/>
       <c r="AG47" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH47" s="19" t="s">
-        <v>186</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="AH47" s="19"/>
       <c r="AI47" s="19"/>
-      <c r="AJ47" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="AK47" s="19"/>
+      <c r="AJ47" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="AK47" s="63" t="s">
+        <v>272</v>
+      </c>
       <c r="AL47" s="19"/>
-      <c r="AM47" s="47" t="s">
-        <v>186</v>
-      </c>
-      <c r="AN47" s="19"/>
+      <c r="AM47" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="AN47" s="63" t="s">
+        <v>272</v>
+      </c>
       <c r="AO47" s="19"/>
     </row>
-    <row r="48" spans="1:41" ht="86.4" outlineLevel="2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>254</v>
       </c>
       <c r="D48" s="33"/>
       <c r="E48" s="6"/>
       <c r="M48" s="26"/>
-      <c r="X48" s="37"/>
-      <c r="AA48" s="46"/>
-      <c r="AD48" s="57"/>
-      <c r="AE48" s="33"/>
-      <c r="AF48" s="33"/>
+      <c r="Y48"/>
+      <c r="Z48"/>
+      <c r="AA48"/>
+      <c r="AB48"/>
+      <c r="AC48"/>
+      <c r="AD48"/>
+      <c r="AE48"/>
+      <c r="AF48"/>
       <c r="AG48" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH48" s="19"/>
       <c r="AI48" s="19"/>
       <c r="AJ48" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AK48" s="63" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AL48" s="19"/>
       <c r="AM48" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AN48" s="63" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="AO48" s="19"/>
     </row>
@@ -3909,28 +3903,24 @@
       <c r="AE49"/>
       <c r="AF49"/>
       <c r="AG49" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH49" s="19"/>
       <c r="AI49" s="19"/>
       <c r="AJ49" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AK49" s="63" t="s">
-        <v>280</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="AK49" s="19"/>
       <c r="AL49" s="19"/>
       <c r="AM49" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AN49" s="63" t="s">
-        <v>280</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="AN49" s="19"/>
       <c r="AO49" s="19"/>
     </row>
     <row r="50" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D50" s="33"/>
       <c r="E50" s="6"/>
@@ -3944,24 +3934,24 @@
       <c r="AE50"/>
       <c r="AF50"/>
       <c r="AG50" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH50" s="19"/>
       <c r="AI50" s="19"/>
       <c r="AJ50" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AK50" s="19"/>
       <c r="AL50" s="19"/>
       <c r="AM50" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AN50" s="19"/>
       <c r="AO50" s="19"/>
     </row>
     <row r="51" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D51" s="33"/>
       <c r="E51" s="6"/>
@@ -3975,24 +3965,28 @@
       <c r="AE51"/>
       <c r="AF51"/>
       <c r="AG51" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH51" s="19"/>
       <c r="AI51" s="19"/>
-      <c r="AJ51" s="43" t="s">
-        <v>285</v>
+      <c r="AJ51" s="44" t="s">
+        <v>165</v>
       </c>
       <c r="AK51" s="19"/>
-      <c r="AL51" s="19"/>
-      <c r="AM51" s="43" t="s">
-        <v>285</v>
+      <c r="AL51" s="63" t="s">
+        <v>274</v>
+      </c>
+      <c r="AM51" s="44" t="s">
+        <v>165</v>
       </c>
       <c r="AN51" s="19"/>
-      <c r="AO51" s="19"/>
+      <c r="AO51" s="63" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="52" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A52" s="32" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D52" s="33"/>
       <c r="E52" s="6"/>
@@ -4006,28 +4000,24 @@
       <c r="AE52"/>
       <c r="AF52"/>
       <c r="AG52" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH52" s="19"/>
       <c r="AI52" s="19"/>
-      <c r="AJ52" s="44" t="s">
-        <v>166</v>
+      <c r="AJ52" s="43" t="s">
+        <v>284</v>
       </c>
       <c r="AK52" s="19"/>
-      <c r="AL52" s="63" t="s">
-        <v>275</v>
-      </c>
-      <c r="AM52" s="44" t="s">
-        <v>166</v>
+      <c r="AL52" s="19"/>
+      <c r="AM52" s="43" t="s">
+        <v>284</v>
       </c>
       <c r="AN52" s="19"/>
-      <c r="AO52" s="63" t="s">
-        <v>275</v>
-      </c>
+      <c r="AO52" s="19"/>
     </row>
     <row r="53" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D53" s="33"/>
       <c r="E53" s="6"/>
@@ -4041,24 +4031,28 @@
       <c r="AE53"/>
       <c r="AF53"/>
       <c r="AG53" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH53" s="19"/>
       <c r="AI53" s="19"/>
       <c r="AJ53" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AK53" s="19"/>
-      <c r="AL53" s="19"/>
+      <c r="AL53" s="63" t="s">
+        <v>275</v>
+      </c>
       <c r="AM53" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AN53" s="19"/>
-      <c r="AO53" s="19"/>
+      <c r="AO53" s="63" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="54" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A54" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D54" s="33"/>
       <c r="E54" s="6"/>
@@ -4071,165 +4065,169 @@
       <c r="AD54"/>
       <c r="AE54"/>
       <c r="AF54"/>
-      <c r="AG54" s="45" t="s">
+      <c r="AG54" s="46" t="s">
         <v>167</v>
       </c>
       <c r="AH54" s="19"/>
       <c r="AI54" s="19"/>
       <c r="AJ54" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AK54" s="19"/>
-      <c r="AL54" s="63" t="s">
-        <v>276</v>
-      </c>
+      <c r="AL54" s="19"/>
       <c r="AM54" s="43" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AN54" s="19"/>
-      <c r="AO54" s="63" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="55" spans="1:41" ht="28.8" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A55" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D55" s="33"/>
+      <c r="AO54" s="19"/>
+    </row>
+    <row r="55" spans="1:41" ht="115.2" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A55" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>170</v>
+      </c>
       <c r="E55" s="6"/>
       <c r="M55" s="26"/>
-      <c r="Y55"/>
-      <c r="Z55"/>
-      <c r="AA55"/>
-      <c r="AB55"/>
-      <c r="AC55"/>
-      <c r="AD55"/>
-      <c r="AE55"/>
-      <c r="AF55"/>
-      <c r="AG55" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AH55" s="19"/>
+      <c r="P55">
+        <v>70</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>50</v>
+      </c>
+      <c r="S55">
+        <v>5</v>
+      </c>
+      <c r="T55">
+        <v>50</v>
+      </c>
+      <c r="U55">
+        <v>5</v>
+      </c>
+      <c r="X55" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y55" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA55" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB55" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="AD55" s="57" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE55" s="62" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF55" s="33"/>
+      <c r="AG55" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="AH55" s="55" t="s">
+        <v>240</v>
+      </c>
       <c r="AI55" s="19"/>
       <c r="AJ55" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AK55" s="19"/>
+        <v>284</v>
+      </c>
+      <c r="AK55" s="55" t="s">
+        <v>270</v>
+      </c>
       <c r="AL55" s="19"/>
       <c r="AM55" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AN55" s="19"/>
+        <v>284</v>
+      </c>
+      <c r="AN55" s="55" t="s">
+        <v>270</v>
+      </c>
       <c r="AO55" s="19"/>
     </row>
-    <row r="56" spans="1:41" ht="115.2" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A56" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="D56" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="6"/>
-      <c r="M56" s="26"/>
-      <c r="P56">
-        <v>70</v>
-      </c>
-      <c r="Q56">
-        <v>0</v>
-      </c>
-      <c r="R56">
-        <v>50</v>
-      </c>
-      <c r="S56">
-        <v>5</v>
-      </c>
-      <c r="T56">
-        <v>50</v>
-      </c>
-      <c r="U56">
-        <v>5</v>
-      </c>
-      <c r="X56" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y56" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="AA56" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB56" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="AD56" s="57" t="s">
-        <v>167</v>
-      </c>
-      <c r="AE56" s="62" t="s">
-        <v>241</v>
-      </c>
+    <row r="56" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="50" t="s">
+        <v>260</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="28">
+        <v>87</v>
+      </c>
+      <c r="W56" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD56" s="33"/>
+      <c r="AE56" s="33"/>
       <c r="AF56" s="33"/>
-      <c r="AG56" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="AH56" s="55" t="s">
-        <v>241</v>
-      </c>
+      <c r="AG56" s="19"/>
+      <c r="AH56" s="19"/>
       <c r="AI56" s="19"/>
-      <c r="AJ56" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AK56" s="55" t="s">
-        <v>271</v>
-      </c>
+      <c r="AJ56" s="19"/>
+      <c r="AK56" s="19"/>
       <c r="AL56" s="19"/>
-      <c r="AM56" s="43" t="s">
-        <v>285</v>
-      </c>
-      <c r="AN56" s="55" t="s">
-        <v>271</v>
-      </c>
+      <c r="AM56" s="19"/>
+      <c r="AN56" s="19"/>
       <c r="AO56" s="19"/>
     </row>
-    <row r="57" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>18</v>
-      </c>
+    <row r="57" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="E57" s="6"/>
       <c r="F57" s="6"/>
       <c r="G57" s="6"/>
-      <c r="H57" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H57" s="11"/>
+      <c r="I57" s="9"/>
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
-      <c r="M57" s="28">
-        <v>87</v>
-      </c>
-      <c r="W57" t="s">
-        <v>163</v>
-      </c>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
       <c r="AD57" s="33"/>
       <c r="AE57" s="33"/>
       <c r="AF57" s="33"/>
-      <c r="AG57" s="19"/>
+      <c r="AG57" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AH57" s="19"/>
       <c r="AI57" s="19"/>
-      <c r="AJ57" s="19"/>
-      <c r="AK57" s="19"/>
+      <c r="AJ57" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="AK57" s="63" t="s">
+        <v>285</v>
+      </c>
       <c r="AL57" s="19"/>
-      <c r="AM57" s="19"/>
-      <c r="AN57" s="19"/>
+      <c r="AM57" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="AN57" s="63" t="s">
+        <v>285</v>
+      </c>
       <c r="AO57" s="19"/>
     </row>
     <row r="58" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
@@ -4247,28 +4245,23 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
       <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
       <c r="AD58" s="33"/>
       <c r="AE58" s="33"/>
       <c r="AF58" s="33"/>
       <c r="AG58" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH58" s="19"/>
       <c r="AI58" s="19"/>
       <c r="AJ58" s="43" t="s">
-        <v>287</v>
-      </c>
-      <c r="AK58" s="63" t="s">
         <v>286</v>
       </c>
+      <c r="AK58" s="19"/>
       <c r="AL58" s="19"/>
       <c r="AM58" s="43" t="s">
-        <v>287</v>
-      </c>
-      <c r="AN58" s="63" t="s">
         <v>286</v>
       </c>
+      <c r="AN58" s="19"/>
       <c r="AO58" s="19"/>
     </row>
     <row r="59" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
@@ -4290,7 +4283,7 @@
       <c r="AE59" s="33"/>
       <c r="AF59" s="33"/>
       <c r="AG59" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH59" s="19"/>
       <c r="AI59" s="19"/>
@@ -4307,10 +4300,10 @@
     </row>
     <row r="60" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A60" s="32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D60" s="32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -4323,28 +4316,26 @@
       <c r="AD60" s="33"/>
       <c r="AE60" s="33"/>
       <c r="AF60" s="33"/>
-      <c r="AG60" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AG60" s="19"/>
       <c r="AH60" s="19"/>
       <c r="AI60" s="19"/>
-      <c r="AJ60" s="43" t="s">
-        <v>288</v>
+      <c r="AJ60" s="45" t="s">
+        <v>166</v>
       </c>
       <c r="AK60" s="19"/>
       <c r="AL60" s="19"/>
       <c r="AM60" s="43" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AN60" s="19"/>
       <c r="AO60" s="19"/>
     </row>
     <row r="61" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D61" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="6"/>
@@ -4357,26 +4348,28 @@
       <c r="AD61" s="33"/>
       <c r="AE61" s="33"/>
       <c r="AF61" s="33"/>
-      <c r="AG61" s="19"/>
+      <c r="AG61" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AH61" s="19"/>
       <c r="AI61" s="19"/>
       <c r="AJ61" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AK61" s="19"/>
       <c r="AL61" s="19"/>
       <c r="AM61" s="43" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AN61" s="19"/>
       <c r="AO61" s="19"/>
     </row>
     <row r="62" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="32" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="6"/>
@@ -4390,29 +4383,27 @@
       <c r="AE62" s="33"/>
       <c r="AF62" s="33"/>
       <c r="AG62" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH62" s="19"/>
       <c r="AI62" s="19"/>
-      <c r="AJ62" s="45" t="s">
-        <v>167</v>
+      <c r="AJ62" s="43" t="s">
+        <v>286</v>
       </c>
       <c r="AK62" s="19"/>
       <c r="AL62" s="19"/>
-      <c r="AM62" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN62" s="63" t="s">
-        <v>303</v>
-      </c>
+      <c r="AM62" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="AN62" s="19"/>
       <c r="AO62" s="19"/>
     </row>
     <row r="63" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A63" s="32" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="6"/>
@@ -4426,27 +4417,27 @@
       <c r="AE63" s="33"/>
       <c r="AF63" s="33"/>
       <c r="AG63" s="45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AH63" s="19"/>
       <c r="AI63" s="19"/>
-      <c r="AJ63" s="43" t="s">
-        <v>287</v>
+      <c r="AJ63" s="45" t="s">
+        <v>166</v>
       </c>
       <c r="AK63" s="19"/>
       <c r="AL63" s="19"/>
       <c r="AM63" s="43" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AN63" s="19"/>
       <c r="AO63" s="19"/>
     </row>
-    <row r="64" spans="1:41" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
       <c r="A64" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="6"/>
@@ -4459,111 +4450,90 @@
       <c r="AD64" s="33"/>
       <c r="AE64" s="33"/>
       <c r="AF64" s="33"/>
-      <c r="AG64" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AG64" s="19"/>
       <c r="AH64" s="19"/>
       <c r="AI64" s="19"/>
-      <c r="AJ64" s="45" t="s">
-        <v>167</v>
-      </c>
+      <c r="AJ64" s="19"/>
       <c r="AK64" s="19"/>
       <c r="AL64" s="19"/>
-      <c r="AM64" s="45" t="s">
+      <c r="AM64" s="19"/>
+      <c r="AN64" s="19"/>
+      <c r="AO64" s="19"/>
+    </row>
+    <row r="65" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="M65" s="26"/>
+      <c r="R65">
+        <v>10</v>
+      </c>
+      <c r="S65" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="V65">
+        <v>60</v>
+      </c>
+      <c r="W65" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="X65" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="AN64" s="63" t="s">
-        <v>304</v>
-      </c>
-      <c r="AO64" s="19"/>
-    </row>
-    <row r="65" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="D65" s="32" t="s">
-        <v>260</v>
-      </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="9"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="28"/>
-      <c r="AD65" s="33"/>
-      <c r="AE65" s="33"/>
+      <c r="Y65" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA65" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB65" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="AD65" s="60" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE65" s="33" t="s">
+        <v>186</v>
+      </c>
       <c r="AF65" s="33"/>
-      <c r="AG65" s="19"/>
-      <c r="AH65" s="19"/>
+      <c r="AG65" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="AH65" s="19" t="s">
+        <v>186</v>
+      </c>
       <c r="AI65" s="19"/>
-      <c r="AJ65" s="19"/>
-      <c r="AK65" s="19"/>
+      <c r="AJ65" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="AK65" s="19" t="s">
+        <v>186</v>
+      </c>
       <c r="AL65" s="19"/>
-      <c r="AM65" s="19"/>
-      <c r="AN65" s="19"/>
+      <c r="AM65" s="46" t="s">
+        <v>263</v>
+      </c>
+      <c r="AN65" s="19" t="s">
+        <v>186</v>
+      </c>
       <c r="AO65" s="19"/>
     </row>
-    <row r="66" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="30" t="s">
+    <row r="66" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="D66" s="30" t="s">
-        <v>71</v>
-      </c>
       <c r="M66" s="26"/>
-      <c r="R66">
-        <v>10</v>
-      </c>
-      <c r="S66" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="V66">
-        <v>60</v>
-      </c>
-      <c r="W66" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="X66" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y66" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA66" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB66" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="AD66" s="60" t="s">
-        <v>168</v>
-      </c>
-      <c r="AE66" s="33" t="s">
-        <v>187</v>
-      </c>
-      <c r="AF66" s="33"/>
-      <c r="AG66" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="AH66" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="AG66" s="19"/>
+      <c r="AH66" s="19"/>
       <c r="AI66" s="19"/>
-      <c r="AJ66" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="AK66" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="AJ66" s="19"/>
+      <c r="AK66" s="19"/>
       <c r="AL66" s="19"/>
-      <c r="AM66" s="46" t="s">
-        <v>264</v>
-      </c>
-      <c r="AN66" s="19" t="s">
-        <v>187</v>
-      </c>
+      <c r="AM66" s="19"/>
+      <c r="AN66" s="19"/>
       <c r="AO66" s="19"/>
     </row>
     <row r="67" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
@@ -4646,6 +4616,18 @@
         <v>77</v>
       </c>
       <c r="M72" s="26"/>
+      <c r="P72">
+        <v>5</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>5</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
       <c r="AG72" s="19"/>
       <c r="AH72" s="19"/>
       <c r="AI72" s="19"/>
@@ -4683,115 +4665,140 @@
       <c r="AN73" s="19"/>
       <c r="AO73" s="19"/>
     </row>
-    <row r="74" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:41" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>79</v>
+      </c>
       <c r="D74" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="M74" s="26"/>
+        <v>80</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
       <c r="P74">
         <v>5</v>
       </c>
       <c r="Q74">
         <v>0</v>
       </c>
-      <c r="R74">
-        <v>5</v>
-      </c>
-      <c r="S74">
-        <v>0</v>
-      </c>
-      <c r="AG74" s="19"/>
-      <c r="AH74" s="19"/>
-      <c r="AI74" s="19"/>
-      <c r="AJ74" s="19"/>
-      <c r="AK74" s="19"/>
-      <c r="AL74" s="19"/>
-      <c r="AM74" s="19"/>
+      <c r="S74" t="s">
+        <v>150</v>
+      </c>
+      <c r="W74" t="s">
+        <v>163</v>
+      </c>
+      <c r="X74" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA74" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AB74" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="AC74" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="AG74" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AH74" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="AI74" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="AJ74" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK74" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL74" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="AM74" s="43" t="s">
+        <v>164</v>
+      </c>
       <c r="AN74" s="19"/>
-      <c r="AO74" s="19"/>
-    </row>
-    <row r="75" spans="1:41" ht="115.2" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="23" t="s">
-        <v>305</v>
-      </c>
-      <c r="C75" s="23" t="s">
-        <v>80</v>
-      </c>
+      <c r="AO74" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="75" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="13"/>
       <c r="D75" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="E75" s="6"/>
       <c r="F75" s="6"/>
       <c r="G75" s="6"/>
-      <c r="H75" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>15</v>
-      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" s="9"/>
       <c r="K75" s="12"/>
       <c r="L75" s="12"/>
-      <c r="P75">
-        <v>5</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="S75" t="s">
+      <c r="M75" s="26"/>
+      <c r="R75">
+        <v>90</v>
+      </c>
+      <c r="S75" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="W75" t="s">
-        <v>164</v>
-      </c>
       <c r="X75" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+      <c r="Y75" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="AA75" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB75" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC75" s="19" t="s">
-        <v>212</v>
+        <v>164</v>
+      </c>
+      <c r="AB75" s="55" t="s">
+        <v>234</v>
       </c>
       <c r="AG75" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH75" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="AI75" s="19" t="s">
-        <v>212</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AI75" s="19"/>
       <c r="AJ75" s="43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AK75" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="AL75" s="19" t="s">
-        <v>212</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="AL75" s="19"/>
       <c r="AM75" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AN75" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="AO75" s="19" t="s">
-        <v>212</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AN75" s="19"/>
+      <c r="AO75" s="19"/>
     </row>
     <row r="76" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="C76" s="13"/>
       <c r="D76" s="13" t="s">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -4801,53 +4808,71 @@
       <c r="K76" s="12"/>
       <c r="L76" s="12"/>
       <c r="M76" s="26"/>
+      <c r="P76">
+        <v>10</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
       <c r="R76">
-        <v>90</v>
-      </c>
-      <c r="S76" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="X76" s="38" t="s">
-        <v>166</v>
+        <v>30</v>
+      </c>
+      <c r="S76">
+        <v>5</v>
+      </c>
+      <c r="X76" s="42" t="s">
+        <v>189</v>
       </c>
       <c r="Y76" s="19" t="s">
-        <v>183</v>
+        <v>188</v>
+      </c>
+      <c r="Z76" s="19" t="s">
+        <v>187</v>
       </c>
       <c r="AA76" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB76" s="55" t="s">
-        <v>235</v>
+        <v>164</v>
+      </c>
+      <c r="AB76" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="AC76" s="19" t="s">
+        <v>187</v>
       </c>
       <c r="AG76" s="43" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="AH76" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="AI76" s="19"/>
+        <v>238</v>
+      </c>
+      <c r="AI76" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="AJ76" s="43" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="AK76" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="AL76" s="19"/>
+        <v>238</v>
+      </c>
+      <c r="AL76" s="19" t="s">
+        <v>187</v>
+      </c>
       <c r="AM76" s="43" t="s">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="AN76" s="55" t="s">
-        <v>235</v>
-      </c>
-      <c r="AO76" s="19"/>
-    </row>
-    <row r="77" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+      <c r="AO76" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="77" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="C77" s="13"/>
       <c r="D77" s="13" t="s">
-        <v>191</v>
+        <v>82</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -4858,64 +4883,40 @@
       <c r="L77" s="12"/>
       <c r="M77" s="26"/>
       <c r="P77">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="Q77">
         <v>0</v>
       </c>
       <c r="R77">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="S77">
         <v>5</v>
       </c>
-      <c r="X77" s="42" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y77" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="Z77" s="19" t="s">
-        <v>188</v>
+      <c r="X77" s="39" t="s">
+        <v>164</v>
       </c>
       <c r="AA77" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB77" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="AC77" s="19" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="AG77" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="AH77" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="AI77" s="19" t="s">
-        <v>188</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AH77" s="19"/>
+      <c r="AI77" s="19"/>
       <c r="AJ77" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="AK77" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="AL77" s="19" t="s">
-        <v>188</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="AK77" s="19"/>
+      <c r="AL77" s="19"/>
       <c r="AM77" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="AN77" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="AO77" s="19" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="78" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="AN77" s="19"/>
+      <c r="AO77" s="19"/>
+    </row>
+    <row r="78" spans="1:41" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
         <v>83</v>
       </c>
@@ -4932,40 +4933,52 @@
       <c r="L78" s="12"/>
       <c r="M78" s="26"/>
       <c r="P78">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="Q78">
         <v>0</v>
       </c>
       <c r="R78">
-        <v>40</v>
-      </c>
-      <c r="S78">
-        <v>5</v>
-      </c>
-      <c r="X78" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="S78" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="X78" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="AA78" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AG78" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AH78" s="19"/>
+      <c r="Y78" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="AA78" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="AB78" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="AG78" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH78" s="19" t="s">
+        <v>212</v>
+      </c>
       <c r="AI78" s="19"/>
-      <c r="AJ78" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AK78" s="19"/>
+      <c r="AJ78" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="AK78" s="19" t="s">
+        <v>212</v>
+      </c>
       <c r="AL78" s="19"/>
-      <c r="AM78" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AN78" s="19"/>
+      <c r="AM78" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="AN78" s="19" t="s">
+        <v>212</v>
+      </c>
       <c r="AO78" s="19"/>
     </row>
-    <row r="79" spans="1:41" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>84</v>
       </c>
@@ -4981,73 +4994,47 @@
       <c r="K79" s="12"/>
       <c r="L79" s="12"/>
       <c r="M79" s="26"/>
-      <c r="P79">
-        <v>5</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
       <c r="R79">
-        <v>30</v>
-      </c>
-      <c r="S79" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="X79" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y79" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="AA79" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AB79" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="AG79" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AH79" s="19" t="s">
-        <v>213</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="S79">
+        <v>10</v>
+      </c>
+      <c r="AG79" s="19"/>
+      <c r="AH79" s="19"/>
       <c r="AI79" s="19"/>
-      <c r="AJ79" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AK79" s="19" t="s">
-        <v>213</v>
-      </c>
+      <c r="AJ79" s="19"/>
+      <c r="AK79" s="19"/>
       <c r="AL79" s="19"/>
-      <c r="AM79" s="44" t="s">
-        <v>236</v>
-      </c>
-      <c r="AN79" s="19" t="s">
-        <v>213</v>
-      </c>
+      <c r="AM79" s="19"/>
+      <c r="AN79" s="19"/>
       <c r="AO79" s="19"/>
     </row>
     <row r="80" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C80" s="13"/>
       <c r="D80" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
       <c r="G80" s="6"/>
       <c r="H80" s="6"/>
-      <c r="I80" s="9"/>
-      <c r="K80" s="12"/>
-      <c r="L80" s="12"/>
+      <c r="J80" s="9"/>
       <c r="M80" s="26"/>
+      <c r="P80">
+        <v>5</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
       <c r="R80">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="S80">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AG80" s="19"/>
       <c r="AH80" s="19"/>
@@ -5059,13 +5046,13 @@
       <c r="AN80" s="19"/>
       <c r="AO80" s="19"/>
     </row>
-    <row r="81" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:41" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C81" s="13"/>
       <c r="D81" s="13" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -5073,29 +5060,53 @@
       <c r="H81" s="6"/>
       <c r="J81" s="9"/>
       <c r="M81" s="26"/>
-      <c r="P81">
-        <v>5</v>
-      </c>
-      <c r="Q81">
-        <v>0</v>
-      </c>
-      <c r="R81">
-        <v>10</v>
-      </c>
-      <c r="S81">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="19"/>
-      <c r="AH81" s="19"/>
-      <c r="AI81" s="19"/>
-      <c r="AJ81" s="19"/>
-      <c r="AK81" s="19"/>
-      <c r="AL81" s="19"/>
-      <c r="AM81" s="19"/>
-      <c r="AN81" s="19"/>
-      <c r="AO81" s="19"/>
-    </row>
-    <row r="82" spans="1:41" ht="72" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="X81" s="37" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y81" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z81" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AA81" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="AB81" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="AC81" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG81" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="AH81" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="AI81" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AJ81" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="AK81" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="AL81" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="AM81" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="AN81" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="AO81" s="19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="82" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
         <v>86</v>
       </c>
@@ -5109,53 +5120,56 @@
       <c r="H82" s="6"/>
       <c r="J82" s="9"/>
       <c r="M82" s="26"/>
+      <c r="S82" s="36" t="s">
+        <v>143</v>
+      </c>
       <c r="X82" s="37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y82" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Z82" s="19" t="s">
         <v>194</v>
       </c>
       <c r="AA82" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AB82" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AC82" s="19" t="s">
         <v>194</v>
       </c>
       <c r="AG82" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AH82" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI82" s="19" t="s">
         <v>194</v>
       </c>
       <c r="AJ82" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AK82" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL82" s="19" t="s">
         <v>194</v>
       </c>
       <c r="AM82" s="46" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AN82" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AO82" s="19" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="83" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:41" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>87</v>
       </c>
@@ -5170,149 +5184,140 @@
       <c r="J83" s="9"/>
       <c r="M83" s="26"/>
       <c r="S83" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="X83" s="37" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="Y83" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="Z83" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AA83" s="46" t="s">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="AB83" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AC83" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AG83" s="46" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="AH83" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AI83" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AJ83" s="46" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="AK83" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL83" s="19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="AM83" s="46" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
       <c r="AN83" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AO83" s="19" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="84" spans="1:41" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="50">
+        <v>4</v>
+      </c>
+      <c r="B84" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="J84" s="9"/>
-      <c r="M84" s="26"/>
-      <c r="S84" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="X84" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="Y84" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z84" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA84" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="AB84" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AC84" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AG84" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="AH84" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AI84" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AJ84" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="AK84" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL84" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="AM84" s="46" t="s">
-        <v>242</v>
-      </c>
-      <c r="AN84" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="AO84" s="19" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="85" spans="1:41" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="50">
-        <v>4</v>
-      </c>
-      <c r="B85" s="16" t="s">
+      <c r="C84" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="M84" s="28">
+        <v>106</v>
+      </c>
+      <c r="AG84" s="19"/>
+      <c r="AH84" s="19"/>
+      <c r="AI84" s="19"/>
+      <c r="AJ84" s="19"/>
+      <c r="AK84" s="19"/>
+      <c r="AL84" s="19"/>
+      <c r="AM84" s="19"/>
+      <c r="AN84" s="19"/>
+      <c r="AO84" s="19"/>
+    </row>
+    <row r="85" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="C85" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="M85" s="28">
-        <v>106</v>
-      </c>
-      <c r="AG85" s="19"/>
+      <c r="E85" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="J85" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="M85" s="26"/>
+      <c r="P85">
+        <v>20</v>
+      </c>
+      <c r="Q85">
+        <v>5</v>
+      </c>
+      <c r="R85">
+        <v>50</v>
+      </c>
+      <c r="S85">
+        <v>10</v>
+      </c>
+      <c r="X85" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA85" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG85" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AH85" s="19"/>
       <c r="AI85" s="19"/>
-      <c r="AJ85" s="19"/>
+      <c r="AJ85" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AK85" s="19"/>
       <c r="AL85" s="19"/>
-      <c r="AM85" s="19"/>
+      <c r="AM85" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AN85" s="19"/>
       <c r="AO85" s="19"/>
     </row>
-    <row r="86" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A86" s="49" t="s">
         <v>216</v>
       </c>
       <c r="C86" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="D86" s="34" t="s">
-        <v>91</v>
+      <c r="D86" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>18</v>
@@ -5321,62 +5326,88 @@
       <c r="G86" s="6"/>
       <c r="H86" s="6"/>
       <c r="J86" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M86" s="26"/>
       <c r="P86">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R86">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="S86">
-        <v>10</v>
-      </c>
-      <c r="X86" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="X86" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="AA86" s="45" t="s">
+      <c r="Y86" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="Z86" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA86" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="AG86" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AH86" s="19"/>
-      <c r="AI86" s="19"/>
-      <c r="AJ86" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK86" s="19"/>
-      <c r="AL86" s="19"/>
-      <c r="AM86" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN86" s="19"/>
-      <c r="AO86" s="19"/>
-    </row>
-    <row r="87" spans="1:41" ht="57.6" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="C87" s="27" t="s">
-        <v>217</v>
+      <c r="AB86" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC86" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="AG86" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="AH86" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI86" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="AJ86" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="AK86" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL86" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="AM86" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="AN86" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="AO86" s="19" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="87" spans="1:41" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="J87" s="14" t="s">
-        <v>94</v>
-      </c>
+      <c r="H87" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J87" s="6"/>
+      <c r="K87" s="12"/>
+      <c r="L87" s="12"/>
       <c r="M87" s="26"/>
       <c r="P87">
         <v>10</v>
@@ -5391,60 +5422,49 @@
         <v>0</v>
       </c>
       <c r="X87" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y87" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="Z87" s="19" t="s">
         <v>196</v>
       </c>
       <c r="AA87" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AB87" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AC87" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="AG87" s="43" t="s">
-        <v>266</v>
+        <v>229</v>
+      </c>
+      <c r="AG87" s="45" t="s">
+        <v>236</v>
       </c>
       <c r="AH87" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AI87" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="AJ87" s="43" t="s">
-        <v>266</v>
+        <v>229</v>
+      </c>
+      <c r="AI87" s="19"/>
+      <c r="AJ87" s="45" t="s">
+        <v>236</v>
       </c>
       <c r="AK87" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AL87" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="AM87" s="43" t="s">
-        <v>266</v>
+        <v>229</v>
+      </c>
+      <c r="AL87" s="19"/>
+      <c r="AM87" s="45" t="s">
+        <v>236</v>
       </c>
       <c r="AN87" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="AO87" s="19" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="88" spans="1:41" ht="100.8" outlineLevel="1" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+      <c r="AO87" s="19"/>
+    </row>
+    <row r="88" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A88" s="30" t="s">
-        <v>95</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="B88" s="15"/>
       <c r="C88" s="23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D88" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>18</v>
@@ -5452,65 +5472,46 @@
       <c r="F88" s="6"/>
       <c r="G88" s="6"/>
       <c r="H88" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="J88" s="6"/>
-      <c r="K88" s="12"/>
-      <c r="L88" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="I88" s="6"/>
+      <c r="J88" s="12"/>
       <c r="M88" s="26"/>
-      <c r="P88">
-        <v>10</v>
-      </c>
-      <c r="Q88">
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <v>10</v>
-      </c>
-      <c r="S88">
-        <v>0</v>
-      </c>
       <c r="X88" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y88" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AA88" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AB88" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="AG88" s="45" t="s">
-        <v>237</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="AG88" s="19"/>
       <c r="AH88" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AI88" s="19"/>
-      <c r="AJ88" s="45" t="s">
-        <v>237</v>
-      </c>
+      <c r="AJ88" s="19"/>
       <c r="AK88" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AL88" s="19"/>
-      <c r="AM88" s="45" t="s">
-        <v>237</v>
-      </c>
+      <c r="AM88" s="19"/>
       <c r="AN88" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AO88" s="19"/>
     </row>
     <row r="89" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A89" s="30" t="s">
-        <v>97</v>
+        <v>242</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="23" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="D89" s="13" t="s">
         <v>98</v>
@@ -5518,149 +5519,157 @@
       <c r="E89" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="10"/>
       <c r="H89" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="I89" s="6"/>
-      <c r="J89" s="12"/>
+        <v>52</v>
+      </c>
+      <c r="I89" s="15"/>
+      <c r="J89" s="10"/>
+      <c r="K89" s="13"/>
+      <c r="L89" s="13"/>
       <c r="M89" s="26"/>
-      <c r="X89" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y89" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA89" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB89" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AG89" s="19"/>
-      <c r="AH89" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AI89" s="19"/>
-      <c r="AJ89" s="19"/>
-      <c r="AK89" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AL89" s="19"/>
-      <c r="AM89" s="19"/>
-      <c r="AN89" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="AO89" s="19"/>
-    </row>
-    <row r="90" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="X89" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA89" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC89" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG89" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH89" s="19"/>
+      <c r="AI89" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="AJ89" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="AK89" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL89" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="AM89" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="AN89" s="63" t="s">
+        <v>282</v>
+      </c>
+      <c r="AO89" s="19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="90" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A90" s="30" t="s">
         <v>243</v>
       </c>
       <c r="B90" s="15"/>
-      <c r="C90" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="C90" s="23"/>
+      <c r="D90" s="13"/>
+      <c r="E90" s="6"/>
       <c r="F90" s="10"/>
       <c r="G90" s="10"/>
-      <c r="H90" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H90" s="11"/>
       <c r="I90" s="15"/>
       <c r="J90" s="10"/>
       <c r="K90" s="13"/>
       <c r="L90" s="13"/>
       <c r="M90" s="26"/>
       <c r="X90" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA90" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AG90" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AH90" s="19"/>
+      <c r="AI90" s="19"/>
+      <c r="AJ90" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK90" s="19"/>
+      <c r="AL90" s="19"/>
+      <c r="AM90" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AN90" s="19"/>
+      <c r="AO90" s="19"/>
+    </row>
+    <row r="91" spans="1:41" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="15"/>
+      <c r="C91" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D91" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="12"/>
+      <c r="L91" s="12"/>
+      <c r="M91" s="26"/>
+      <c r="X91" s="37" t="s">
+        <v>167</v>
+      </c>
+      <c r="Y91" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="AA91" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AB91" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AG91" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="AA90" s="44" t="s">
+      <c r="AH91" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="AI91" s="19"/>
+      <c r="AJ91" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="AC90" s="19" t="s">
+      <c r="AK91" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="AG90" s="44" t="s">
+      <c r="AL91" s="19"/>
+      <c r="AM91" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="AH90" s="19"/>
-      <c r="AI90" s="19" t="s">
+      <c r="AN91" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="AJ90" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="AK90" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="AL90" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="AM90" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="AN90" s="63" t="s">
-        <v>283</v>
-      </c>
-      <c r="AO90" s="19" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="91" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="B91" s="15"/>
-      <c r="C91" s="23"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="6"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="10"/>
-      <c r="H91" s="11"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="10"/>
-      <c r="K91" s="13"/>
-      <c r="L91" s="13"/>
-      <c r="M91" s="26"/>
-      <c r="X91" s="38" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA91" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AG91" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AH91" s="19"/>
-      <c r="AI91" s="19"/>
-      <c r="AJ91" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK91" s="19"/>
-      <c r="AL91" s="19"/>
-      <c r="AM91" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AN91" s="19"/>
       <c r="AO91" s="19"/>
     </row>
-    <row r="92" spans="1:41" ht="86.4" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:41" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A92" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D92" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>18</v>
@@ -5668,228 +5677,238 @@
       <c r="F92" s="6"/>
       <c r="G92" s="6"/>
       <c r="H92" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
-      <c r="K92" s="12"/>
-      <c r="L92" s="12"/>
+      <c r="K92" s="17"/>
+      <c r="L92" s="17"/>
       <c r="M92" s="26"/>
       <c r="X92" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y92" s="19" t="s">
-        <v>182</v>
+        <v>196</v>
+      </c>
+      <c r="Z92" s="19" t="s">
+        <v>197</v>
       </c>
       <c r="AA92" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB92" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AG92" s="45" t="s">
         <v>167</v>
       </c>
-      <c r="AH92" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AI92" s="19"/>
-      <c r="AJ92" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AK92" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AL92" s="19"/>
-      <c r="AM92" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AN92" s="19" t="s">
-        <v>228</v>
-      </c>
-      <c r="AO92" s="19"/>
-    </row>
-    <row r="93" spans="1:41" ht="63" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="B93" s="15"/>
-      <c r="C93" s="23" t="s">
-        <v>102</v>
-      </c>
+      <c r="AB92" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AC92" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AG92" s="19"/>
+      <c r="AH92" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AI92" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AJ92" s="19"/>
+      <c r="AK92" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AL92" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="AM92" s="19"/>
+      <c r="AN92" s="53">
+        <v>46309</v>
+      </c>
+      <c r="AO92" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" s="18"/>
       <c r="D93" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>18</v>
-      </c>
+      <c r="E93" s="6"/>
       <c r="F93" s="6"/>
       <c r="G93" s="6"/>
-      <c r="H93" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H93" s="6"/>
       <c r="I93" s="6"/>
       <c r="J93" s="6"/>
       <c r="K93" s="17"/>
       <c r="L93" s="17"/>
       <c r="M93" s="26"/>
       <c r="X93" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y93" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="Z93" s="19" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="AA93" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB93" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AC93" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AG93" s="19"/>
-      <c r="AH93" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AI93" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AJ93" s="19"/>
-      <c r="AK93" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AL93" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="AM93" s="19"/>
-      <c r="AN93" s="53">
-        <v>46309</v>
-      </c>
-      <c r="AO93" s="19" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="94" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="AG93" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AH93" s="19"/>
+      <c r="AI93" s="19"/>
+      <c r="AJ93" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK93" s="19"/>
+      <c r="AL93" s="19"/>
+      <c r="AM93" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN93" s="19"/>
+      <c r="AO93" s="19"/>
+    </row>
+    <row r="94" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="B94" s="18"/>
+      <c r="C94" s="23" t="s">
+        <v>104</v>
+      </c>
       <c r="D94" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="6"/>
+        <v>105</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I94" s="19"/>
+      <c r="J94" s="12"/>
       <c r="K94" s="17"/>
       <c r="L94" s="17"/>
       <c r="M94" s="26"/>
       <c r="X94" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="Y94" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z94" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="AA94" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="AB94" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AC94" s="19" t="s">
+        <v>199</v>
       </c>
       <c r="AG94" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AH94" s="19"/>
-      <c r="AI94" s="19"/>
+        <v>167</v>
+      </c>
+      <c r="AH94" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AI94" s="19" t="s">
+        <v>199</v>
+      </c>
       <c r="AJ94" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AK94" s="19"/>
-      <c r="AL94" s="19"/>
+        <v>167</v>
+      </c>
+      <c r="AK94" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AL94" s="19" t="s">
+        <v>199</v>
+      </c>
       <c r="AM94" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AN94" s="19"/>
-      <c r="AO94" s="19"/>
+        <v>167</v>
+      </c>
+      <c r="AN94" s="53">
+        <v>46314</v>
+      </c>
+      <c r="AO94" s="19" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="95" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A95" s="30" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C95" s="23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="E95" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E95" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F95" s="12"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="I95" s="19"/>
-      <c r="J95" s="12"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J95" s="6"/>
       <c r="K95" s="17"/>
       <c r="L95" s="17"/>
       <c r="M95" s="26"/>
       <c r="X95" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Y95" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z95" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="Z95" s="19" t="s">
-        <v>200</v>
-      </c>
       <c r="AA95" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB95" s="53">
-        <v>46314</v>
+        <v>167</v>
+      </c>
+      <c r="AB95" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="AC95" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG95" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AH95" s="53">
-        <v>46314</v>
+        <v>167</v>
+      </c>
+      <c r="AH95" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="AI95" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AJ95" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AK95" s="53">
-        <v>46314</v>
+        <v>167</v>
+      </c>
+      <c r="AK95" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="AL95" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AM95" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AN95" s="53">
-        <v>46314</v>
+        <v>167</v>
+      </c>
+      <c r="AN95" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="AO95" s="19" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="96" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="C96" s="23" t="s">
-        <v>107</v>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="96" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>18</v>
@@ -5897,124 +5916,91 @@
       <c r="F96" s="6"/>
       <c r="G96" s="6"/>
       <c r="H96" s="11" t="s">
-        <v>53</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I96" s="6"/>
       <c r="J96" s="6"/>
-      <c r="K96" s="17"/>
-      <c r="L96" s="17"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
       <c r="M96" s="26"/>
+      <c r="P96">
+        <v>5</v>
+      </c>
+      <c r="S96" t="s">
+        <v>149</v>
+      </c>
       <c r="X96" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y96" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="Z96" s="19" t="s">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="AA96" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AB96" s="19" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="AC96" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AG96" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AH96" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AG96" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="AH96" s="19"/>
       <c r="AI96" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AJ96" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AK96" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="AJ96" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK96" s="19"/>
       <c r="AL96" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="AM96" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AN96" s="19" t="s">
-        <v>199</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="AM96" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="AN96" s="19"/>
       <c r="AO96" s="19" t="s">
-        <v>200</v>
+        <v>248</v>
       </c>
     </row>
     <row r="97" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A97" s="5" t="s">
-        <v>109</v>
+        <v>277</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>18</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="D97" s="13"/>
+      <c r="E97" s="6"/>
       <c r="F97" s="6"/>
       <c r="G97" s="6"/>
-      <c r="H97" s="11" t="s">
-        <v>53</v>
-      </c>
+      <c r="H97" s="11"/>
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
       <c r="M97" s="26"/>
-      <c r="P97">
-        <v>5</v>
-      </c>
-      <c r="S97" t="s">
-        <v>150</v>
-      </c>
-      <c r="X97" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA97" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB97" s="19" t="s">
-        <v>225</v>
-      </c>
-      <c r="AC97" s="19" t="s">
-        <v>226</v>
-      </c>
-      <c r="AG97" s="43" t="s">
-        <v>245</v>
-      </c>
+      <c r="X97" s="37"/>
+      <c r="AA97" s="46"/>
+      <c r="AG97" s="43"/>
       <c r="AH97" s="19"/>
-      <c r="AI97" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AJ97" s="43" t="s">
-        <v>165</v>
+      <c r="AI97" s="19"/>
+      <c r="AJ97" s="47" t="s">
+        <v>280</v>
       </c>
       <c r="AK97" s="19"/>
-      <c r="AL97" s="19" t="s">
-        <v>249</v>
-      </c>
-      <c r="AM97" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="AN97" s="19"/>
-      <c r="AO97" s="19" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="98" spans="1:41" ht="28.8" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="AL97" s="19"/>
+      <c r="AM97" s="60" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN97" s="63" t="s">
+        <v>281</v>
+      </c>
+      <c r="AO97" s="19"/>
+    </row>
+    <row r="98" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C98" s="16" t="s">
         <v>268</v>
@@ -6034,172 +6020,164 @@
       <c r="AG98" s="43"/>
       <c r="AH98" s="19"/>
       <c r="AI98" s="19"/>
-      <c r="AJ98" s="47" t="s">
+      <c r="AJ98" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="AK98" s="63" t="s">
         <v>281</v>
       </c>
-      <c r="AK98" s="19"/>
       <c r="AL98" s="19"/>
-      <c r="AM98" s="47" t="s">
+      <c r="AM98" s="60" t="s">
+        <v>167</v>
+      </c>
+      <c r="AN98" s="63" t="s">
         <v>281</v>
       </c>
-      <c r="AN98" s="19"/>
       <c r="AO98" s="19"/>
     </row>
-    <row r="99" spans="1:41" ht="43.2" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>269</v>
-      </c>
-      <c r="D99" s="13"/>
-      <c r="E99" s="6"/>
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="11"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
-      <c r="M99" s="26"/>
-      <c r="X99" s="37"/>
-      <c r="AA99" s="46"/>
-      <c r="AG99" s="43"/>
+    <row r="99" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A99" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="M99" s="28">
+        <v>156</v>
+      </c>
+      <c r="X99" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA99" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="AG99" s="46" t="s">
+        <v>202</v>
+      </c>
       <c r="AH99" s="19"/>
       <c r="AI99" s="19"/>
-      <c r="AJ99" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AK99" s="63" t="s">
-        <v>282</v>
-      </c>
+      <c r="AJ99" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="AK99" s="19"/>
       <c r="AL99" s="19"/>
-      <c r="AM99" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="AN99" s="63" t="s">
-        <v>282</v>
-      </c>
+      <c r="AM99" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="AN99" s="19"/>
       <c r="AO99" s="19"/>
     </row>
-    <row r="100" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A100" s="50" t="s">
-        <v>223</v>
-      </c>
-      <c r="B100" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C100" s="24" t="s">
+    <row r="100" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="M100" s="28">
-        <v>156</v>
-      </c>
+      <c r="B100" s="18"/>
+      <c r="C100" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="26"/>
       <c r="X100" s="37" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="AA100" s="46" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="AG100" s="46" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="AH100" s="19"/>
       <c r="AI100" s="19"/>
       <c r="AJ100" s="46" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="AK100" s="19"/>
       <c r="AL100" s="19"/>
       <c r="AM100" s="46" t="s">
-        <v>203</v>
+        <v>167</v>
       </c>
       <c r="AN100" s="19"/>
       <c r="AO100" s="19"/>
     </row>
     <row r="101" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A101" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B101" s="18"/>
       <c r="C101" s="16" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E101" s="6"/>
       <c r="F101" s="6"/>
       <c r="G101" s="6"/>
       <c r="H101" s="21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J101" s="6"/>
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
       <c r="M101" s="26"/>
       <c r="X101" s="37" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AA101" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG101" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AH101" s="19"/>
       <c r="AI101" s="19"/>
       <c r="AJ101" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AK101" s="19"/>
       <c r="AL101" s="19"/>
       <c r="AM101" s="46" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AN101" s="19"/>
       <c r="AO101" s="19"/>
     </row>
     <row r="102" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
-        <v>116</v>
-      </c>
+      <c r="A102"/>
       <c r="B102" s="18"/>
-      <c r="C102" s="16" t="s">
-        <v>116</v>
-      </c>
+      <c r="C102"/>
       <c r="D102" s="13" t="s">
         <v>117</v>
       </c>
       <c r="E102" s="6"/>
       <c r="F102" s="6"/>
       <c r="G102" s="6"/>
-      <c r="H102" s="21" t="s">
-        <v>115</v>
-      </c>
+      <c r="H102" s="21"/>
       <c r="J102" s="6"/>
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
       <c r="M102" s="26"/>
-      <c r="X102" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="AA102" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="AG102" s="46" t="s">
-        <v>168</v>
-      </c>
+      <c r="AG102" s="19"/>
       <c r="AH102" s="19"/>
       <c r="AI102" s="19"/>
-      <c r="AJ102" s="46" t="s">
-        <v>168</v>
-      </c>
+      <c r="AJ102" s="19"/>
       <c r="AK102" s="19"/>
       <c r="AL102" s="19"/>
-      <c r="AM102" s="46" t="s">
-        <v>168</v>
-      </c>
+      <c r="AM102" s="19"/>
       <c r="AN102" s="19"/>
       <c r="AO102" s="19"/>
     </row>
@@ -6278,7 +6256,7 @@
       <c r="AN105" s="19"/>
       <c r="AO105" s="19"/>
     </row>
-    <row r="106" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A106"/>
       <c r="B106" s="18"/>
       <c r="C106"/>
@@ -6303,106 +6281,97 @@
       <c r="AN106" s="19"/>
       <c r="AO106" s="19"/>
     </row>
-    <row r="107" spans="1:41" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A107"/>
+    <row r="107" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="5" t="s">
+        <v>122</v>
+      </c>
       <c r="B107" s="18"/>
-      <c r="C107"/>
-      <c r="D107" s="13" t="s">
+      <c r="C107" s="16" t="s">
         <v>122</v>
       </c>
+      <c r="D107" s="13"/>
       <c r="E107" s="6"/>
       <c r="F107" s="6"/>
       <c r="G107" s="6"/>
-      <c r="H107" s="21"/>
+      <c r="H107" s="21" t="s">
+        <v>114</v>
+      </c>
       <c r="J107" s="6"/>
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
       <c r="M107" s="26"/>
-      <c r="AG107" s="19"/>
+      <c r="X107" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="AA107" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="AG107" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AH107" s="19"/>
       <c r="AI107" s="19"/>
-      <c r="AJ107" s="19"/>
+      <c r="AJ107" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AK107" s="19"/>
       <c r="AL107" s="19"/>
-      <c r="AM107" s="19"/>
+      <c r="AM107" s="45" t="s">
+        <v>166</v>
+      </c>
       <c r="AN107" s="19"/>
       <c r="AO107" s="19"/>
     </row>
-    <row r="108" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="5" t="s">
+    <row r="108" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A108" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="B108" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B108" s="18"/>
-      <c r="C108" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="D108" s="13"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="J108" s="6"/>
-      <c r="K108" s="6"/>
-      <c r="L108" s="6"/>
-      <c r="M108" s="26"/>
-      <c r="X108" s="42" t="s">
+      <c r="C108" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="M108" s="28">
+        <v>89</v>
+      </c>
+      <c r="X108" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="AA108" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="AG108" s="45" t="s">
-        <v>167</v>
+      <c r="AA108" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="AG108" s="46" t="s">
+        <v>202</v>
       </c>
       <c r="AH108" s="19"/>
       <c r="AI108" s="19"/>
-      <c r="AJ108" s="45" t="s">
-        <v>167</v>
+      <c r="AJ108" s="46" t="s">
+        <v>202</v>
       </c>
       <c r="AK108" s="19"/>
       <c r="AL108" s="19"/>
-      <c r="AM108" s="45" t="s">
-        <v>167</v>
+      <c r="AM108" s="46" t="s">
+        <v>202</v>
       </c>
       <c r="AN108" s="19"/>
       <c r="AO108" s="19"/>
     </row>
-    <row r="109" spans="1:41" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A109" s="50" t="s">
-        <v>224</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="C109" s="24" t="s">
+    <row r="109" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="48"/>
+      <c r="B109" s="18"/>
+      <c r="C109" s="16"/>
+      <c r="D109" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="M109" s="28">
-        <v>89</v>
-      </c>
-      <c r="X109" s="37" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA109" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AG109" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AH109" s="19"/>
-      <c r="AI109" s="19"/>
-      <c r="AJ109" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AK109" s="19"/>
-      <c r="AL109" s="19"/>
-      <c r="AM109" s="46" t="s">
-        <v>203</v>
-      </c>
-      <c r="AN109" s="19"/>
-      <c r="AO109" s="19"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="6"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="21"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="26"/>
     </row>
     <row r="110" spans="1:41" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A110" s="48"/>
@@ -6452,38 +6421,36 @@
       <c r="L112" s="6"/>
       <c r="M112" s="26"/>
     </row>
-    <row r="113" spans="1:39" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A113" s="48"/>
       <c r="B113" s="18"/>
-      <c r="C113" s="16"/>
-      <c r="D113" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="E113" s="6"/>
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="21"/>
-      <c r="J113" s="6"/>
-      <c r="K113" s="6"/>
-      <c r="L113" s="6"/>
-      <c r="M113" s="26"/>
+      <c r="C113" s="18"/>
+      <c r="D113" s="18"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="18"/>
+      <c r="G113" s="18"/>
+      <c r="H113" s="18"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="12"/>
+      <c r="K113" s="17"/>
+      <c r="L113" s="17"/>
+      <c r="M113" s="17"/>
     </row>
     <row r="114" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A114" s="48"/>
-      <c r="B114" s="18"/>
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="19"/>
-      <c r="J114" s="12"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="6"/>
+      <c r="F114" s="6"/>
+      <c r="G114" s="6"/>
+      <c r="H114" s="6"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6"/>
       <c r="K114" s="17"/>
       <c r="L114" s="17"/>
       <c r="M114" s="17"/>
     </row>
-    <row r="115" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:39" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A115" s="51"/>
+      <c r="B115" s="8"/>
       <c r="D115" s="12"/>
       <c r="E115" s="6"/>
       <c r="F115" s="6"/>
@@ -6493,195 +6460,181 @@
       <c r="J115" s="6"/>
       <c r="K115" s="17"/>
       <c r="L115" s="17"/>
-      <c r="M115" s="17"/>
-    </row>
-    <row r="116" spans="1:39" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="A116" s="51"/>
-      <c r="B116" s="8"/>
-      <c r="D116" s="12"/>
-      <c r="E116" s="6"/>
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="17"/>
-      <c r="L116" s="17"/>
-      <c r="M116" s="29">
-        <f>M2+M9+M32+M44+M57+M85+M100+M109</f>
+      <c r="M115" s="29">
+        <f>M2+M9+M32+M43+M56+M84+M99+M108</f>
         <v>825</v>
       </c>
     </row>
-    <row r="121" spans="1:39" ht="46.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:39" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A120" s="52" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" s="1"/>
+    </row>
+    <row r="121" spans="1:39" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A121" s="52" t="s">
         <v>130</v>
       </c>
       <c r="B121" s="1"/>
     </row>
-    <row r="122" spans="1:39" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A122" s="52" t="s">
+    <row r="123" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="A123" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="B122" s="1"/>
+      <c r="B123" s="8"/>
+      <c r="C123" s="15" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="124" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A124" s="51" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B124" s="8"/>
       <c r="C124" s="15" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="125" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A125" s="51" t="s">
         <v>134</v>
       </c>
-      <c r="B125" s="8"/>
-      <c r="C125" s="15" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="127" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="1:39" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A126" s="49" t="s">
+        <v>289</v>
+      </c>
+      <c r="AM126" s="39" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="127" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A127" s="49" t="s">
         <v>290</v>
       </c>
-      <c r="AM127" s="39" t="s">
-        <v>165</v>
+      <c r="AM127" s="47" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="128" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A128" s="49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="AM128" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="129" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A129" s="49" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="AM129" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="130" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A130" s="49" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM130" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="131" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A131" s="49" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AM131" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="132" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A132" s="49" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AM132" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="133" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A133" s="49" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="AM133" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="134" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A134" s="49" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AM134" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="135" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A135" s="49" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="AM135" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="136" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A136" s="49" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="AM136" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="137" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A137" s="49" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AM137" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="138" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A138" s="49" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM138" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="139" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A139" s="49" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="AM139" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="140" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A140" s="49" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM140" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="141" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A141" s="49" t="s">
-        <v>302</v>
+        <v>150</v>
       </c>
       <c r="AM141" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="142" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A142" s="49" t="s">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="AM142" s="47" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="143" spans="1:39" x14ac:dyDescent="0.3">
-      <c r="A143" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="AM143" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="D86" r:id="rId1" xr:uid="{DA624192-AF92-421C-B882-954902949584}"/>
+    <hyperlink ref="D85" r:id="rId1" xr:uid="{DA624192-AF92-421C-B882-954902949584}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
